--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120024406</v>
+        <v>120024081</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502726</v>
+        <v>502703</v>
       </c>
       <c r="R7" t="n">
-        <v>6919308</v>
+        <v>6919322</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120024081</v>
+        <v>120024406</v>
       </c>
       <c r="B8" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502703</v>
+        <v>502726</v>
       </c>
       <c r="R8" t="n">
-        <v>6919322</v>
+        <v>6919308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120029012</v>
+        <v>120028121</v>
       </c>
       <c r="B18" t="n">
-        <v>78263</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,25 +2512,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502589</v>
+        <v>502828</v>
       </c>
       <c r="R18" t="n">
-        <v>6919321</v>
+        <v>6919422</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2612,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120028121</v>
+        <v>120029012</v>
       </c>
       <c r="B19" t="n">
-        <v>90527</v>
+        <v>78263</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,25 +2624,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502828</v>
+        <v>502589</v>
       </c>
       <c r="R19" t="n">
-        <v>6919422</v>
+        <v>6919321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120067947</v>
+        <v>120068779</v>
       </c>
       <c r="B32" t="n">
-        <v>90930</v>
+        <v>91884</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4080,25 +4080,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>298</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502748</v>
+        <v>502513</v>
       </c>
       <c r="R32" t="n">
-        <v>6919557</v>
+        <v>6919490</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,12 +4153,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Tillsammans med timmergröppa</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4185,10 +4180,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120068779</v>
+        <v>120067947</v>
       </c>
       <c r="B33" t="n">
-        <v>91884</v>
+        <v>90930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4197,25 +4192,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502513</v>
+        <v>502748</v>
       </c>
       <c r="R33" t="n">
-        <v>6919490</v>
+        <v>6919557</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4260,7 +4255,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4270,7 +4265,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Tillsammans med timmergröppa</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120067558</v>
+        <v>120069378</v>
       </c>
       <c r="B36" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4538,25 +4538,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4566,13 +4566,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502813</v>
+        <v>502481</v>
       </c>
       <c r="R36" t="n">
-        <v>6919527</v>
+        <v>6919451</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4638,10 +4638,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120069378</v>
+        <v>120067558</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4650,25 +4650,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4678,13 +4678,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502481</v>
+        <v>502813</v>
       </c>
       <c r="R37" t="n">
-        <v>6919451</v>
+        <v>6919527</v>
       </c>
       <c r="S37" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -2836,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120067723</v>
+        <v>120069700</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,25 +2848,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502732</v>
+        <v>502566</v>
       </c>
       <c r="R21" t="n">
-        <v>6919555</v>
+        <v>6919324</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,22 +2936,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120069700</v>
+        <v>120069360</v>
       </c>
       <c r="B22" t="n">
-        <v>91844</v>
+        <v>78263</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,25 +2960,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4365</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,13 +2988,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502566</v>
+        <v>502491</v>
       </c>
       <c r="R22" t="n">
-        <v>6919324</v>
+        <v>6919384</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,22 +3048,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120069360</v>
+        <v>120067723</v>
       </c>
       <c r="B23" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,25 +3072,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502491</v>
+        <v>502732</v>
       </c>
       <c r="R23" t="n">
-        <v>6919384</v>
+        <v>6919555</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120068779</v>
+        <v>120067947</v>
       </c>
       <c r="B32" t="n">
-        <v>91884</v>
+        <v>90930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4080,25 +4080,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502513</v>
+        <v>502748</v>
       </c>
       <c r="R32" t="n">
-        <v>6919490</v>
+        <v>6919557</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,7 +4153,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Tillsammans med timmergröppa</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,10 +4185,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120067947</v>
+        <v>120068779</v>
       </c>
       <c r="B33" t="n">
-        <v>90930</v>
+        <v>91884</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4192,25 +4197,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>298</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502748</v>
+        <v>502513</v>
       </c>
       <c r="R33" t="n">
-        <v>6919557</v>
+        <v>6919490</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4255,7 +4260,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4265,12 +4270,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Tillsammans med timmergröppa</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5772,10 +5772,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120065324</v>
+        <v>120066423</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>78263</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5788,42 +5788,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503005</v>
+        <v>502973</v>
       </c>
       <c r="R47" t="n">
-        <v>6919310</v>
+        <v>6919384</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5852,7 +5847,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5862,7 +5857,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5877,22 +5872,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120066423</v>
+        <v>120065324</v>
       </c>
       <c r="B48" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5905,37 +5900,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502973</v>
+        <v>503005</v>
       </c>
       <c r="R48" t="n">
-        <v>6919384</v>
+        <v>6919310</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5989,12 +5989,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120024983</v>
+        <v>120024626</v>
       </c>
       <c r="B2" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502808</v>
+        <v>502784</v>
       </c>
       <c r="R2" t="n">
-        <v>6919302</v>
+        <v>6919311</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120027766</v>
+        <v>120028546</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502871</v>
+        <v>502717</v>
       </c>
       <c r="R3" t="n">
-        <v>6919391</v>
+        <v>6919429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120027814</v>
+        <v>120028121</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502886</v>
+        <v>502828</v>
       </c>
       <c r="R4" t="n">
-        <v>6919441</v>
+        <v>6919422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120031101</v>
+        <v>120024983</v>
       </c>
       <c r="B5" t="n">
-        <v>90494</v>
+        <v>78263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,41 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2013</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502863</v>
+        <v>502808</v>
       </c>
       <c r="R5" t="n">
-        <v>6919305</v>
+        <v>6919302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,18 +1084,27 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1117,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120028686</v>
+        <v>120025266</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502735</v>
+        <v>502825</v>
       </c>
       <c r="R6" t="n">
-        <v>6919361</v>
+        <v>6919306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Inte jättegamla.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1351,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120024406</v>
+        <v>120028274</v>
       </c>
       <c r="B8" t="n">
-        <v>79144</v>
+        <v>57463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,34 +1363,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502726</v>
+        <v>502778</v>
       </c>
       <c r="R8" t="n">
-        <v>6919308</v>
+        <v>6919405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,7 +1468,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120027055</v>
+        <v>120028686</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1504,14 +1509,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502889</v>
+        <v>502735</v>
       </c>
       <c r="R9" t="n">
-        <v>6919376</v>
+        <v>6919361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1558,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Inte jättegamla.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120027825</v>
+        <v>120031101</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>90494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,43 +1602,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2013</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502881</v>
+        <v>502863</v>
       </c>
       <c r="R10" t="n">
-        <v>6919412</v>
+        <v>6919305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,32 +1666,18 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Både gamla och färska spår på samma tall.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1702,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120026409</v>
+        <v>120027825</v>
       </c>
       <c r="B11" t="n">
-        <v>89633</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,34 +1712,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502910</v>
+        <v>502881</v>
       </c>
       <c r="R11" t="n">
-        <v>6919294</v>
+        <v>6919412</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,6 +1787,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Både gamla och färska spår på samma tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120025266</v>
+        <v>120029012</v>
       </c>
       <c r="B12" t="n">
         <v>78263</v>
@@ -1854,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502825</v>
+        <v>502589</v>
       </c>
       <c r="R12" t="n">
-        <v>6919306</v>
+        <v>6919321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1903,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120028274</v>
+        <v>120028984</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,31 +1946,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502778</v>
+        <v>502586</v>
       </c>
       <c r="R13" t="n">
-        <v>6919405</v>
+        <v>6919340</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120027968</v>
+        <v>120026409</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,38 +2059,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502856</v>
+        <v>502910</v>
       </c>
       <c r="R14" t="n">
-        <v>6919392</v>
+        <v>6919294</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120028984</v>
+        <v>120024406</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>79144</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,39 +2175,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502586</v>
+        <v>502726</v>
       </c>
       <c r="R15" t="n">
-        <v>6919340</v>
+        <v>6919308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,7 +2271,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120024626</v>
+        <v>120027814</v>
       </c>
       <c r="B16" t="n">
         <v>91840</v>
@@ -2312,14 +2307,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502784</v>
+        <v>502886</v>
       </c>
       <c r="R16" t="n">
-        <v>6919311</v>
+        <v>6919441</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2388,10 +2383,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120028546</v>
+        <v>120027766</v>
       </c>
       <c r="B17" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,25 +2395,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,10 +2423,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502717</v>
+        <v>502871</v>
       </c>
       <c r="R17" t="n">
-        <v>6919429</v>
+        <v>6919391</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2468,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120028121</v>
+        <v>120027968</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,21 +2511,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2540,10 +2535,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502828</v>
+        <v>502856</v>
       </c>
       <c r="R18" t="n">
-        <v>6919422</v>
+        <v>6919392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2575,7 +2570,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2580,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120029012</v>
+        <v>120027055</v>
       </c>
       <c r="B19" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2628,34 +2623,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502589</v>
+        <v>502889</v>
       </c>
       <c r="R19" t="n">
-        <v>6919321</v>
+        <v>6919376</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120068130</v>
+        <v>120067689</v>
       </c>
       <c r="B20" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502709</v>
+        <v>502765</v>
       </c>
       <c r="R20" t="n">
-        <v>6919568</v>
+        <v>6919539</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,22 +2824,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120069700</v>
+        <v>120065228</v>
       </c>
       <c r="B21" t="n">
-        <v>91844</v>
+        <v>91884</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,38 +2848,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502566</v>
+        <v>503010</v>
       </c>
       <c r="R21" t="n">
-        <v>6919324</v>
+        <v>6919294</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,10 +2948,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120069360</v>
+        <v>120069084</v>
       </c>
       <c r="B22" t="n">
-        <v>78263</v>
+        <v>90527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,25 +2960,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,13 +2988,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502491</v>
+        <v>502514</v>
       </c>
       <c r="R22" t="n">
-        <v>6919384</v>
+        <v>6919477</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,19 +3048,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120067723</v>
+        <v>120068252</v>
       </c>
       <c r="B23" t="n">
         <v>91840</v>
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502732</v>
+        <v>502690</v>
       </c>
       <c r="R23" t="n">
-        <v>6919555</v>
+        <v>6919538</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120065184</v>
+        <v>120065022</v>
       </c>
       <c r="B24" t="n">
-        <v>79144</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3184,41 +3184,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503055</v>
+        <v>503071</v>
       </c>
       <c r="R24" t="n">
-        <v>6919216</v>
+        <v>6919233</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3247,7 +3256,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,7 +3266,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3272,22 +3281,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120065228</v>
+        <v>120069993</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3296,38 +3305,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503010</v>
+        <v>502615</v>
       </c>
       <c r="R25" t="n">
-        <v>6919294</v>
+        <v>6919305</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3359,7 +3377,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3387,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3396,10 +3414,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120069084</v>
+        <v>120069026</v>
       </c>
       <c r="B26" t="n">
-        <v>90527</v>
+        <v>90576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,25 +3426,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3471,7 +3489,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3481,7 +3499,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3508,10 +3526,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120068117</v>
+        <v>120069969</v>
       </c>
       <c r="B27" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3524,21 +3542,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3548,13 +3566,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502709</v>
+        <v>502630</v>
       </c>
       <c r="R27" t="n">
-        <v>6919568</v>
+        <v>6919303</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3583,7 +3601,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3593,7 +3611,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3608,22 +3626,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120066174</v>
+        <v>120067652</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3632,25 +3650,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3660,10 +3678,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502971</v>
+        <v>502795</v>
       </c>
       <c r="R28" t="n">
-        <v>6919362</v>
+        <v>6919545</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3732,7 +3750,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120068337</v>
+        <v>120067975</v>
       </c>
       <c r="B29" t="n">
         <v>91840</v>
@@ -3772,13 +3790,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502628</v>
+        <v>502758</v>
       </c>
       <c r="R29" t="n">
-        <v>6919549</v>
+        <v>6919553</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3807,7 +3825,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3817,7 +3835,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3832,22 +3850,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120065342</v>
+        <v>120067493</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3856,25 +3874,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3884,10 +3902,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503007</v>
+        <v>502805</v>
       </c>
       <c r="R30" t="n">
-        <v>6919317</v>
+        <v>6919532</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,10 +3974,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120069367</v>
+        <v>120066174</v>
       </c>
       <c r="B31" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3968,25 +3986,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3996,10 +4014,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502491</v>
+        <v>502971</v>
       </c>
       <c r="R31" t="n">
-        <v>6919384</v>
+        <v>6919362</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4068,10 +4086,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120067947</v>
+        <v>120068337</v>
       </c>
       <c r="B32" t="n">
-        <v>90930</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4080,25 +4098,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>298</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4108,13 +4126,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502748</v>
+        <v>502628</v>
       </c>
       <c r="R32" t="n">
-        <v>6919557</v>
+        <v>6919549</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4143,7 +4161,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,12 +4171,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Tillsammans med timmergröppa</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4173,22 +4186,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120068779</v>
+        <v>120065184</v>
       </c>
       <c r="B33" t="n">
-        <v>91884</v>
+        <v>79144</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4201,34 +4214,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502513</v>
+        <v>503055</v>
       </c>
       <c r="R33" t="n">
-        <v>6919490</v>
+        <v>6919216</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4260,7 +4273,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4270,7 +4283,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4297,10 +4310,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120065915</v>
+        <v>120067569</v>
       </c>
       <c r="B34" t="n">
-        <v>57463</v>
+        <v>78263</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4313,42 +4326,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502996</v>
+        <v>502813</v>
       </c>
       <c r="R34" t="n">
-        <v>6919352</v>
+        <v>6919527</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4377,7 +4385,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4387,7 +4395,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4402,22 +4410,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120069969</v>
+        <v>120068117</v>
       </c>
       <c r="B35" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4430,21 +4438,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4454,13 +4462,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502630</v>
+        <v>502709</v>
       </c>
       <c r="R35" t="n">
-        <v>6919303</v>
+        <v>6919568</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4489,7 +4497,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4499,7 +4507,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4514,22 +4522,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120069378</v>
+        <v>120067947</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>90930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4538,25 +4546,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4566,13 +4574,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502481</v>
+        <v>502748</v>
       </c>
       <c r="R36" t="n">
-        <v>6919451</v>
+        <v>6919557</v>
       </c>
       <c r="S36" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4601,7 +4609,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4611,7 +4619,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Tillsammans med timmergröppa</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4638,10 +4651,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120067558</v>
+        <v>120066170</v>
       </c>
       <c r="B37" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4654,34 +4667,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502813</v>
+        <v>502988</v>
       </c>
       <c r="R37" t="n">
-        <v>6919527</v>
+        <v>6919354</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4713,7 +4726,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4723,7 +4736,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4750,10 +4763,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120069641</v>
+        <v>120068130</v>
       </c>
       <c r="B38" t="n">
-        <v>57463</v>
+        <v>79144</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4766,42 +4779,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502573</v>
+        <v>502709</v>
       </c>
       <c r="R38" t="n">
-        <v>6919359</v>
+        <v>6919568</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4830,7 +4838,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4840,7 +4848,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4855,22 +4863,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120067493</v>
+        <v>120065915</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4883,34 +4891,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502805</v>
+        <v>502996</v>
       </c>
       <c r="R39" t="n">
-        <v>6919532</v>
+        <v>6919352</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4979,10 +4992,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120068252</v>
+        <v>120069700</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4991,25 +5004,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5019,13 +5032,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502690</v>
+        <v>502566</v>
       </c>
       <c r="R40" t="n">
-        <v>6919538</v>
+        <v>6919324</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5054,7 +5067,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5064,7 +5077,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5079,19 +5092,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120064989</v>
+        <v>120067639</v>
       </c>
       <c r="B41" t="n">
         <v>78263</v>
@@ -5127,17 +5140,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503055</v>
+        <v>502795</v>
       </c>
       <c r="R41" t="n">
-        <v>6919216</v>
+        <v>6919546</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5166,7 +5179,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5176,7 +5189,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5191,22 +5204,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120067311</v>
+        <v>120066423</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5219,37 +5232,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502822</v>
+        <v>502973</v>
       </c>
       <c r="R42" t="n">
-        <v>6919420</v>
+        <v>6919384</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5278,7 +5291,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5288,7 +5301,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5303,22 +5316,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120067652</v>
+        <v>120064989</v>
       </c>
       <c r="B43" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5331,37 +5344,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502795</v>
+        <v>503055</v>
       </c>
       <c r="R43" t="n">
-        <v>6919545</v>
+        <v>6919216</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5390,7 +5403,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5400,7 +5413,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5415,19 +5428,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120067975</v>
+        <v>120067723</v>
       </c>
       <c r="B44" t="n">
         <v>91840</v>
@@ -5467,13 +5480,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502758</v>
+        <v>502732</v>
       </c>
       <c r="R44" t="n">
-        <v>6919553</v>
+        <v>6919555</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5502,7 +5515,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5512,7 +5525,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5527,22 +5540,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120065022</v>
+        <v>120068779</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5551,50 +5564,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503071</v>
+        <v>502513</v>
       </c>
       <c r="R45" t="n">
-        <v>6919233</v>
+        <v>6919490</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5623,7 +5627,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5633,7 +5637,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5648,22 +5652,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120065504</v>
+        <v>120069641</v>
       </c>
       <c r="B46" t="n">
-        <v>91834</v>
+        <v>57463</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5676,34 +5680,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502986</v>
+        <v>502573</v>
       </c>
       <c r="R46" t="n">
-        <v>6919325</v>
+        <v>6919359</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5772,10 +5781,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120066423</v>
+        <v>120067558</v>
       </c>
       <c r="B47" t="n">
-        <v>78263</v>
+        <v>79115</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5788,34 +5797,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502973</v>
+        <v>502813</v>
       </c>
       <c r="R47" t="n">
-        <v>6919384</v>
+        <v>6919527</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5847,7 +5856,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5857,7 +5866,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5884,10 +5893,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120065324</v>
+        <v>120065504</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>91834</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5900,39 +5909,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503005</v>
+        <v>502986</v>
       </c>
       <c r="R48" t="n">
-        <v>6919310</v>
+        <v>6919325</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6001,7 +6005,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120067639</v>
+        <v>120069360</v>
       </c>
       <c r="B49" t="n">
         <v>78263</v>
@@ -6041,10 +6045,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502795</v>
+        <v>502491</v>
       </c>
       <c r="R49" t="n">
-        <v>6919546</v>
+        <v>6919384</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6113,10 +6117,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120067569</v>
+        <v>120069367</v>
       </c>
       <c r="B50" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6129,21 +6133,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6153,13 +6157,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502813</v>
+        <v>502491</v>
       </c>
       <c r="R50" t="n">
-        <v>6919527</v>
+        <v>6919384</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6188,7 +6192,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6198,7 +6202,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6213,22 +6217,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120069993</v>
+        <v>120065342</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6237,50 +6241,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502615</v>
+        <v>503007</v>
       </c>
       <c r="R51" t="n">
-        <v>6919305</v>
+        <v>6919317</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6309,7 +6304,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6319,7 +6314,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6334,22 +6329,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120067689</v>
+        <v>120065324</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6358,38 +6353,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502765</v>
+        <v>503005</v>
       </c>
       <c r="R52" t="n">
-        <v>6919539</v>
+        <v>6919310</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120066170</v>
+        <v>120067311</v>
       </c>
       <c r="B53" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6474,37 +6474,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502988</v>
+        <v>502822</v>
       </c>
       <c r="R53" t="n">
-        <v>6919354</v>
+        <v>6919420</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6558,22 +6558,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120069026</v>
+        <v>120069378</v>
       </c>
       <c r="B54" t="n">
-        <v>90576</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>502514</v>
+        <v>502481</v>
       </c>
       <c r="R54" t="n">
-        <v>6919477</v>
+        <v>6919451</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6679,6 +6679,1330 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120120181</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>502417</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6919645</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120142120</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>502335</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6919623</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120120227</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>502410</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6919658</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120118385</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78263</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>502456</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6919412</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120120273</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78263</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>502391</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6919666</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120142073</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78171</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>353</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>502373</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6919669</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120119728</v>
+      </c>
+      <c r="B61" t="n">
+        <v>90807</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>65</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>502366</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6919546</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120142102</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78171</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>353</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>502265</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6919613</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120118347</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78171</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>353</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>502471</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6919424</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120119046</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78263</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>502418</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6919456</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120142089</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>502373</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6919669</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120121333</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>502264</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6919557</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -1818,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120029012</v>
+        <v>120028984</v>
       </c>
       <c r="B12" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,34 +1834,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502589</v>
+        <v>502586</v>
       </c>
       <c r="R12" t="n">
-        <v>6919321</v>
+        <v>6919340</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120028984</v>
+        <v>120029012</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>78263</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,39 +1951,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502586</v>
+        <v>502589</v>
       </c>
       <c r="R13" t="n">
-        <v>6919340</v>
+        <v>6919321</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120026409</v>
+        <v>120024406</v>
       </c>
       <c r="B14" t="n">
-        <v>89633</v>
+        <v>79144</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,34 +2063,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502910</v>
+        <v>502726</v>
       </c>
       <c r="R14" t="n">
-        <v>6919294</v>
+        <v>6919308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120024406</v>
+        <v>120026409</v>
       </c>
       <c r="B15" t="n">
-        <v>79144</v>
+        <v>89633</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,34 +2175,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502726</v>
+        <v>502910</v>
       </c>
       <c r="R15" t="n">
-        <v>6919308</v>
+        <v>6919294</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -4992,10 +4992,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120069700</v>
+        <v>120067639</v>
       </c>
       <c r="B40" t="n">
-        <v>91844</v>
+        <v>78263</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5004,25 +5004,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4365</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502566</v>
+        <v>502795</v>
       </c>
       <c r="R40" t="n">
-        <v>6919324</v>
+        <v>6919546</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,22 +5092,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120067639</v>
+        <v>120069700</v>
       </c>
       <c r="B41" t="n">
-        <v>78263</v>
+        <v>91844</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5116,25 +5116,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>4365</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502795</v>
+        <v>502566</v>
       </c>
       <c r="R41" t="n">
-        <v>6919546</v>
+        <v>6919324</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,22 +5204,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120066423</v>
+        <v>120067723</v>
       </c>
       <c r="B42" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5228,41 +5228,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502973</v>
+        <v>502732</v>
       </c>
       <c r="R42" t="n">
-        <v>6919384</v>
+        <v>6919555</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,19 +5316,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120064989</v>
+        <v>120066423</v>
       </c>
       <c r="B43" t="n">
         <v>78263</v>
@@ -5364,14 +5364,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503055</v>
+        <v>502973</v>
       </c>
       <c r="R43" t="n">
-        <v>6919216</v>
+        <v>6919384</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5440,10 +5440,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120067723</v>
+        <v>120064989</v>
       </c>
       <c r="B44" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5452,41 +5452,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502732</v>
+        <v>503055</v>
       </c>
       <c r="R44" t="n">
-        <v>6919555</v>
+        <v>6919216</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5540,12 +5540,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120067311</v>
+        <v>120069378</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6470,25 +6470,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6498,13 +6498,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502822</v>
+        <v>502481</v>
       </c>
       <c r="R53" t="n">
-        <v>6919420</v>
+        <v>6919451</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6558,22 +6558,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120069378</v>
+        <v>120067311</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>502481</v>
+        <v>502822</v>
       </c>
       <c r="R54" t="n">
-        <v>6919451</v>
+        <v>6919420</v>
       </c>
       <c r="S54" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,12 +6670,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120024626</v>
+        <v>120027766</v>
       </c>
       <c r="B2" t="n">
         <v>91840</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502784</v>
+        <v>502871</v>
       </c>
       <c r="R2" t="n">
-        <v>6919311</v>
+        <v>6919391</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120028546</v>
+        <v>120024081</v>
       </c>
       <c r="B3" t="n">
-        <v>90807</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502717</v>
+        <v>502703</v>
       </c>
       <c r="R3" t="n">
-        <v>6919429</v>
+        <v>6919322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120028121</v>
+        <v>120028686</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502828</v>
+        <v>502735</v>
       </c>
       <c r="R4" t="n">
-        <v>6919422</v>
+        <v>6919361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,6 +990,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Inte jättegamla.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120024983</v>
+        <v>120027055</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502808</v>
+        <v>502889</v>
       </c>
       <c r="R5" t="n">
-        <v>6919302</v>
+        <v>6919376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120025266</v>
+        <v>120028984</v>
       </c>
       <c r="B6" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502825</v>
+        <v>502586</v>
       </c>
       <c r="R6" t="n">
-        <v>6919306</v>
+        <v>6919340</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120024081</v>
+        <v>120029012</v>
       </c>
       <c r="B7" t="n">
         <v>78263</v>
@@ -1275,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502703</v>
+        <v>502589</v>
       </c>
       <c r="R7" t="n">
-        <v>6919322</v>
+        <v>6919321</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120028274</v>
+        <v>120024406</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>79144</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,43 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502778</v>
+        <v>502726</v>
       </c>
       <c r="R8" t="n">
-        <v>6919405</v>
+        <v>6919308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120028686</v>
+        <v>120027968</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,43 +1491,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502735</v>
+        <v>502856</v>
       </c>
       <c r="R9" t="n">
-        <v>6919361</v>
+        <v>6919392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,12 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Inte jättegamla.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120031101</v>
+        <v>120024983</v>
       </c>
       <c r="B10" t="n">
-        <v>90494</v>
+        <v>78263</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,41 +1603,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2013</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502863</v>
+        <v>502808</v>
       </c>
       <c r="R10" t="n">
-        <v>6919305</v>
+        <v>6919302</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,18 +1664,27 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1696,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120027825</v>
+        <v>120026409</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>89633</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,39 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502881</v>
+        <v>502910</v>
       </c>
       <c r="R11" t="n">
-        <v>6919412</v>
+        <v>6919294</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,11 +1789,6 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Både gamla och färska spår på samma tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120028984</v>
+        <v>120031101</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>90494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,43 +1827,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2013</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502586</v>
+        <v>502863</v>
       </c>
       <c r="R12" t="n">
-        <v>6919340</v>
+        <v>6919305</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,27 +1891,18 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1935,7 +1921,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120029012</v>
+        <v>120025266</v>
       </c>
       <c r="B13" t="n">
         <v>78263</v>
@@ -1975,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502589</v>
+        <v>502825</v>
       </c>
       <c r="R13" t="n">
-        <v>6919321</v>
+        <v>6919306</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120024406</v>
+        <v>120024626</v>
       </c>
       <c r="B14" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,25 +2045,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2087,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502726</v>
+        <v>502784</v>
       </c>
       <c r="R14" t="n">
-        <v>6919308</v>
+        <v>6919311</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120026409</v>
+        <v>120028274</v>
       </c>
       <c r="B15" t="n">
-        <v>89633</v>
+        <v>57463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,34 +2161,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502910</v>
+        <v>502778</v>
       </c>
       <c r="R15" t="n">
-        <v>6919294</v>
+        <v>6919405</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,7 +2229,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2239,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2383,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120027766</v>
+        <v>120027825</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,38 +2390,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502871</v>
+        <v>502881</v>
       </c>
       <c r="R17" t="n">
-        <v>6919391</v>
+        <v>6919412</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,6 +2469,11 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Både gamla och färska spår på samma tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120027968</v>
+        <v>120028121</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,21 +2516,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2535,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502856</v>
+        <v>502828</v>
       </c>
       <c r="R18" t="n">
-        <v>6919392</v>
+        <v>6919422</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2580,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120027055</v>
+        <v>120028546</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>90807</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,43 +2624,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502889</v>
+        <v>502717</v>
       </c>
       <c r="R19" t="n">
-        <v>6919376</v>
+        <v>6919429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120067689</v>
+        <v>120067569</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502765</v>
+        <v>502813</v>
       </c>
       <c r="R20" t="n">
-        <v>6919539</v>
+        <v>6919527</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,22 +2824,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120065228</v>
+        <v>120069378</v>
       </c>
       <c r="B21" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,41 +2848,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503010</v>
+        <v>502481</v>
       </c>
       <c r="R21" t="n">
-        <v>6919294</v>
+        <v>6919451</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,10 +2948,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120069084</v>
+        <v>120067558</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>79115</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,25 +2960,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502514</v>
+        <v>502813</v>
       </c>
       <c r="R22" t="n">
-        <v>6919477</v>
+        <v>6919527</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3060,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120068252</v>
+        <v>120064989</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,41 +3072,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502690</v>
+        <v>503055</v>
       </c>
       <c r="R23" t="n">
-        <v>6919538</v>
+        <v>6919216</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3160,22 +3160,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120065022</v>
+        <v>120069700</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>91844</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3188,46 +3188,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503071</v>
+        <v>502566</v>
       </c>
       <c r="R24" t="n">
-        <v>6919233</v>
+        <v>6919324</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3256,7 +3247,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3266,7 +3257,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,22 +3272,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120069993</v>
+        <v>120069026</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>90576</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3305,47 +3296,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502615</v>
+        <v>502514</v>
       </c>
       <c r="R25" t="n">
-        <v>6919305</v>
+        <v>6919477</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3377,7 +3359,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3387,7 +3369,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3414,10 +3396,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120069026</v>
+        <v>120067311</v>
       </c>
       <c r="B26" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3430,21 +3412,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3454,13 +3436,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502514</v>
+        <v>502822</v>
       </c>
       <c r="R26" t="n">
-        <v>6919477</v>
+        <v>6919420</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3489,7 +3471,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3499,7 +3481,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3514,22 +3496,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120069969</v>
+        <v>120067652</v>
       </c>
       <c r="B27" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3542,21 +3524,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3566,10 +3548,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502630</v>
+        <v>502795</v>
       </c>
       <c r="R27" t="n">
-        <v>6919303</v>
+        <v>6919545</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3638,10 +3620,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120067652</v>
+        <v>120065228</v>
       </c>
       <c r="B28" t="n">
-        <v>79115</v>
+        <v>91884</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3654,37 +3636,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502795</v>
+        <v>503010</v>
       </c>
       <c r="R28" t="n">
-        <v>6919545</v>
+        <v>6919294</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3713,7 +3695,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3723,7 +3705,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3738,19 +3720,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120067975</v>
+        <v>120067723</v>
       </c>
       <c r="B29" t="n">
         <v>91840</v>
@@ -3790,13 +3772,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502758</v>
+        <v>502732</v>
       </c>
       <c r="R29" t="n">
-        <v>6919553</v>
+        <v>6919555</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3825,7 +3807,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3835,7 +3817,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3850,22 +3832,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120067493</v>
+        <v>120065022</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3874,38 +3856,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502805</v>
+        <v>503071</v>
       </c>
       <c r="R30" t="n">
-        <v>6919532</v>
+        <v>6919233</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3974,10 +3965,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120066174</v>
+        <v>120066423</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3986,41 +3977,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502971</v>
+        <v>502973</v>
       </c>
       <c r="R31" t="n">
-        <v>6919362</v>
+        <v>6919384</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4049,7 +4040,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4059,7 +4050,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4074,22 +4065,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120068337</v>
+        <v>120069969</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4098,25 +4089,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4126,10 +4117,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502628</v>
+        <v>502630</v>
       </c>
       <c r="R32" t="n">
-        <v>6919549</v>
+        <v>6919303</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4198,10 +4189,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120065184</v>
+        <v>120065504</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>91834</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4214,37 +4205,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503055</v>
+        <v>502986</v>
       </c>
       <c r="R33" t="n">
-        <v>6919216</v>
+        <v>6919325</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4273,7 +4264,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4283,7 +4274,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4298,22 +4289,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120067569</v>
+        <v>120069367</v>
       </c>
       <c r="B34" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4326,21 +4317,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4350,13 +4341,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502813</v>
+        <v>502491</v>
       </c>
       <c r="R34" t="n">
-        <v>6919527</v>
+        <v>6919384</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4385,7 +4376,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4395,7 +4386,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4410,22 +4401,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120068117</v>
+        <v>120067639</v>
       </c>
       <c r="B35" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4438,21 +4429,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4462,13 +4453,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502709</v>
+        <v>502795</v>
       </c>
       <c r="R35" t="n">
-        <v>6919568</v>
+        <v>6919546</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4497,7 +4488,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4507,7 +4498,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4522,22 +4513,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120067947</v>
+        <v>120068337</v>
       </c>
       <c r="B36" t="n">
-        <v>90930</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4546,25 +4537,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>298</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4574,13 +4565,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502748</v>
+        <v>502628</v>
       </c>
       <c r="R36" t="n">
-        <v>6919557</v>
+        <v>6919549</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4609,7 +4600,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4619,12 +4610,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Tillsammans med timmergröppa</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4639,22 +4625,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120066170</v>
+        <v>120068779</v>
       </c>
       <c r="B37" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4667,34 +4653,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502988</v>
+        <v>502513</v>
       </c>
       <c r="R37" t="n">
-        <v>6919354</v>
+        <v>6919490</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4726,7 +4712,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4736,7 +4722,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4763,10 +4749,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120068130</v>
+        <v>120065342</v>
       </c>
       <c r="B38" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4775,25 +4761,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4803,13 +4789,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502709</v>
+        <v>503007</v>
       </c>
       <c r="R38" t="n">
-        <v>6919568</v>
+        <v>6919317</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4838,7 +4824,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4848,7 +4834,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4863,22 +4849,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120065915</v>
+        <v>120069993</v>
       </c>
       <c r="B39" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4887,31 +4873,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4920,13 +4910,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502996</v>
+        <v>502615</v>
       </c>
       <c r="R39" t="n">
-        <v>6919352</v>
+        <v>6919305</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4955,7 +4945,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4965,7 +4955,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4980,22 +4970,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120067639</v>
+        <v>120065915</v>
       </c>
       <c r="B40" t="n">
-        <v>78263</v>
+        <v>57463</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5008,34 +4998,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502795</v>
+        <v>502996</v>
       </c>
       <c r="R40" t="n">
-        <v>6919546</v>
+        <v>6919352</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5104,10 +5099,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120069700</v>
+        <v>120065324</v>
       </c>
       <c r="B41" t="n">
-        <v>91844</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5116,41 +5111,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502566</v>
+        <v>503005</v>
       </c>
       <c r="R41" t="n">
-        <v>6919324</v>
+        <v>6919310</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,22 +5204,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120067723</v>
+        <v>120066170</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5228,41 +5228,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502732</v>
+        <v>502988</v>
       </c>
       <c r="R42" t="n">
-        <v>6919555</v>
+        <v>6919354</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,22 +5316,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120066423</v>
+        <v>120068252</v>
       </c>
       <c r="B43" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5340,41 +5340,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502973</v>
+        <v>502690</v>
       </c>
       <c r="R43" t="n">
-        <v>6919384</v>
+        <v>6919538</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,22 +5428,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120064989</v>
+        <v>120069084</v>
       </c>
       <c r="B44" t="n">
-        <v>78263</v>
+        <v>90527</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5452,38 +5452,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503055</v>
+        <v>502514</v>
       </c>
       <c r="R44" t="n">
-        <v>6919216</v>
+        <v>6919477</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5552,10 +5552,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120068779</v>
+        <v>120068130</v>
       </c>
       <c r="B45" t="n">
-        <v>91884</v>
+        <v>79144</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5568,21 +5568,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502513</v>
+        <v>502709</v>
       </c>
       <c r="R45" t="n">
-        <v>6919490</v>
+        <v>6919568</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5664,10 +5664,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120069641</v>
+        <v>120068117</v>
       </c>
       <c r="B46" t="n">
-        <v>57463</v>
+        <v>79115</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5680,42 +5680,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502573</v>
+        <v>502709</v>
       </c>
       <c r="R46" t="n">
-        <v>6919359</v>
+        <v>6919568</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5744,7 +5739,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5754,7 +5749,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5769,22 +5764,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120067558</v>
+        <v>120067975</v>
       </c>
       <c r="B47" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5793,25 +5788,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5821,10 +5816,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502813</v>
+        <v>502758</v>
       </c>
       <c r="R47" t="n">
-        <v>6919527</v>
+        <v>6919553</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5856,7 +5851,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5866,7 +5861,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5893,10 +5888,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120065504</v>
+        <v>120067947</v>
       </c>
       <c r="B48" t="n">
-        <v>91834</v>
+        <v>90930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5905,25 +5900,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5933,13 +5928,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502986</v>
+        <v>502748</v>
       </c>
       <c r="R48" t="n">
-        <v>6919325</v>
+        <v>6919557</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5968,7 +5963,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5978,7 +5973,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Tillsammans med timmergröppa</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5993,22 +5993,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120069360</v>
+        <v>120066174</v>
       </c>
       <c r="B49" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6017,25 +6017,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502491</v>
+        <v>502971</v>
       </c>
       <c r="R49" t="n">
-        <v>6919384</v>
+        <v>6919362</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120069367</v>
+        <v>120067689</v>
       </c>
       <c r="B50" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6129,25 +6129,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502491</v>
+        <v>502765</v>
       </c>
       <c r="R50" t="n">
-        <v>6919384</v>
+        <v>6919539</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120065342</v>
+        <v>120067493</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6241,25 +6241,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503007</v>
+        <v>502805</v>
       </c>
       <c r="R51" t="n">
-        <v>6919317</v>
+        <v>6919532</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120065324</v>
+        <v>120065184</v>
       </c>
       <c r="B52" t="n">
-        <v>57310</v>
+        <v>79144</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6357,42 +6357,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503005</v>
+        <v>503055</v>
       </c>
       <c r="R52" t="n">
-        <v>6919310</v>
+        <v>6919216</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6421,7 +6416,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6431,7 +6426,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6446,22 +6441,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120069378</v>
+        <v>120069641</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6470,41 +6465,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502481</v>
+        <v>502573</v>
       </c>
       <c r="R53" t="n">
-        <v>6919451</v>
+        <v>6919359</v>
       </c>
       <c r="S53" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6558,22 +6558,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120067311</v>
+        <v>120069360</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6586,21 +6586,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>502822</v>
+        <v>502491</v>
       </c>
       <c r="R54" t="n">
-        <v>6919420</v>
+        <v>6919384</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120120181</v>
+        <v>120119046</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6694,25 +6694,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>502417</v>
+        <v>502418</v>
       </c>
       <c r="R55" t="n">
-        <v>6919645</v>
+        <v>6919456</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6794,10 +6794,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120142120</v>
+        <v>120142102</v>
       </c>
       <c r="B56" t="n">
-        <v>57463</v>
+        <v>78171</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6810,31 +6810,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6842,10 +6837,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502335</v>
+        <v>502265</v>
       </c>
       <c r="R56" t="n">
-        <v>6919623</v>
+        <v>6919613</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6886,6 +6881,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7016,10 +7012,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120118385</v>
+        <v>120120181</v>
       </c>
       <c r="B58" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7028,25 +7024,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7056,10 +7052,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502456</v>
+        <v>502417</v>
       </c>
       <c r="R58" t="n">
-        <v>6919412</v>
+        <v>6919645</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7128,10 +7124,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120120273</v>
+        <v>120142073</v>
       </c>
       <c r="B59" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7144,34 +7140,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502391</v>
+        <v>502373</v>
       </c>
       <c r="R59" t="n">
-        <v>6919666</v>
+        <v>6919669</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7201,27 +7200,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7240,10 +7230,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120142073</v>
+        <v>120142089</v>
       </c>
       <c r="B60" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7252,25 +7242,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7346,10 +7336,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120119728</v>
+        <v>120142120</v>
       </c>
       <c r="B61" t="n">
-        <v>90807</v>
+        <v>57463</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7358,38 +7348,46 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>65</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502366</v>
+        <v>502335</v>
       </c>
       <c r="R61" t="n">
-        <v>6919546</v>
+        <v>6919623</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7419,19 +7417,9 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7458,10 +7446,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120142102</v>
+        <v>120119728</v>
       </c>
       <c r="B62" t="n">
-        <v>78171</v>
+        <v>90807</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7470,41 +7458,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502265</v>
+        <v>502366</v>
       </c>
       <c r="R62" t="n">
-        <v>6919613</v>
+        <v>6919546</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7534,18 +7519,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7564,10 +7558,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120118347</v>
+        <v>120120273</v>
       </c>
       <c r="B63" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7580,21 +7574,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7604,10 +7598,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502471</v>
+        <v>502391</v>
       </c>
       <c r="R63" t="n">
-        <v>6919424</v>
+        <v>6919666</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7676,10 +7670,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120119046</v>
+        <v>120121333</v>
       </c>
       <c r="B64" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7688,25 +7682,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7716,10 +7710,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502418</v>
+        <v>502264</v>
       </c>
       <c r="R64" t="n">
-        <v>6919456</v>
+        <v>6919557</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7751,7 +7745,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7761,7 +7755,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7788,10 +7782,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120142089</v>
+        <v>120118347</v>
       </c>
       <c r="B65" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7800,41 +7794,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>502373</v>
+        <v>502471</v>
       </c>
       <c r="R65" t="n">
-        <v>6919669</v>
+        <v>6919424</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7864,18 +7855,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7894,10 +7894,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120121333</v>
+        <v>120118385</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7906,25 +7906,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502264</v>
+        <v>502456</v>
       </c>
       <c r="R66" t="n">
-        <v>6919557</v>
+        <v>6919412</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -3172,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120069700</v>
+        <v>120069026</v>
       </c>
       <c r="B24" t="n">
-        <v>91844</v>
+        <v>90576</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3184,25 +3184,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4365</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502566</v>
+        <v>502514</v>
       </c>
       <c r="R24" t="n">
-        <v>6919324</v>
+        <v>6919477</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,10 +3284,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120069026</v>
+        <v>120069700</v>
       </c>
       <c r="B25" t="n">
-        <v>90576</v>
+        <v>91844</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3296,25 +3296,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502514</v>
+        <v>502566</v>
       </c>
       <c r="R25" t="n">
-        <v>6919477</v>
+        <v>6919324</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120024081</v>
+        <v>120027825</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502703</v>
+        <v>502881</v>
       </c>
       <c r="R3" t="n">
-        <v>6919322</v>
+        <v>6919412</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,6 +878,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Både gamla och färska spår på samma tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120028686</v>
+        <v>120024081</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78263</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502735</v>
+        <v>502703</v>
       </c>
       <c r="R4" t="n">
-        <v>6919361</v>
+        <v>6919322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Inte jättegamla.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120027055</v>
+        <v>120027814</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,43 +1033,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502889</v>
+        <v>502886</v>
       </c>
       <c r="R5" t="n">
-        <v>6919376</v>
+        <v>6919441</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120028984</v>
+        <v>120025266</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502586</v>
+        <v>502825</v>
       </c>
       <c r="R6" t="n">
-        <v>6919340</v>
+        <v>6919306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120029012</v>
+        <v>120028274</v>
       </c>
       <c r="B7" t="n">
-        <v>78263</v>
+        <v>57463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1261,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502589</v>
+        <v>502778</v>
       </c>
       <c r="R7" t="n">
-        <v>6919321</v>
+        <v>6919405</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120024406</v>
+        <v>120024983</v>
       </c>
       <c r="B8" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502726</v>
+        <v>502808</v>
       </c>
       <c r="R8" t="n">
-        <v>6919308</v>
+        <v>6919302</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120027968</v>
+        <v>120028546</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502856</v>
+        <v>502717</v>
       </c>
       <c r="R9" t="n">
-        <v>6919392</v>
+        <v>6919429</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120024983</v>
+        <v>120024406</v>
       </c>
       <c r="B10" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502808</v>
+        <v>502726</v>
       </c>
       <c r="R10" t="n">
-        <v>6919302</v>
+        <v>6919308</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120026409</v>
+        <v>120027055</v>
       </c>
       <c r="B11" t="n">
-        <v>89633</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1718,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502910</v>
+        <v>502889</v>
       </c>
       <c r="R11" t="n">
-        <v>6919294</v>
+        <v>6919376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120031101</v>
+        <v>120028121</v>
       </c>
       <c r="B12" t="n">
-        <v>90494</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,41 +1831,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2013</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502863</v>
+        <v>502828</v>
       </c>
       <c r="R12" t="n">
-        <v>6919305</v>
+        <v>6919422</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,18 +1892,27 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1921,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120025266</v>
+        <v>120028686</v>
       </c>
       <c r="B13" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,34 +1947,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502825</v>
+        <v>502735</v>
       </c>
       <c r="R13" t="n">
-        <v>6919306</v>
+        <v>6919361</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Inte jättegamla.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120024626</v>
+        <v>120029012</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,25 +2065,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502784</v>
+        <v>502589</v>
       </c>
       <c r="R14" t="n">
-        <v>6919311</v>
+        <v>6919321</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120028274</v>
+        <v>120028984</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,31 +2181,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2194,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502778</v>
+        <v>502586</v>
       </c>
       <c r="R15" t="n">
-        <v>6919405</v>
+        <v>6919340</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2266,7 +2282,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120027814</v>
+        <v>120027968</v>
       </c>
       <c r="B16" t="n">
         <v>91840</v>
@@ -2302,14 +2318,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502886</v>
+        <v>502856</v>
       </c>
       <c r="R16" t="n">
-        <v>6919441</v>
+        <v>6919392</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120027825</v>
+        <v>120026409</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>89633</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,39 +2410,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502881</v>
+        <v>502910</v>
       </c>
       <c r="R17" t="n">
-        <v>6919412</v>
+        <v>6919294</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,11 +2480,6 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Både gamla och färska spår på samma tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120028121</v>
+        <v>120024626</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,21 +2522,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2540,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502828</v>
+        <v>502784</v>
       </c>
       <c r="R18" t="n">
-        <v>6919422</v>
+        <v>6919311</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2575,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120028546</v>
+        <v>120031101</v>
       </c>
       <c r="B19" t="n">
-        <v>90807</v>
+        <v>90494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,38 +2630,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>2013</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502717</v>
+        <v>502863</v>
       </c>
       <c r="R19" t="n">
-        <v>6919429</v>
+        <v>6919305</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2685,27 +2694,18 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120067569</v>
+        <v>120067723</v>
       </c>
       <c r="B20" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502813</v>
+        <v>502732</v>
       </c>
       <c r="R20" t="n">
-        <v>6919527</v>
+        <v>6919555</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,12 +2824,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120067558</v>
+        <v>120068130</v>
       </c>
       <c r="B22" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502813</v>
+        <v>502709</v>
       </c>
       <c r="R22" t="n">
-        <v>6919527</v>
+        <v>6919568</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3060,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120064989</v>
+        <v>120068117</v>
       </c>
       <c r="B23" t="n">
-        <v>78263</v>
+        <v>79115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3076,34 +3076,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503055</v>
+        <v>502709</v>
       </c>
       <c r="R23" t="n">
-        <v>6919216</v>
+        <v>6919568</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120069026</v>
+        <v>120064989</v>
       </c>
       <c r="B24" t="n">
-        <v>90576</v>
+        <v>78263</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3188,34 +3188,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502514</v>
+        <v>503055</v>
       </c>
       <c r="R24" t="n">
-        <v>6919477</v>
+        <v>6919216</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,10 +3284,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120069700</v>
+        <v>120065324</v>
       </c>
       <c r="B25" t="n">
-        <v>91844</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3296,41 +3296,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502566</v>
+        <v>503005</v>
       </c>
       <c r="R25" t="n">
-        <v>6919324</v>
+        <v>6919310</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3359,7 +3364,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3374,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3384,22 +3389,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120067311</v>
+        <v>120065342</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,25 +3413,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3436,10 +3441,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502822</v>
+        <v>503007</v>
       </c>
       <c r="R26" t="n">
-        <v>6919420</v>
+        <v>6919317</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3508,10 +3513,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120067652</v>
+        <v>120069084</v>
       </c>
       <c r="B27" t="n">
-        <v>79115</v>
+        <v>90527</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3520,25 +3525,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3548,13 +3553,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502795</v>
+        <v>502514</v>
       </c>
       <c r="R27" t="n">
-        <v>6919545</v>
+        <v>6919477</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3583,7 +3588,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3593,7 +3598,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3608,19 +3613,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120065228</v>
+        <v>120068779</v>
       </c>
       <c r="B28" t="n">
         <v>91884</v>
@@ -3656,14 +3661,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503010</v>
+        <v>502513</v>
       </c>
       <c r="R28" t="n">
-        <v>6919294</v>
+        <v>6919490</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3695,7 +3700,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3705,7 +3710,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3732,10 +3737,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120067723</v>
+        <v>120069026</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>90576</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3744,25 +3749,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3772,13 +3777,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502732</v>
+        <v>502514</v>
       </c>
       <c r="R29" t="n">
-        <v>6919555</v>
+        <v>6919477</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3807,7 +3812,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3817,7 +3822,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3832,22 +3837,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120065022</v>
+        <v>120066423</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3856,50 +3861,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503071</v>
+        <v>502973</v>
       </c>
       <c r="R30" t="n">
-        <v>6919233</v>
+        <v>6919384</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3928,7 +3924,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3938,7 +3934,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3953,22 +3949,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120066423</v>
+        <v>120068337</v>
       </c>
       <c r="B31" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3977,41 +3973,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502973</v>
+        <v>502628</v>
       </c>
       <c r="R31" t="n">
-        <v>6919384</v>
+        <v>6919549</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4040,7 +4036,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4050,7 +4046,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,22 +4061,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120069969</v>
+        <v>120069993</v>
       </c>
       <c r="B32" t="n">
-        <v>78171</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4089,41 +4085,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502630</v>
+        <v>502615</v>
       </c>
       <c r="R32" t="n">
-        <v>6919303</v>
+        <v>6919305</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4152,7 +4157,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4162,7 +4167,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,22 +4182,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120065504</v>
+        <v>120067311</v>
       </c>
       <c r="B33" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4205,21 +4210,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4229,10 +4234,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502986</v>
+        <v>502822</v>
       </c>
       <c r="R33" t="n">
-        <v>6919325</v>
+        <v>6919420</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4301,10 +4306,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120069367</v>
+        <v>120066170</v>
       </c>
       <c r="B34" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4317,37 +4322,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502491</v>
+        <v>502988</v>
       </c>
       <c r="R34" t="n">
-        <v>6919384</v>
+        <v>6919354</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4376,7 +4381,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4386,7 +4391,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4401,22 +4406,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120067639</v>
+        <v>120065184</v>
       </c>
       <c r="B35" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4429,37 +4434,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502795</v>
+        <v>503055</v>
       </c>
       <c r="R35" t="n">
-        <v>6919546</v>
+        <v>6919216</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4488,7 +4493,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4498,7 +4503,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4513,19 +4518,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120068337</v>
+        <v>120067975</v>
       </c>
       <c r="B36" t="n">
         <v>91840</v>
@@ -4565,13 +4570,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502628</v>
+        <v>502758</v>
       </c>
       <c r="R36" t="n">
-        <v>6919549</v>
+        <v>6919553</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4600,7 +4605,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4610,7 +4615,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4625,22 +4630,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120068779</v>
+        <v>120069367</v>
       </c>
       <c r="B37" t="n">
-        <v>91884</v>
+        <v>78262</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4653,21 +4658,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4677,13 +4682,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502513</v>
+        <v>502491</v>
       </c>
       <c r="R37" t="n">
-        <v>6919490</v>
+        <v>6919384</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4712,7 +4717,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4722,7 +4727,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4737,22 +4742,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120065342</v>
+        <v>120067652</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4761,25 +4766,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4789,10 +4794,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503007</v>
+        <v>502795</v>
       </c>
       <c r="R38" t="n">
-        <v>6919317</v>
+        <v>6919545</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4861,10 +4866,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120069993</v>
+        <v>120065228</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4873,47 +4878,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502615</v>
+        <v>503010</v>
       </c>
       <c r="R39" t="n">
-        <v>6919305</v>
+        <v>6919294</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4945,7 +4941,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4955,7 +4951,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5099,10 +5095,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120065324</v>
+        <v>120067558</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>79115</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5115,42 +5111,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503005</v>
+        <v>502813</v>
       </c>
       <c r="R41" t="n">
-        <v>6919310</v>
+        <v>6919527</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5179,7 +5170,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5189,7 +5180,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,22 +5195,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120066170</v>
+        <v>120067493</v>
       </c>
       <c r="B42" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5232,37 +5223,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502988</v>
+        <v>502805</v>
       </c>
       <c r="R42" t="n">
-        <v>6919354</v>
+        <v>6919532</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5291,7 +5282,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5301,7 +5292,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,22 +5307,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120068252</v>
+        <v>120065504</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5340,25 +5331,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5368,10 +5359,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502690</v>
+        <v>502986</v>
       </c>
       <c r="R43" t="n">
-        <v>6919538</v>
+        <v>6919325</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5440,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120069084</v>
+        <v>120069969</v>
       </c>
       <c r="B44" t="n">
-        <v>90527</v>
+        <v>78171</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5452,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5480,13 +5471,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502514</v>
+        <v>502630</v>
       </c>
       <c r="R44" t="n">
-        <v>6919477</v>
+        <v>6919303</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5515,7 +5506,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5525,7 +5516,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5540,22 +5531,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120068130</v>
+        <v>120069700</v>
       </c>
       <c r="B45" t="n">
-        <v>79144</v>
+        <v>91844</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5564,25 +5555,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5592,10 +5583,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502709</v>
+        <v>502566</v>
       </c>
       <c r="R45" t="n">
-        <v>6919568</v>
+        <v>6919324</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5627,7 +5618,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5637,7 +5628,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5664,10 +5655,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120068117</v>
+        <v>120068252</v>
       </c>
       <c r="B46" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5676,25 +5667,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5704,13 +5695,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502709</v>
+        <v>502690</v>
       </c>
       <c r="R46" t="n">
-        <v>6919568</v>
+        <v>6919538</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5739,7 +5730,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5749,7 +5740,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5764,22 +5755,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120067975</v>
+        <v>120067639</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5788,25 +5779,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5816,13 +5807,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502758</v>
+        <v>502795</v>
       </c>
       <c r="R47" t="n">
-        <v>6919553</v>
+        <v>6919546</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5851,7 +5842,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5861,7 +5852,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5876,22 +5867,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120067947</v>
+        <v>120067689</v>
       </c>
       <c r="B48" t="n">
-        <v>90930</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5900,25 +5891,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>298</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5928,13 +5919,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502748</v>
+        <v>502765</v>
       </c>
       <c r="R48" t="n">
-        <v>6919557</v>
+        <v>6919539</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5963,7 +5954,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5973,12 +5964,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Tillsammans med timmergröppa</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5993,22 +5979,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120066174</v>
+        <v>120069641</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6017,38 +6003,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502971</v>
+        <v>502573</v>
       </c>
       <c r="R49" t="n">
-        <v>6919362</v>
+        <v>6919359</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6117,7 +6108,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120067689</v>
+        <v>120066174</v>
       </c>
       <c r="B50" t="n">
         <v>91840</v>
@@ -6157,10 +6148,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502765</v>
+        <v>502971</v>
       </c>
       <c r="R50" t="n">
-        <v>6919539</v>
+        <v>6919362</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6229,10 +6220,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120067493</v>
+        <v>120065022</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6241,38 +6232,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502805</v>
+        <v>503071</v>
       </c>
       <c r="R51" t="n">
-        <v>6919532</v>
+        <v>6919233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120065184</v>
+        <v>120067569</v>
       </c>
       <c r="B52" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6357,34 +6357,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503055</v>
+        <v>502813</v>
       </c>
       <c r="R52" t="n">
-        <v>6919216</v>
+        <v>6919527</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120069641</v>
+        <v>120067947</v>
       </c>
       <c r="B53" t="n">
-        <v>57463</v>
+        <v>90930</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6465,46 +6465,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502573</v>
+        <v>502748</v>
       </c>
       <c r="R53" t="n">
-        <v>6919359</v>
+        <v>6919557</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,7 +6528,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6543,7 +6538,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tillsammans med timmergröppa</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6558,12 +6558,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120119046</v>
+        <v>120142089</v>
       </c>
       <c r="B55" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6694,38 +6694,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>502418</v>
+        <v>502373</v>
       </c>
       <c r="R55" t="n">
-        <v>6919456</v>
+        <v>6919669</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6755,27 +6758,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6794,10 +6788,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120142102</v>
+        <v>120142120</v>
       </c>
       <c r="B56" t="n">
-        <v>78171</v>
+        <v>57463</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6810,26 +6804,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6837,10 +6836,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502265</v>
+        <v>502335</v>
       </c>
       <c r="R56" t="n">
-        <v>6919613</v>
+        <v>6919623</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6881,7 +6880,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6900,10 +6898,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120120227</v>
+        <v>120120181</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6912,25 +6910,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6940,10 +6938,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502410</v>
+        <v>502417</v>
       </c>
       <c r="R57" t="n">
-        <v>6919658</v>
+        <v>6919645</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7012,10 +7010,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120120181</v>
+        <v>120142102</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7024,38 +7022,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502417</v>
+        <v>502265</v>
       </c>
       <c r="R58" t="n">
-        <v>6919645</v>
+        <v>6919613</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7085,27 +7086,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7124,10 +7116,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120142073</v>
+        <v>120121333</v>
       </c>
       <c r="B59" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7136,41 +7128,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502373</v>
+        <v>502264</v>
       </c>
       <c r="R59" t="n">
-        <v>6919669</v>
+        <v>6919557</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7200,18 +7189,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7230,10 +7228,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120142089</v>
+        <v>120120227</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7242,41 +7240,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502373</v>
+        <v>502410</v>
       </c>
       <c r="R60" t="n">
-        <v>6919669</v>
+        <v>6919658</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7306,18 +7301,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7336,10 +7340,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120142120</v>
+        <v>120119728</v>
       </c>
       <c r="B61" t="n">
-        <v>57463</v>
+        <v>90807</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7348,46 +7352,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>65</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502335</v>
+        <v>502366</v>
       </c>
       <c r="R61" t="n">
-        <v>6919623</v>
+        <v>6919546</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7417,9 +7413,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7446,10 +7452,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120119728</v>
+        <v>120118385</v>
       </c>
       <c r="B62" t="n">
-        <v>90807</v>
+        <v>78263</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7458,25 +7464,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7486,10 +7492,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502366</v>
+        <v>502456</v>
       </c>
       <c r="R62" t="n">
-        <v>6919546</v>
+        <v>6919412</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7558,10 +7564,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120120273</v>
+        <v>120142073</v>
       </c>
       <c r="B63" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7574,34 +7580,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502391</v>
+        <v>502373</v>
       </c>
       <c r="R63" t="n">
-        <v>6919666</v>
+        <v>6919669</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7631,27 +7640,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7670,10 +7670,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120121333</v>
+        <v>120118347</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7682,25 +7682,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502264</v>
+        <v>502471</v>
       </c>
       <c r="R64" t="n">
-        <v>6919557</v>
+        <v>6919424</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7782,10 +7782,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120118347</v>
+        <v>120119046</v>
       </c>
       <c r="B65" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7798,21 +7798,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7822,10 +7822,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>502471</v>
+        <v>502418</v>
       </c>
       <c r="R65" t="n">
-        <v>6919424</v>
+        <v>6919456</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120118385</v>
+        <v>120120273</v>
       </c>
       <c r="B66" t="n">
         <v>78263</v>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502456</v>
+        <v>502391</v>
       </c>
       <c r="R66" t="n">
-        <v>6919412</v>
+        <v>6919666</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -4194,10 +4194,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120067311</v>
+        <v>120066170</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4210,37 +4210,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502822</v>
+        <v>502988</v>
       </c>
       <c r="R33" t="n">
-        <v>6919420</v>
+        <v>6919354</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,19 +4294,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120066170</v>
+        <v>120065184</v>
       </c>
       <c r="B34" t="n">
         <v>79144</v>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502988</v>
+        <v>503055</v>
       </c>
       <c r="R34" t="n">
-        <v>6919354</v>
+        <v>6919216</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120065184</v>
+        <v>120067311</v>
       </c>
       <c r="B35" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4434,37 +4434,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503055</v>
+        <v>502822</v>
       </c>
       <c r="R35" t="n">
-        <v>6919216</v>
+        <v>6919420</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,12 +4518,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -6898,10 +6898,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120120181</v>
+        <v>120142102</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6910,38 +6910,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502417</v>
+        <v>502265</v>
       </c>
       <c r="R57" t="n">
-        <v>6919645</v>
+        <v>6919613</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6971,27 +6974,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7010,10 +7004,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120142102</v>
+        <v>120120181</v>
       </c>
       <c r="B58" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7022,41 +7016,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502265</v>
+        <v>502417</v>
       </c>
       <c r="R58" t="n">
-        <v>6919613</v>
+        <v>6919645</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7086,18 +7077,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120121333</v>
+        <v>120120227</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7128,25 +7128,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502264</v>
+        <v>502410</v>
       </c>
       <c r="R59" t="n">
-        <v>6919557</v>
+        <v>6919658</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7191,7 +7191,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7228,10 +7228,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120120227</v>
+        <v>120121333</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7240,25 +7240,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502410</v>
+        <v>502264</v>
       </c>
       <c r="R60" t="n">
-        <v>6919658</v>
+        <v>6919557</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -4194,10 +4194,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120066170</v>
+        <v>120067311</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4210,37 +4210,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502988</v>
+        <v>502822</v>
       </c>
       <c r="R33" t="n">
-        <v>6919354</v>
+        <v>6919420</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,19 +4294,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120065184</v>
+        <v>120066170</v>
       </c>
       <c r="B34" t="n">
         <v>79144</v>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503055</v>
+        <v>502988</v>
       </c>
       <c r="R34" t="n">
-        <v>6919216</v>
+        <v>6919354</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120067311</v>
+        <v>120065184</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4434,37 +4434,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502822</v>
+        <v>503055</v>
       </c>
       <c r="R35" t="n">
-        <v>6919420</v>
+        <v>6919216</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,22 +4518,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120067975</v>
+        <v>120069367</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4542,25 +4542,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4570,13 +4570,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502758</v>
+        <v>502491</v>
       </c>
       <c r="R36" t="n">
-        <v>6919553</v>
+        <v>6919384</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,22 +4630,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120069367</v>
+        <v>120067975</v>
       </c>
       <c r="B37" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4654,25 +4654,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4682,13 +4682,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502491</v>
+        <v>502758</v>
       </c>
       <c r="R37" t="n">
-        <v>6919384</v>
+        <v>6919553</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4742,22 +4742,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120067652</v>
+        <v>120065228</v>
       </c>
       <c r="B38" t="n">
-        <v>79115</v>
+        <v>91884</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4770,37 +4770,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>5449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502795</v>
+        <v>503010</v>
       </c>
       <c r="R38" t="n">
-        <v>6919545</v>
+        <v>6919294</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4854,22 +4854,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120065228</v>
+        <v>120067652</v>
       </c>
       <c r="B39" t="n">
-        <v>91884</v>
+        <v>79115</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4882,37 +4882,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503010</v>
+        <v>502795</v>
       </c>
       <c r="R39" t="n">
-        <v>6919294</v>
+        <v>6919545</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4966,12 +4966,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6898,10 +6898,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120142102</v>
+        <v>120120181</v>
       </c>
       <c r="B57" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6910,41 +6910,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502265</v>
+        <v>502417</v>
       </c>
       <c r="R57" t="n">
-        <v>6919613</v>
+        <v>6919645</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6974,18 +6971,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7004,10 +7010,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120120181</v>
+        <v>120142102</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7016,38 +7022,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502417</v>
+        <v>502265</v>
       </c>
       <c r="R58" t="n">
-        <v>6919645</v>
+        <v>6919613</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7077,27 +7086,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120120227</v>
+        <v>120121333</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7128,25 +7128,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502410</v>
+        <v>502264</v>
       </c>
       <c r="R59" t="n">
-        <v>6919658</v>
+        <v>6919557</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7191,7 +7191,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7228,10 +7228,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120121333</v>
+        <v>120120227</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7240,25 +7240,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502264</v>
+        <v>502410</v>
       </c>
       <c r="R60" t="n">
-        <v>6919557</v>
+        <v>6919658</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7670,10 +7670,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120118347</v>
+        <v>120119046</v>
       </c>
       <c r="B64" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7686,21 +7686,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502471</v>
+        <v>502418</v>
       </c>
       <c r="R64" t="n">
-        <v>6919424</v>
+        <v>6919456</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7782,10 +7782,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120119046</v>
+        <v>120118347</v>
       </c>
       <c r="B65" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7798,21 +7798,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7822,10 +7822,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>502418</v>
+        <v>502471</v>
       </c>
       <c r="R65" t="n">
-        <v>6919456</v>
+        <v>6919424</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120069969</v>
+        <v>120069700</v>
       </c>
       <c r="B44" t="n">
-        <v>78171</v>
+        <v>91844</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,13 +5471,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502630</v>
+        <v>502566</v>
       </c>
       <c r="R44" t="n">
-        <v>6919303</v>
+        <v>6919324</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5531,22 +5531,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120069700</v>
+        <v>120069969</v>
       </c>
       <c r="B45" t="n">
-        <v>91844</v>
+        <v>78171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5555,25 +5555,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5583,13 +5583,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502566</v>
+        <v>502630</v>
       </c>
       <c r="R45" t="n">
-        <v>6919324</v>
+        <v>6919303</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5643,12 +5643,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6220,10 +6220,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120065022</v>
+        <v>120067569</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6232,50 +6232,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503071</v>
+        <v>502813</v>
       </c>
       <c r="R51" t="n">
-        <v>6919233</v>
+        <v>6919527</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6304,7 +6295,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6314,7 +6305,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,22 +6320,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120067569</v>
+        <v>120065022</v>
       </c>
       <c r="B52" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6353,41 +6344,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502813</v>
+        <v>503071</v>
       </c>
       <c r="R52" t="n">
-        <v>6919527</v>
+        <v>6919233</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6441,12 +6441,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -4530,10 +4530,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120069367</v>
+        <v>120067975</v>
       </c>
       <c r="B36" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4542,25 +4542,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4570,13 +4570,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502491</v>
+        <v>502758</v>
       </c>
       <c r="R36" t="n">
-        <v>6919384</v>
+        <v>6919553</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,22 +4630,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120067975</v>
+        <v>120069367</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4654,25 +4654,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4682,13 +4682,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502758</v>
+        <v>502491</v>
       </c>
       <c r="R37" t="n">
-        <v>6919553</v>
+        <v>6919384</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4742,22 +4742,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120065228</v>
+        <v>120067652</v>
       </c>
       <c r="B38" t="n">
-        <v>91884</v>
+        <v>79115</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4770,37 +4770,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503010</v>
+        <v>502795</v>
       </c>
       <c r="R38" t="n">
-        <v>6919294</v>
+        <v>6919545</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4854,22 +4854,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120067652</v>
+        <v>120065228</v>
       </c>
       <c r="B39" t="n">
-        <v>79115</v>
+        <v>91884</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4882,37 +4882,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>5449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502795</v>
+        <v>503010</v>
       </c>
       <c r="R39" t="n">
-        <v>6919545</v>
+        <v>6919294</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4966,12 +4966,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120069700</v>
+        <v>120069969</v>
       </c>
       <c r="B44" t="n">
-        <v>91844</v>
+        <v>78171</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,13 +5471,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502566</v>
+        <v>502630</v>
       </c>
       <c r="R44" t="n">
-        <v>6919324</v>
+        <v>6919303</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5531,22 +5531,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120069969</v>
+        <v>120069700</v>
       </c>
       <c r="B45" t="n">
-        <v>78171</v>
+        <v>91844</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5555,25 +5555,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5583,13 +5583,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502630</v>
+        <v>502566</v>
       </c>
       <c r="R45" t="n">
-        <v>6919303</v>
+        <v>6919324</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5643,12 +5643,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -6898,10 +6898,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120120181</v>
+        <v>120142102</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6910,38 +6910,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502417</v>
+        <v>502265</v>
       </c>
       <c r="R57" t="n">
-        <v>6919645</v>
+        <v>6919613</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6971,27 +6974,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7010,10 +7004,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120142102</v>
+        <v>120120181</v>
       </c>
       <c r="B58" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7022,41 +7016,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502265</v>
+        <v>502417</v>
       </c>
       <c r="R58" t="n">
-        <v>6919613</v>
+        <v>6919645</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7086,18 +7077,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120121333</v>
+        <v>120120227</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7128,25 +7128,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502264</v>
+        <v>502410</v>
       </c>
       <c r="R59" t="n">
-        <v>6919557</v>
+        <v>6919658</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7191,7 +7191,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7228,10 +7228,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120120227</v>
+        <v>120121333</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7240,25 +7240,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502410</v>
+        <v>502264</v>
       </c>
       <c r="R60" t="n">
-        <v>6919658</v>
+        <v>6919557</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7670,10 +7670,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120119046</v>
+        <v>120118347</v>
       </c>
       <c r="B64" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7686,21 +7686,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502418</v>
+        <v>502471</v>
       </c>
       <c r="R64" t="n">
-        <v>6919456</v>
+        <v>6919424</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7782,10 +7782,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120118347</v>
+        <v>120119046</v>
       </c>
       <c r="B65" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7798,21 +7798,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7822,10 +7822,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>502471</v>
+        <v>502418</v>
       </c>
       <c r="R65" t="n">
-        <v>6919424</v>
+        <v>6919456</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -4073,10 +4073,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120069993</v>
+        <v>120066170</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>79144</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4085,47 +4085,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502615</v>
+        <v>502988</v>
       </c>
       <c r="R32" t="n">
-        <v>6919305</v>
+        <v>6919354</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4157,7 +4148,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4167,7 +4158,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4194,10 +4185,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120067311</v>
+        <v>120065184</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4210,37 +4201,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502822</v>
+        <v>503055</v>
       </c>
       <c r="R33" t="n">
-        <v>6919420</v>
+        <v>6919216</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4269,7 +4260,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4279,7 +4270,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,22 +4285,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120066170</v>
+        <v>120067311</v>
       </c>
       <c r="B34" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4322,37 +4313,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502988</v>
+        <v>502822</v>
       </c>
       <c r="R34" t="n">
-        <v>6919354</v>
+        <v>6919420</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4381,7 +4372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4391,7 +4382,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,22 +4397,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120065184</v>
+        <v>120069993</v>
       </c>
       <c r="B35" t="n">
-        <v>79144</v>
+        <v>97907</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4430,38 +4421,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503055</v>
+        <v>502615</v>
       </c>
       <c r="R35" t="n">
-        <v>6919216</v>
+        <v>6919305</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -7116,10 +7116,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120120227</v>
+        <v>120121333</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7128,25 +7128,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502410</v>
+        <v>502264</v>
       </c>
       <c r="R59" t="n">
-        <v>6919658</v>
+        <v>6919557</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7191,7 +7191,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7228,10 +7228,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120121333</v>
+        <v>120120227</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7240,25 +7240,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502264</v>
+        <v>502410</v>
       </c>
       <c r="R60" t="n">
-        <v>6919557</v>
+        <v>6919658</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120027766</v>
+        <v>120028121</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502871</v>
+        <v>502828</v>
       </c>
       <c r="R2" t="n">
-        <v>6919391</v>
+        <v>6919422</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>120027825</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120024081</v>
+        <v>120024406</v>
       </c>
       <c r="B4" t="n">
-        <v>78263</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502703</v>
+        <v>502726</v>
       </c>
       <c r="R4" t="n">
-        <v>6919322</v>
+        <v>6919308</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120027814</v>
+        <v>120024626</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,14 +1057,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502886</v>
+        <v>502784</v>
       </c>
       <c r="R5" t="n">
-        <v>6919441</v>
+        <v>6919311</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120025266</v>
+        <v>120029012</v>
       </c>
       <c r="B6" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502825</v>
+        <v>502589</v>
       </c>
       <c r="R6" t="n">
-        <v>6919306</v>
+        <v>6919321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120028274</v>
+        <v>120028686</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,31 +1261,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1294,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502778</v>
+        <v>502735</v>
       </c>
       <c r="R7" t="n">
-        <v>6919405</v>
+        <v>6919361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,6 +1336,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Inte jättegamla.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120024983</v>
+        <v>120031101</v>
       </c>
       <c r="B8" t="n">
-        <v>78263</v>
+        <v>90512</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,38 +1379,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>2013</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502808</v>
+        <v>502863</v>
       </c>
       <c r="R8" t="n">
-        <v>6919302</v>
+        <v>6919305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,27 +1443,18 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1478,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120028546</v>
+        <v>120024983</v>
       </c>
       <c r="B9" t="n">
-        <v>90807</v>
+        <v>78279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1485,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502717</v>
+        <v>502808</v>
       </c>
       <c r="R9" t="n">
-        <v>6919429</v>
+        <v>6919302</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120024406</v>
+        <v>120027968</v>
       </c>
       <c r="B10" t="n">
-        <v>79144</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,25 +1597,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502726</v>
+        <v>502856</v>
       </c>
       <c r="R10" t="n">
-        <v>6919308</v>
+        <v>6919392</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1702,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120027055</v>
+        <v>120027766</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,43 +1709,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502889</v>
+        <v>502871</v>
       </c>
       <c r="R11" t="n">
-        <v>6919376</v>
+        <v>6919391</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1819,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120028121</v>
+        <v>120024081</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>78279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,25 +1821,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1859,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502828</v>
+        <v>502703</v>
       </c>
       <c r="R12" t="n">
-        <v>6919422</v>
+        <v>6919322</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1894,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120028686</v>
+        <v>120027814</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,43 +1933,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502735</v>
+        <v>502886</v>
       </c>
       <c r="R13" t="n">
-        <v>6919361</v>
+        <v>6919441</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Inte jättegamla.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120029012</v>
+        <v>120026409</v>
       </c>
       <c r="B14" t="n">
-        <v>78263</v>
+        <v>89650</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,34 +2049,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502589</v>
+        <v>502910</v>
       </c>
       <c r="R14" t="n">
-        <v>6919321</v>
+        <v>6919294</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,7 +2148,7 @@
         <v>120028984</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2282,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120027968</v>
+        <v>120025266</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>78279</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,25 +2274,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2322,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502856</v>
+        <v>502825</v>
       </c>
       <c r="R16" t="n">
-        <v>6919392</v>
+        <v>6919306</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2394,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120026409</v>
+        <v>120028274</v>
       </c>
       <c r="B17" t="n">
-        <v>89633</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2410,34 +2390,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502910</v>
+        <v>502778</v>
       </c>
       <c r="R17" t="n">
-        <v>6919294</v>
+        <v>6919405</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2468,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120024626</v>
+        <v>120028546</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>90825</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,25 +2507,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2535,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502784</v>
+        <v>502717</v>
       </c>
       <c r="R18" t="n">
-        <v>6919311</v>
+        <v>6919429</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,7 +2570,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2580,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120031101</v>
+        <v>120027055</v>
       </c>
       <c r="B19" t="n">
-        <v>90494</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,41 +2619,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2013</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502863</v>
+        <v>502889</v>
       </c>
       <c r="R19" t="n">
-        <v>6919305</v>
+        <v>6919376</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2694,18 +2685,27 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120067723</v>
+        <v>120067493</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502732</v>
+        <v>502805</v>
       </c>
       <c r="R20" t="n">
-        <v>6919555</v>
+        <v>6919532</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120069378</v>
+        <v>120067569</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>78279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,25 +2848,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502481</v>
+        <v>502813</v>
       </c>
       <c r="R21" t="n">
-        <v>6919451</v>
+        <v>6919527</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,10 +2948,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120068130</v>
+        <v>120067975</v>
       </c>
       <c r="B22" t="n">
-        <v>79144</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,25 +2960,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502709</v>
+        <v>502758</v>
       </c>
       <c r="R22" t="n">
-        <v>6919568</v>
+        <v>6919553</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3060,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120068117</v>
+        <v>120068252</v>
       </c>
       <c r="B23" t="n">
-        <v>79115</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,25 +3072,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3100,13 +3100,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502709</v>
+        <v>502690</v>
       </c>
       <c r="R23" t="n">
-        <v>6919568</v>
+        <v>6919538</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3160,22 +3160,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120064989</v>
+        <v>120067947</v>
       </c>
       <c r="B24" t="n">
-        <v>78263</v>
+        <v>90948</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3184,38 +3184,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503055</v>
+        <v>502748</v>
       </c>
       <c r="R24" t="n">
-        <v>6919216</v>
+        <v>6919557</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,7 +3257,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tillsammans med timmergröppa</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,10 +3289,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120065324</v>
+        <v>120065342</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3296,43 +3301,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503005</v>
+        <v>503007</v>
       </c>
       <c r="R25" t="n">
-        <v>6919310</v>
+        <v>6919317</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120065342</v>
+        <v>120066170</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3413,41 +3413,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503007</v>
+        <v>502988</v>
       </c>
       <c r="R26" t="n">
-        <v>6919317</v>
+        <v>6919354</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3501,22 +3501,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120069084</v>
+        <v>120065184</v>
       </c>
       <c r="B27" t="n">
-        <v>90527</v>
+        <v>79160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3525,38 +3525,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502514</v>
+        <v>503055</v>
       </c>
       <c r="R27" t="n">
-        <v>6919477</v>
+        <v>6919216</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3625,10 +3625,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120068779</v>
+        <v>120067639</v>
       </c>
       <c r="B28" t="n">
-        <v>91884</v>
+        <v>78279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3641,21 +3641,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3665,13 +3665,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502513</v>
+        <v>502795</v>
       </c>
       <c r="R28" t="n">
-        <v>6919490</v>
+        <v>6919546</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3725,22 +3725,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120069026</v>
+        <v>120065915</v>
       </c>
       <c r="B29" t="n">
-        <v>90576</v>
+        <v>57473</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3753,37 +3753,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502514</v>
+        <v>502996</v>
       </c>
       <c r="R29" t="n">
-        <v>6919477</v>
+        <v>6919352</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3812,7 +3817,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3822,7 +3827,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3837,22 +3842,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120066423</v>
+        <v>120068779</v>
       </c>
       <c r="B30" t="n">
-        <v>78263</v>
+        <v>91902</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3865,34 +3870,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502973</v>
+        <v>502513</v>
       </c>
       <c r="R30" t="n">
-        <v>6919384</v>
+        <v>6919490</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3924,7 +3929,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3934,7 +3939,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3961,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120068337</v>
+        <v>120069026</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>90594</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3973,25 +3978,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4001,13 +4006,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502628</v>
+        <v>502514</v>
       </c>
       <c r="R31" t="n">
-        <v>6919549</v>
+        <v>6919477</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4036,7 +4041,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4046,7 +4051,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4061,22 +4066,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120066170</v>
+        <v>120069993</v>
       </c>
       <c r="B32" t="n">
-        <v>79144</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4085,38 +4090,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502988</v>
+        <v>502615</v>
       </c>
       <c r="R32" t="n">
-        <v>6919354</v>
+        <v>6919305</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4148,7 +4162,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4158,7 +4172,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4185,10 +4199,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120065184</v>
+        <v>120067558</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>79131</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4201,34 +4215,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503055</v>
+        <v>502813</v>
       </c>
       <c r="R33" t="n">
-        <v>6919216</v>
+        <v>6919527</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4260,7 +4274,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4270,7 +4284,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4297,10 +4311,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120067311</v>
+        <v>120066174</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4309,25 +4323,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4337,10 +4351,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502822</v>
+        <v>502971</v>
       </c>
       <c r="R34" t="n">
-        <v>6919420</v>
+        <v>6919362</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4409,10 +4423,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120069993</v>
+        <v>120068117</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>79131</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4421,47 +4435,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502615</v>
+        <v>502709</v>
       </c>
       <c r="R35" t="n">
-        <v>6919305</v>
+        <v>6919568</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4493,7 +4498,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4503,7 +4508,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,10 +4535,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120067975</v>
+        <v>120068130</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>79160</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4542,25 +4547,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4570,10 +4575,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502758</v>
+        <v>502709</v>
       </c>
       <c r="R36" t="n">
-        <v>6919553</v>
+        <v>6919568</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4605,7 +4610,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4615,7 +4620,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4642,10 +4647,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120069367</v>
+        <v>120064989</v>
       </c>
       <c r="B37" t="n">
-        <v>78262</v>
+        <v>78279</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4658,37 +4663,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502491</v>
+        <v>503055</v>
       </c>
       <c r="R37" t="n">
-        <v>6919384</v>
+        <v>6919216</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4717,7 +4722,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4727,7 +4732,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4742,22 +4747,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120067652</v>
+        <v>120069641</v>
       </c>
       <c r="B38" t="n">
-        <v>79115</v>
+        <v>57473</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4770,34 +4775,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502795</v>
+        <v>502573</v>
       </c>
       <c r="R38" t="n">
-        <v>6919545</v>
+        <v>6919359</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4866,10 +4876,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120065228</v>
+        <v>120069360</v>
       </c>
       <c r="B39" t="n">
-        <v>91884</v>
+        <v>78279</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4882,37 +4892,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503010</v>
+        <v>502491</v>
       </c>
       <c r="R39" t="n">
-        <v>6919294</v>
+        <v>6919384</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4941,7 +4951,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4951,7 +4961,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4966,22 +4976,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120065915</v>
+        <v>120069700</v>
       </c>
       <c r="B40" t="n">
-        <v>57463</v>
+        <v>91862</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4990,46 +5000,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502996</v>
+        <v>502566</v>
       </c>
       <c r="R40" t="n">
-        <v>6919352</v>
+        <v>6919324</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5058,7 +5063,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5068,7 +5073,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5083,22 +5088,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120067558</v>
+        <v>120068337</v>
       </c>
       <c r="B41" t="n">
-        <v>79115</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5107,25 +5112,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5135,13 +5140,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502813</v>
+        <v>502628</v>
       </c>
       <c r="R41" t="n">
-        <v>6919527</v>
+        <v>6919549</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5170,7 +5175,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5180,7 +5185,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5195,22 +5200,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120067493</v>
+        <v>120069969</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5223,21 +5228,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5247,10 +5252,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502805</v>
+        <v>502630</v>
       </c>
       <c r="R42" t="n">
-        <v>6919532</v>
+        <v>6919303</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5319,10 +5324,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120065504</v>
+        <v>120067723</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5331,25 +5336,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5359,10 +5364,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502986</v>
+        <v>502732</v>
       </c>
       <c r="R43" t="n">
-        <v>6919325</v>
+        <v>6919555</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5431,10 +5436,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120069969</v>
+        <v>120069084</v>
       </c>
       <c r="B44" t="n">
-        <v>78171</v>
+        <v>90545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5448,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,13 +5476,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502630</v>
+        <v>502514</v>
       </c>
       <c r="R44" t="n">
-        <v>6919303</v>
+        <v>6919477</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5506,7 +5511,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5516,7 +5521,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5531,22 +5536,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120069700</v>
+        <v>120065022</v>
       </c>
       <c r="B45" t="n">
-        <v>91844</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5559,37 +5564,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4365</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502566</v>
+        <v>503071</v>
       </c>
       <c r="R45" t="n">
-        <v>6919324</v>
+        <v>6919233</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5618,7 +5632,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5628,7 +5642,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5643,22 +5657,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120068252</v>
+        <v>120069367</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>78278</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5667,25 +5681,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5695,10 +5709,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502690</v>
+        <v>502491</v>
       </c>
       <c r="R46" t="n">
-        <v>6919538</v>
+        <v>6919384</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5767,10 +5781,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120067639</v>
+        <v>120067311</v>
       </c>
       <c r="B47" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5783,21 +5797,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5807,10 +5821,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502795</v>
+        <v>502822</v>
       </c>
       <c r="R47" t="n">
-        <v>6919546</v>
+        <v>6919420</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5882,7 +5896,7 @@
         <v>120067689</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5991,10 +6005,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120069641</v>
+        <v>120069378</v>
       </c>
       <c r="B49" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6003,46 +6017,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502573</v>
+        <v>502481</v>
       </c>
       <c r="R49" t="n">
-        <v>6919359</v>
+        <v>6919451</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6071,7 +6080,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6090,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,22 +6105,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120066174</v>
+        <v>120066423</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>78279</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6120,41 +6129,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502971</v>
+        <v>502973</v>
       </c>
       <c r="R50" t="n">
-        <v>6919362</v>
+        <v>6919384</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6183,7 +6192,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6193,7 +6202,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6208,22 +6217,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120067569</v>
+        <v>120067652</v>
       </c>
       <c r="B51" t="n">
-        <v>78263</v>
+        <v>79131</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6236,21 +6245,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6260,13 +6269,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502813</v>
+        <v>502795</v>
       </c>
       <c r="R51" t="n">
-        <v>6919527</v>
+        <v>6919545</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6295,7 +6304,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6305,7 +6314,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6320,22 +6329,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120065022</v>
+        <v>120065504</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>91852</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6344,47 +6353,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503071</v>
+        <v>502986</v>
       </c>
       <c r="R52" t="n">
-        <v>6919233</v>
+        <v>6919325</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6453,10 +6453,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120067947</v>
+        <v>120065228</v>
       </c>
       <c r="B53" t="n">
-        <v>90930</v>
+        <v>91902</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6465,38 +6465,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>298</v>
+        <v>5449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502748</v>
+        <v>503010</v>
       </c>
       <c r="R53" t="n">
-        <v>6919557</v>
+        <v>6919294</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6538,12 +6538,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tillsammans med timmergröppa</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6570,10 +6565,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120069360</v>
+        <v>120065324</v>
       </c>
       <c r="B54" t="n">
-        <v>78263</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6586,34 +6581,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>502491</v>
+        <v>503005</v>
       </c>
       <c r="R54" t="n">
-        <v>6919384</v>
+        <v>6919310</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120142089</v>
+        <v>120120181</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6716,19 +6716,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>502373</v>
+        <v>502417</v>
       </c>
       <c r="R55" t="n">
-        <v>6919669</v>
+        <v>6919645</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6758,18 +6755,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6788,10 +6794,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120142120</v>
+        <v>120120273</v>
       </c>
       <c r="B56" t="n">
-        <v>57463</v>
+        <v>78279</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6804,42 +6810,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502335</v>
+        <v>502391</v>
       </c>
       <c r="R56" t="n">
-        <v>6919623</v>
+        <v>6919666</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6869,9 +6867,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6898,10 +6906,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120142102</v>
+        <v>120118347</v>
       </c>
       <c r="B57" t="n">
-        <v>78171</v>
+        <v>78187</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6932,19 +6940,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502265</v>
+        <v>502471</v>
       </c>
       <c r="R57" t="n">
-        <v>6919613</v>
+        <v>6919424</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6974,18 +6979,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7004,10 +7018,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120120181</v>
+        <v>120119728</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>90825</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7016,25 +7030,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7044,10 +7058,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502417</v>
+        <v>502366</v>
       </c>
       <c r="R58" t="n">
-        <v>6919645</v>
+        <v>6919546</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7119,7 +7133,7 @@
         <v>120121333</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7228,10 +7242,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120120227</v>
+        <v>120119046</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7244,21 +7258,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7268,10 +7282,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502410</v>
+        <v>502418</v>
       </c>
       <c r="R60" t="n">
-        <v>6919658</v>
+        <v>6919456</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7340,10 +7354,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120119728</v>
+        <v>120142102</v>
       </c>
       <c r="B61" t="n">
-        <v>90807</v>
+        <v>78187</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7352,38 +7366,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502366</v>
+        <v>502265</v>
       </c>
       <c r="R61" t="n">
-        <v>6919546</v>
+        <v>6919613</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7413,27 +7430,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7452,10 +7460,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120118385</v>
+        <v>120142073</v>
       </c>
       <c r="B62" t="n">
-        <v>78263</v>
+        <v>78187</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7468,34 +7476,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502456</v>
+        <v>502373</v>
       </c>
       <c r="R62" t="n">
-        <v>6919412</v>
+        <v>6919669</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7525,27 +7536,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7564,10 +7566,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120142073</v>
+        <v>120120227</v>
       </c>
       <c r="B63" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7580,37 +7582,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502373</v>
+        <v>502410</v>
       </c>
       <c r="R63" t="n">
-        <v>6919669</v>
+        <v>6919658</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7640,18 +7639,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7670,10 +7678,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120118347</v>
+        <v>120118385</v>
       </c>
       <c r="B64" t="n">
-        <v>78171</v>
+        <v>78279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7686,21 +7694,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7710,10 +7718,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502471</v>
+        <v>502456</v>
       </c>
       <c r="R64" t="n">
-        <v>6919424</v>
+        <v>6919412</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7782,10 +7790,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120119046</v>
+        <v>120142089</v>
       </c>
       <c r="B65" t="n">
-        <v>78263</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7794,38 +7802,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>502418</v>
+        <v>502373</v>
       </c>
       <c r="R65" t="n">
-        <v>6919456</v>
+        <v>6919669</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7855,27 +7866,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7894,10 +7896,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120120273</v>
+        <v>120142120</v>
       </c>
       <c r="B66" t="n">
-        <v>78263</v>
+        <v>57473</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7910,34 +7912,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502391</v>
+        <v>502335</v>
       </c>
       <c r="R66" t="n">
-        <v>6919666</v>
+        <v>6919623</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7967,19 +7977,9 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:29</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -2262,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120025266</v>
+        <v>120028274</v>
       </c>
       <c r="B16" t="n">
-        <v>78279</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,34 +2278,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502825</v>
+        <v>502778</v>
       </c>
       <c r="R16" t="n">
-        <v>6919306</v>
+        <v>6919405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2347,7 +2356,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,10 +2383,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120028274</v>
+        <v>120025266</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>78279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,43 +2399,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502778</v>
+        <v>502825</v>
       </c>
       <c r="R17" t="n">
-        <v>6919405</v>
+        <v>6919306</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3625,10 +3625,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120067639</v>
+        <v>120065915</v>
       </c>
       <c r="B28" t="n">
-        <v>78279</v>
+        <v>57473</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3641,34 +3641,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502795</v>
+        <v>502996</v>
       </c>
       <c r="R28" t="n">
-        <v>6919546</v>
+        <v>6919352</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3737,10 +3742,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120065915</v>
+        <v>120067639</v>
       </c>
       <c r="B29" t="n">
-        <v>57473</v>
+        <v>78279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3753,39 +3758,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502996</v>
+        <v>502795</v>
       </c>
       <c r="R29" t="n">
-        <v>6919352</v>
+        <v>6919546</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120069026</v>
+        <v>120067558</v>
       </c>
       <c r="B31" t="n">
-        <v>90594</v>
+        <v>79131</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3982,21 +3982,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502514</v>
+        <v>502813</v>
       </c>
       <c r="R31" t="n">
-        <v>6919477</v>
+        <v>6919527</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4199,10 +4199,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120067558</v>
+        <v>120069026</v>
       </c>
       <c r="B33" t="n">
-        <v>79131</v>
+        <v>90594</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4215,21 +4215,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502813</v>
+        <v>502514</v>
       </c>
       <c r="R33" t="n">
-        <v>6919527</v>
+        <v>6919477</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4759,10 +4759,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120069641</v>
+        <v>120069969</v>
       </c>
       <c r="B38" t="n">
-        <v>57473</v>
+        <v>78187</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4775,39 +4775,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502573</v>
+        <v>502630</v>
       </c>
       <c r="R38" t="n">
-        <v>6919359</v>
+        <v>6919303</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4876,10 +4871,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120069360</v>
+        <v>120069641</v>
       </c>
       <c r="B39" t="n">
-        <v>78279</v>
+        <v>57473</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4892,34 +4887,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502491</v>
+        <v>502573</v>
       </c>
       <c r="R39" t="n">
-        <v>6919384</v>
+        <v>6919359</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5212,10 +5212,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120069969</v>
+        <v>120069360</v>
       </c>
       <c r="B42" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5228,21 +5228,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502630</v>
+        <v>502491</v>
       </c>
       <c r="R42" t="n">
-        <v>6919303</v>
+        <v>6919384</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5436,10 +5436,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120069084</v>
+        <v>120065022</v>
       </c>
       <c r="B44" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5448,41 +5448,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502514</v>
+        <v>503071</v>
       </c>
       <c r="R44" t="n">
-        <v>6919477</v>
+        <v>6919233</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5511,7 +5520,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5521,7 +5530,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5536,22 +5545,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120065022</v>
+        <v>120069084</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5560,50 +5569,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503071</v>
+        <v>502514</v>
       </c>
       <c r="R45" t="n">
-        <v>6919233</v>
+        <v>6919477</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,12 +5657,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120067311</v>
+        <v>120067689</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5793,25 +5793,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502822</v>
+        <v>502765</v>
       </c>
       <c r="R47" t="n">
-        <v>6919420</v>
+        <v>6919539</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5893,7 +5893,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120067689</v>
+        <v>120069378</v>
       </c>
       <c r="B48" t="n">
         <v>91858</v>
@@ -5933,13 +5933,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502765</v>
+        <v>502481</v>
       </c>
       <c r="R48" t="n">
-        <v>6919539</v>
+        <v>6919451</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5993,22 +5993,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120069378</v>
+        <v>120067311</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6017,25 +6017,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6045,13 +6045,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502481</v>
+        <v>502822</v>
       </c>
       <c r="R49" t="n">
-        <v>6919451</v>
+        <v>6919420</v>
       </c>
       <c r="S49" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6105,12 +6105,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120028121</v>
+        <v>120027814</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502828</v>
+        <v>502886</v>
       </c>
       <c r="R2" t="n">
-        <v>6919422</v>
+        <v>6919441</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120027825</v>
+        <v>120028984</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -823,19 +823,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502881</v>
+        <v>502586</v>
       </c>
       <c r="R3" t="n">
-        <v>6919412</v>
+        <v>6919340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Både gamla och färska spår på samma tall.</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120024406</v>
+        <v>120028546</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>90825</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502726</v>
+        <v>502717</v>
       </c>
       <c r="R4" t="n">
-        <v>6919308</v>
+        <v>6919429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120024626</v>
+        <v>120024983</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502784</v>
+        <v>502808</v>
       </c>
       <c r="R5" t="n">
-        <v>6919311</v>
+        <v>6919302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120029012</v>
+        <v>120024626</v>
       </c>
       <c r="B6" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502589</v>
+        <v>502784</v>
       </c>
       <c r="R6" t="n">
-        <v>6919321</v>
+        <v>6919311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120031101</v>
+        <v>120027055</v>
       </c>
       <c r="B8" t="n">
-        <v>90512</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,41 +1374,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2013</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502863</v>
+        <v>502889</v>
       </c>
       <c r="R8" t="n">
-        <v>6919305</v>
+        <v>6919376</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,18 +1440,27 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1473,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120024983</v>
+        <v>120027825</v>
       </c>
       <c r="B9" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,34 +1495,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502808</v>
+        <v>502881</v>
       </c>
       <c r="R9" t="n">
-        <v>6919302</v>
+        <v>6919412</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,6 +1570,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Både gamla och färska spår på samma tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120027968</v>
+        <v>120024081</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,25 +1613,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1625,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502856</v>
+        <v>502703</v>
       </c>
       <c r="R10" t="n">
-        <v>6919392</v>
+        <v>6919322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1697,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120027766</v>
+        <v>120026409</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,38 +1725,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502871</v>
+        <v>502910</v>
       </c>
       <c r="R11" t="n">
-        <v>6919391</v>
+        <v>6919294</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120024081</v>
+        <v>120028274</v>
       </c>
       <c r="B12" t="n">
-        <v>78279</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,34 +1841,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502703</v>
+        <v>502778</v>
       </c>
       <c r="R12" t="n">
-        <v>6919322</v>
+        <v>6919405</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120027814</v>
+        <v>120028121</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,34 +1962,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502886</v>
+        <v>502828</v>
       </c>
       <c r="R13" t="n">
-        <v>6919441</v>
+        <v>6919422</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120026409</v>
+        <v>120031101</v>
       </c>
       <c r="B14" t="n">
-        <v>89650</v>
+        <v>90512</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,38 +2070,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>2013</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502910</v>
+        <v>502863</v>
       </c>
       <c r="R14" t="n">
-        <v>6919294</v>
+        <v>6919305</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,27 +2134,18 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2145,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120028984</v>
+        <v>120025266</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,39 +2180,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502586</v>
+        <v>502825</v>
       </c>
       <c r="R15" t="n">
-        <v>6919340</v>
+        <v>6919306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120028274</v>
+        <v>120024406</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,43 +2292,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502778</v>
+        <v>502726</v>
       </c>
       <c r="R16" t="n">
-        <v>6919405</v>
+        <v>6919308</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,7 +2388,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120025266</v>
+        <v>120029012</v>
       </c>
       <c r="B17" t="n">
         <v>78279</v>
@@ -2423,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502825</v>
+        <v>502589</v>
       </c>
       <c r="R17" t="n">
-        <v>6919306</v>
+        <v>6919321</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2468,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120028546</v>
+        <v>120027968</v>
       </c>
       <c r="B18" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,25 +2512,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2535,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502717</v>
+        <v>502856</v>
       </c>
       <c r="R18" t="n">
-        <v>6919429</v>
+        <v>6919392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2580,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120027055</v>
+        <v>120027766</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,43 +2624,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502889</v>
+        <v>502871</v>
       </c>
       <c r="R19" t="n">
-        <v>6919376</v>
+        <v>6919391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120067493</v>
+        <v>120067689</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502805</v>
+        <v>502765</v>
       </c>
       <c r="R20" t="n">
-        <v>6919532</v>
+        <v>6919539</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120067569</v>
+        <v>120069378</v>
       </c>
       <c r="B21" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,25 +2848,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502813</v>
+        <v>502481</v>
       </c>
       <c r="R21" t="n">
-        <v>6919527</v>
+        <v>6919451</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,10 +2948,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120067975</v>
+        <v>120065915</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,41 +2960,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502758</v>
+        <v>502996</v>
       </c>
       <c r="R22" t="n">
-        <v>6919553</v>
+        <v>6919352</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3023,7 +3028,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3038,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,19 +3053,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120068252</v>
+        <v>120067723</v>
       </c>
       <c r="B23" t="n">
         <v>91858</v>
@@ -3100,10 +3105,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502690</v>
+        <v>502732</v>
       </c>
       <c r="R23" t="n">
-        <v>6919538</v>
+        <v>6919555</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3172,10 +3177,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120067947</v>
+        <v>120066170</v>
       </c>
       <c r="B24" t="n">
-        <v>90948</v>
+        <v>79160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3184,38 +3189,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>298</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502748</v>
+        <v>502988</v>
       </c>
       <c r="R24" t="n">
-        <v>6919557</v>
+        <v>6919354</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3247,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,12 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Tillsammans med timmergröppa</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,7 +3289,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120065342</v>
+        <v>120067975</v>
       </c>
       <c r="B25" t="n">
         <v>91858</v>
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503007</v>
+        <v>502758</v>
       </c>
       <c r="R25" t="n">
-        <v>6919317</v>
+        <v>6919553</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3389,22 +3389,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120066170</v>
+        <v>120068337</v>
       </c>
       <c r="B26" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3413,41 +3413,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502988</v>
+        <v>502628</v>
       </c>
       <c r="R26" t="n">
-        <v>6919354</v>
+        <v>6919549</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3501,22 +3501,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120065184</v>
+        <v>120069993</v>
       </c>
       <c r="B27" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3525,38 +3525,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503055</v>
+        <v>502615</v>
       </c>
       <c r="R27" t="n">
-        <v>6919216</v>
+        <v>6919305</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3588,7 +3597,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3598,7 +3607,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3625,10 +3634,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120065915</v>
+        <v>120067569</v>
       </c>
       <c r="B28" t="n">
-        <v>57473</v>
+        <v>78279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3641,42 +3650,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502996</v>
+        <v>502813</v>
       </c>
       <c r="R28" t="n">
-        <v>6919352</v>
+        <v>6919527</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3705,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3715,7 +3719,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3730,22 +3734,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120067639</v>
+        <v>120065324</v>
       </c>
       <c r="B29" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3758,34 +3762,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502795</v>
+        <v>503005</v>
       </c>
       <c r="R29" t="n">
-        <v>6919546</v>
+        <v>6919310</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120068779</v>
+        <v>120069084</v>
       </c>
       <c r="B30" t="n">
-        <v>91902</v>
+        <v>90545</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3866,25 +3875,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3894,10 +3903,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502513</v>
+        <v>502514</v>
       </c>
       <c r="R30" t="n">
-        <v>6919490</v>
+        <v>6919477</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3929,7 +3938,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3939,7 +3948,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3966,10 +3975,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120067558</v>
+        <v>120064989</v>
       </c>
       <c r="B31" t="n">
-        <v>79131</v>
+        <v>78279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3982,34 +3991,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502813</v>
+        <v>503055</v>
       </c>
       <c r="R31" t="n">
-        <v>6919527</v>
+        <v>6919216</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4041,7 +4050,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4051,7 +4060,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4078,7 +4087,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120069993</v>
+        <v>120065022</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -4113,7 +4122,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4127,13 +4136,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502615</v>
+        <v>503071</v>
       </c>
       <c r="R32" t="n">
-        <v>6919305</v>
+        <v>6919233</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4162,7 +4171,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4172,7 +4181,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4187,22 +4196,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120069026</v>
+        <v>120065184</v>
       </c>
       <c r="B33" t="n">
-        <v>90594</v>
+        <v>79160</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4215,34 +4224,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502514</v>
+        <v>503055</v>
       </c>
       <c r="R33" t="n">
-        <v>6919477</v>
+        <v>6919216</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4274,7 +4283,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4284,7 +4293,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4311,10 +4320,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120066174</v>
+        <v>120067493</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4323,25 +4332,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4351,10 +4360,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502971</v>
+        <v>502805</v>
       </c>
       <c r="R34" t="n">
-        <v>6919362</v>
+        <v>6919532</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4423,10 +4432,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120068117</v>
+        <v>120069641</v>
       </c>
       <c r="B35" t="n">
-        <v>79131</v>
+        <v>57473</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4439,37 +4448,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502709</v>
+        <v>502573</v>
       </c>
       <c r="R35" t="n">
-        <v>6919568</v>
+        <v>6919359</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4498,7 +4512,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4508,7 +4522,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,22 +4537,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120068130</v>
+        <v>120069700</v>
       </c>
       <c r="B36" t="n">
-        <v>79160</v>
+        <v>91862</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4547,25 +4561,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4575,10 +4589,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502709</v>
+        <v>502566</v>
       </c>
       <c r="R36" t="n">
-        <v>6919568</v>
+        <v>6919324</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4610,7 +4624,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4620,7 +4634,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4647,10 +4661,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120064989</v>
+        <v>120069969</v>
       </c>
       <c r="B37" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4663,37 +4677,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503055</v>
+        <v>502630</v>
       </c>
       <c r="R37" t="n">
-        <v>6919216</v>
+        <v>6919303</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4722,7 +4736,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4732,7 +4746,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,22 +4761,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120069969</v>
+        <v>120067947</v>
       </c>
       <c r="B38" t="n">
-        <v>78187</v>
+        <v>90948</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4771,25 +4785,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4799,13 +4813,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502630</v>
+        <v>502748</v>
       </c>
       <c r="R38" t="n">
-        <v>6919303</v>
+        <v>6919557</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4834,7 +4848,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4844,7 +4858,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Tillsammans med timmergröppa</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,22 +4878,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120069641</v>
+        <v>120069367</v>
       </c>
       <c r="B39" t="n">
-        <v>57473</v>
+        <v>78278</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4887,39 +4906,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502573</v>
+        <v>502491</v>
       </c>
       <c r="R39" t="n">
-        <v>6919359</v>
+        <v>6919384</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4988,10 +5002,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120069700</v>
+        <v>120066174</v>
       </c>
       <c r="B40" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5000,25 +5014,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5028,13 +5042,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502566</v>
+        <v>502971</v>
       </c>
       <c r="R40" t="n">
-        <v>6919324</v>
+        <v>6919362</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5063,7 +5077,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5073,7 +5087,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5088,22 +5102,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120068337</v>
+        <v>120067558</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5112,25 +5126,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5140,13 +5154,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502628</v>
+        <v>502813</v>
       </c>
       <c r="R41" t="n">
-        <v>6919549</v>
+        <v>6919527</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5175,7 +5189,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5185,7 +5199,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5200,22 +5214,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120069360</v>
+        <v>120067652</v>
       </c>
       <c r="B42" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5228,21 +5242,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5252,10 +5266,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502491</v>
+        <v>502795</v>
       </c>
       <c r="R42" t="n">
-        <v>6919384</v>
+        <v>6919545</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5324,10 +5338,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120067723</v>
+        <v>120065228</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5336,41 +5350,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502732</v>
+        <v>503010</v>
       </c>
       <c r="R43" t="n">
-        <v>6919555</v>
+        <v>6919294</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5399,7 +5413,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5409,7 +5423,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5424,22 +5438,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120065022</v>
+        <v>120068779</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5448,50 +5462,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503071</v>
+        <v>502513</v>
       </c>
       <c r="R44" t="n">
-        <v>6919233</v>
+        <v>6919490</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5520,7 +5525,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5530,7 +5535,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5545,22 +5550,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120069084</v>
+        <v>120068117</v>
       </c>
       <c r="B45" t="n">
-        <v>90545</v>
+        <v>79131</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5569,25 +5574,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5597,10 +5602,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502514</v>
+        <v>502709</v>
       </c>
       <c r="R45" t="n">
-        <v>6919477</v>
+        <v>6919568</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5632,7 +5637,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5642,7 +5647,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5669,10 +5674,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120069367</v>
+        <v>120067639</v>
       </c>
       <c r="B46" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5685,21 +5690,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5709,10 +5714,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502491</v>
+        <v>502795</v>
       </c>
       <c r="R46" t="n">
-        <v>6919384</v>
+        <v>6919546</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5781,10 +5786,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120067689</v>
+        <v>120068130</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5793,25 +5798,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5821,13 +5826,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502765</v>
+        <v>502709</v>
       </c>
       <c r="R47" t="n">
-        <v>6919539</v>
+        <v>6919568</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5856,7 +5861,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5866,7 +5871,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5881,19 +5886,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120069378</v>
+        <v>120065342</v>
       </c>
       <c r="B48" t="n">
         <v>91858</v>
@@ -5933,13 +5938,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502481</v>
+        <v>503007</v>
       </c>
       <c r="R48" t="n">
-        <v>6919451</v>
+        <v>6919317</v>
       </c>
       <c r="S48" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5968,7 +5973,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5978,7 +5983,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5993,22 +5998,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120067311</v>
+        <v>120066423</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6021,37 +6026,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502822</v>
+        <v>502973</v>
       </c>
       <c r="R49" t="n">
-        <v>6919420</v>
+        <v>6919384</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6080,7 +6085,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6090,7 +6095,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6105,22 +6110,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120066423</v>
+        <v>120067311</v>
       </c>
       <c r="B50" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6133,37 +6138,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502973</v>
+        <v>502822</v>
       </c>
       <c r="R50" t="n">
-        <v>6919384</v>
+        <v>6919420</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6192,7 +6197,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6202,7 +6207,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6217,22 +6222,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120067652</v>
+        <v>120069026</v>
       </c>
       <c r="B51" t="n">
-        <v>79131</v>
+        <v>90594</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6245,21 +6250,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6269,13 +6274,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502795</v>
+        <v>502514</v>
       </c>
       <c r="R51" t="n">
-        <v>6919545</v>
+        <v>6919477</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6304,7 +6309,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6314,7 +6319,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,12 +6334,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6453,10 +6458,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120065228</v>
+        <v>120069360</v>
       </c>
       <c r="B53" t="n">
-        <v>91902</v>
+        <v>78279</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6469,37 +6474,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503010</v>
+        <v>502491</v>
       </c>
       <c r="R53" t="n">
-        <v>6919294</v>
+        <v>6919384</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6528,7 +6533,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6538,7 +6543,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6553,22 +6558,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120065324</v>
+        <v>120068252</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6577,43 +6582,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503005</v>
+        <v>502690</v>
       </c>
       <c r="R54" t="n">
-        <v>6919310</v>
+        <v>6919538</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120120181</v>
+        <v>120142073</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6694,38 +6694,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>502417</v>
+        <v>502373</v>
       </c>
       <c r="R55" t="n">
-        <v>6919645</v>
+        <v>6919669</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6755,27 +6758,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6794,10 +6788,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120120273</v>
+        <v>120119728</v>
       </c>
       <c r="B56" t="n">
-        <v>78279</v>
+        <v>90825</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6806,25 +6800,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6834,10 +6828,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502391</v>
+        <v>502366</v>
       </c>
       <c r="R56" t="n">
-        <v>6919666</v>
+        <v>6919546</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6906,10 +6900,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120118347</v>
+        <v>120142120</v>
       </c>
       <c r="B57" t="n">
-        <v>78187</v>
+        <v>57473</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6922,34 +6916,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502471</v>
+        <v>502335</v>
       </c>
       <c r="R57" t="n">
-        <v>6919424</v>
+        <v>6919623</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6979,19 +6981,9 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7018,10 +7010,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120119728</v>
+        <v>120120273</v>
       </c>
       <c r="B58" t="n">
-        <v>90825</v>
+        <v>78279</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7030,25 +7022,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7058,10 +7050,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502366</v>
+        <v>502391</v>
       </c>
       <c r="R58" t="n">
-        <v>6919546</v>
+        <v>6919666</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7130,7 +7122,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120121333</v>
+        <v>120120181</v>
       </c>
       <c r="B59" t="n">
         <v>91858</v>
@@ -7170,10 +7162,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502264</v>
+        <v>502417</v>
       </c>
       <c r="R59" t="n">
-        <v>6919557</v>
+        <v>6919645</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7205,7 +7197,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7215,7 +7207,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7460,10 +7452,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120142073</v>
+        <v>120118385</v>
       </c>
       <c r="B62" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7476,37 +7468,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502373</v>
+        <v>502456</v>
       </c>
       <c r="R62" t="n">
-        <v>6919669</v>
+        <v>6919412</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7536,18 +7525,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7566,10 +7564,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120120227</v>
+        <v>120118347</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7582,21 +7580,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7606,10 +7604,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502410</v>
+        <v>502471</v>
       </c>
       <c r="R63" t="n">
-        <v>6919658</v>
+        <v>6919424</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7678,10 +7676,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120118385</v>
+        <v>120120227</v>
       </c>
       <c r="B64" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7694,21 +7692,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7718,10 +7716,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502456</v>
+        <v>502410</v>
       </c>
       <c r="R64" t="n">
-        <v>6919412</v>
+        <v>6919658</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7896,10 +7894,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120142120</v>
+        <v>120121333</v>
       </c>
       <c r="B66" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7908,46 +7906,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502335</v>
+        <v>502264</v>
       </c>
       <c r="R66" t="n">
-        <v>6919623</v>
+        <v>6919557</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7977,9 +7967,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120028546</v>
+        <v>120024983</v>
       </c>
       <c r="B4" t="n">
-        <v>90825</v>
+        <v>78279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502717</v>
+        <v>502808</v>
       </c>
       <c r="R4" t="n">
-        <v>6919429</v>
+        <v>6919302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120024983</v>
+        <v>120028546</v>
       </c>
       <c r="B5" t="n">
-        <v>78279</v>
+        <v>90825</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502808</v>
+        <v>502717</v>
       </c>
       <c r="R5" t="n">
-        <v>6919302</v>
+        <v>6919429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -3177,10 +3177,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120066170</v>
+        <v>120067975</v>
       </c>
       <c r="B24" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3189,38 +3189,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502988</v>
+        <v>502758</v>
       </c>
       <c r="R24" t="n">
-        <v>6919354</v>
+        <v>6919553</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,7 +3289,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120067975</v>
+        <v>120068337</v>
       </c>
       <c r="B25" t="n">
         <v>91858</v>
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502758</v>
+        <v>502628</v>
       </c>
       <c r="R25" t="n">
-        <v>6919553</v>
+        <v>6919549</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3389,22 +3389,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120068337</v>
+        <v>120066170</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3413,41 +3413,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502628</v>
+        <v>502988</v>
       </c>
       <c r="R26" t="n">
-        <v>6919549</v>
+        <v>6919354</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3501,22 +3501,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120069993</v>
+        <v>120067569</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3525,47 +3525,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502615</v>
+        <v>502813</v>
       </c>
       <c r="R27" t="n">
-        <v>6919305</v>
+        <v>6919527</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3597,7 +3588,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3607,7 +3598,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3634,10 +3625,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120067569</v>
+        <v>120069993</v>
       </c>
       <c r="B28" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3646,38 +3637,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502813</v>
+        <v>502615</v>
       </c>
       <c r="R28" t="n">
-        <v>6919527</v>
+        <v>6919305</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3863,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120069084</v>
+        <v>120065022</v>
       </c>
       <c r="B30" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,41 +3875,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502514</v>
+        <v>503071</v>
       </c>
       <c r="R30" t="n">
-        <v>6919477</v>
+        <v>6919233</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3938,7 +3947,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3948,7 +3957,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3963,22 +3972,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120064989</v>
+        <v>120069084</v>
       </c>
       <c r="B31" t="n">
-        <v>78279</v>
+        <v>90545</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,38 +3996,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503055</v>
+        <v>502514</v>
       </c>
       <c r="R31" t="n">
-        <v>6919216</v>
+        <v>6919477</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4050,7 +4059,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4060,7 +4069,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4087,10 +4096,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120065022</v>
+        <v>120064989</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4099,50 +4108,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503071</v>
+        <v>503055</v>
       </c>
       <c r="R32" t="n">
-        <v>6919233</v>
+        <v>6919216</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4196,12 +4196,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120069641</v>
+        <v>120069969</v>
       </c>
       <c r="B35" t="n">
-        <v>57473</v>
+        <v>78187</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4448,39 +4448,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502573</v>
+        <v>502630</v>
       </c>
       <c r="R35" t="n">
-        <v>6919359</v>
+        <v>6919303</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4661,10 +4656,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120069969</v>
+        <v>120069641</v>
       </c>
       <c r="B37" t="n">
-        <v>78187</v>
+        <v>57473</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4677,34 +4672,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502630</v>
+        <v>502573</v>
       </c>
       <c r="R37" t="n">
-        <v>6919303</v>
+        <v>6919359</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5450,10 +5450,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120068779</v>
+        <v>120068117</v>
       </c>
       <c r="B44" t="n">
-        <v>91902</v>
+        <v>79131</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5466,21 +5466,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502513</v>
+        <v>502709</v>
       </c>
       <c r="R44" t="n">
-        <v>6919490</v>
+        <v>6919568</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5562,10 +5562,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120068117</v>
+        <v>120067639</v>
       </c>
       <c r="B45" t="n">
-        <v>79131</v>
+        <v>78279</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5578,21 +5578,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5602,13 +5602,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502709</v>
+        <v>502795</v>
       </c>
       <c r="R45" t="n">
-        <v>6919568</v>
+        <v>6919546</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5662,22 +5662,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120067639</v>
+        <v>120068779</v>
       </c>
       <c r="B46" t="n">
-        <v>78279</v>
+        <v>91902</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5690,21 +5690,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5714,13 +5714,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502795</v>
+        <v>502513</v>
       </c>
       <c r="R46" t="n">
-        <v>6919546</v>
+        <v>6919490</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5774,12 +5774,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120069360</v>
+        <v>120068252</v>
       </c>
       <c r="B53" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6470,25 +6470,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502491</v>
+        <v>502690</v>
       </c>
       <c r="R53" t="n">
-        <v>6919384</v>
+        <v>6919538</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120068252</v>
+        <v>120069360</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>502690</v>
+        <v>502491</v>
       </c>
       <c r="R54" t="n">
-        <v>6919538</v>
+        <v>6919384</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120027814</v>
+        <v>120028984</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502886</v>
+        <v>502586</v>
       </c>
       <c r="R2" t="n">
-        <v>6919441</v>
+        <v>6919340</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120028984</v>
+        <v>120024081</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502586</v>
+        <v>502703</v>
       </c>
       <c r="R3" t="n">
-        <v>6919340</v>
+        <v>6919322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120028546</v>
+        <v>120026409</v>
       </c>
       <c r="B5" t="n">
-        <v>90825</v>
+        <v>89650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502717</v>
+        <v>502910</v>
       </c>
       <c r="R5" t="n">
-        <v>6919429</v>
+        <v>6919294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120024626</v>
+        <v>120028686</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,38 +1140,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502784</v>
+        <v>502735</v>
       </c>
       <c r="R6" t="n">
-        <v>6919311</v>
+        <v>6919361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Inte jättegamla.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120028686</v>
+        <v>120031101</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90512</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,43 +1262,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2013</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502735</v>
+        <v>502863</v>
       </c>
       <c r="R7" t="n">
-        <v>6919361</v>
+        <v>6919305</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,32 +1326,18 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Inte jättegamla.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1362,7 +1356,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120027055</v>
+        <v>120027825</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1398,7 +1392,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1407,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502889</v>
+        <v>502881</v>
       </c>
       <c r="R8" t="n">
-        <v>6919376</v>
+        <v>6919412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,6 +1447,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Både gamla och färska spår på samma tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120027825</v>
+        <v>120029012</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,39 +1494,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502881</v>
+        <v>502589</v>
       </c>
       <c r="R9" t="n">
-        <v>6919412</v>
+        <v>6919321</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Både gamla och färska spår på samma tall.</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120024081</v>
+        <v>120025266</v>
       </c>
       <c r="B10" t="n">
         <v>78279</v>
@@ -1641,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502703</v>
+        <v>502825</v>
       </c>
       <c r="R10" t="n">
-        <v>6919322</v>
+        <v>6919306</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120026409</v>
+        <v>120027055</v>
       </c>
       <c r="B11" t="n">
-        <v>89650</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,34 +1718,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502910</v>
+        <v>502889</v>
       </c>
       <c r="R11" t="n">
-        <v>6919294</v>
+        <v>6919376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120028274</v>
+        <v>120027814</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,47 +1831,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502778</v>
+        <v>502886</v>
       </c>
       <c r="R12" t="n">
-        <v>6919405</v>
+        <v>6919441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120028121</v>
+        <v>120028546</v>
       </c>
       <c r="B13" t="n">
-        <v>90545</v>
+        <v>90825</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,25 +1943,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>65</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1986,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502828</v>
+        <v>502717</v>
       </c>
       <c r="R13" t="n">
-        <v>6919422</v>
+        <v>6919429</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2058,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120031101</v>
+        <v>120028274</v>
       </c>
       <c r="B14" t="n">
-        <v>90512</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,41 +2055,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2013</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502863</v>
+        <v>502778</v>
       </c>
       <c r="R14" t="n">
-        <v>6919305</v>
+        <v>6919405</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,18 +2125,27 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120025266</v>
+        <v>120024406</v>
       </c>
       <c r="B15" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,21 +2180,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502825</v>
+        <v>502726</v>
       </c>
       <c r="R15" t="n">
-        <v>6919306</v>
+        <v>6919308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120024406</v>
+        <v>120028121</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>90545</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,25 +2288,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502726</v>
+        <v>502828</v>
       </c>
       <c r="R16" t="n">
-        <v>6919308</v>
+        <v>6919422</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120029012</v>
+        <v>120024626</v>
       </c>
       <c r="B17" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,25 +2400,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502589</v>
+        <v>502784</v>
       </c>
       <c r="R17" t="n">
-        <v>6919321</v>
+        <v>6919311</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,7 +2500,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120027968</v>
+        <v>120027766</v>
       </c>
       <c r="B18" t="n">
         <v>91858</v>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502856</v>
+        <v>502871</v>
       </c>
       <c r="R18" t="n">
-        <v>6919392</v>
+        <v>6919391</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2612,7 +2612,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120027766</v>
+        <v>120027968</v>
       </c>
       <c r="B19" t="n">
         <v>91858</v>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502871</v>
+        <v>502856</v>
       </c>
       <c r="R19" t="n">
-        <v>6919391</v>
+        <v>6919392</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120067689</v>
+        <v>120066174</v>
       </c>
       <c r="B20" t="n">
         <v>91858</v>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502765</v>
+        <v>502971</v>
       </c>
       <c r="R20" t="n">
-        <v>6919539</v>
+        <v>6919362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120069378</v>
+        <v>120068337</v>
       </c>
       <c r="B21" t="n">
         <v>91858</v>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502481</v>
+        <v>502628</v>
       </c>
       <c r="R21" t="n">
-        <v>6919451</v>
+        <v>6919549</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,22 +2936,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120065915</v>
+        <v>120065324</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2964,27 +2964,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502996</v>
+        <v>503005</v>
       </c>
       <c r="R22" t="n">
-        <v>6919352</v>
+        <v>6919310</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3065,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120067723</v>
+        <v>120067569</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3077,25 +3077,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3105,13 +3105,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502732</v>
+        <v>502813</v>
       </c>
       <c r="R23" t="n">
-        <v>6919555</v>
+        <v>6919527</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3165,22 +3165,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120067975</v>
+        <v>120065184</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3189,38 +3189,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502758</v>
+        <v>503055</v>
       </c>
       <c r="R24" t="n">
-        <v>6919553</v>
+        <v>6919216</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,10 +3289,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120068337</v>
+        <v>120069641</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3301,38 +3301,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502628</v>
+        <v>502573</v>
       </c>
       <c r="R25" t="n">
-        <v>6919549</v>
+        <v>6919359</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3401,10 +3406,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120066170</v>
+        <v>120069360</v>
       </c>
       <c r="B26" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3417,37 +3422,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502988</v>
+        <v>502491</v>
       </c>
       <c r="R26" t="n">
-        <v>6919354</v>
+        <v>6919384</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3476,7 +3481,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3486,7 +3491,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3501,22 +3506,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120067569</v>
+        <v>120067652</v>
       </c>
       <c r="B27" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3529,21 +3534,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3553,13 +3558,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502813</v>
+        <v>502795</v>
       </c>
       <c r="R27" t="n">
-        <v>6919527</v>
+        <v>6919545</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3588,7 +3593,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3598,7 +3603,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,22 +3618,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120069993</v>
+        <v>120066423</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3637,47 +3642,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502615</v>
+        <v>502973</v>
       </c>
       <c r="R28" t="n">
-        <v>6919305</v>
+        <v>6919384</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3709,7 +3705,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,7 +3715,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3746,10 +3742,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120065324</v>
+        <v>120069367</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3762,39 +3758,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503005</v>
+        <v>502491</v>
       </c>
       <c r="R29" t="n">
-        <v>6919310</v>
+        <v>6919384</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3863,10 +3854,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120065022</v>
+        <v>120069378</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,50 +3866,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503071</v>
+        <v>502481</v>
       </c>
       <c r="R30" t="n">
-        <v>6919233</v>
+        <v>6919451</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3947,7 +3929,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3957,7 +3939,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3972,22 +3954,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120069084</v>
+        <v>120067947</v>
       </c>
       <c r="B31" t="n">
-        <v>90545</v>
+        <v>90948</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3996,25 +3978,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4024,10 +4006,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502514</v>
+        <v>502748</v>
       </c>
       <c r="R31" t="n">
-        <v>6919477</v>
+        <v>6919557</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4059,7 +4041,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4069,7 +4051,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Tillsammans med timmergröppa</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4096,10 +4083,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120064989</v>
+        <v>120067558</v>
       </c>
       <c r="B32" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4112,34 +4099,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503055</v>
+        <v>502813</v>
       </c>
       <c r="R32" t="n">
-        <v>6919216</v>
+        <v>6919527</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4171,7 +4158,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4181,7 +4168,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4208,10 +4195,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120065184</v>
+        <v>120067639</v>
       </c>
       <c r="B33" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4224,37 +4211,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503055</v>
+        <v>502795</v>
       </c>
       <c r="R33" t="n">
-        <v>6919216</v>
+        <v>6919546</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4283,7 +4270,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4293,7 +4280,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4308,22 +4295,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120067493</v>
+        <v>120065915</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4336,34 +4323,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502805</v>
+        <v>502996</v>
       </c>
       <c r="R34" t="n">
-        <v>6919532</v>
+        <v>6919352</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4432,10 +4424,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120069969</v>
+        <v>120068130</v>
       </c>
       <c r="B35" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4448,21 +4440,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4472,13 +4464,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502630</v>
+        <v>502709</v>
       </c>
       <c r="R35" t="n">
-        <v>6919303</v>
+        <v>6919568</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4507,7 +4499,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4517,7 +4509,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4532,22 +4524,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120069700</v>
+        <v>120065228</v>
       </c>
       <c r="B36" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4556,38 +4548,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502566</v>
+        <v>503010</v>
       </c>
       <c r="R36" t="n">
-        <v>6919324</v>
+        <v>6919294</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4619,7 +4611,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4629,7 +4621,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4656,10 +4648,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120069641</v>
+        <v>120067311</v>
       </c>
       <c r="B37" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4672,39 +4664,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502573</v>
+        <v>502822</v>
       </c>
       <c r="R37" t="n">
-        <v>6919359</v>
+        <v>6919420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4773,10 +4760,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120067947</v>
+        <v>120067493</v>
       </c>
       <c r="B38" t="n">
-        <v>90948</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4785,25 +4772,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>298</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4813,13 +4800,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502748</v>
+        <v>502805</v>
       </c>
       <c r="R38" t="n">
-        <v>6919557</v>
+        <v>6919532</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4848,7 +4835,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4858,12 +4845,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Tillsammans med timmergröppa</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4878,22 +4860,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120069367</v>
+        <v>120067689</v>
       </c>
       <c r="B39" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4902,25 +4884,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4930,10 +4912,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502491</v>
+        <v>502765</v>
       </c>
       <c r="R39" t="n">
-        <v>6919384</v>
+        <v>6919539</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5002,7 +4984,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120066174</v>
+        <v>120067723</v>
       </c>
       <c r="B40" t="n">
         <v>91858</v>
@@ -5042,10 +5024,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502971</v>
+        <v>502732</v>
       </c>
       <c r="R40" t="n">
-        <v>6919362</v>
+        <v>6919555</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5114,10 +5096,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120067558</v>
+        <v>120069084</v>
       </c>
       <c r="B41" t="n">
-        <v>79131</v>
+        <v>90545</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5126,25 +5108,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5154,10 +5136,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502813</v>
+        <v>502514</v>
       </c>
       <c r="R41" t="n">
-        <v>6919527</v>
+        <v>6919477</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5189,7 +5171,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5199,7 +5181,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5226,10 +5208,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120067652</v>
+        <v>120069993</v>
       </c>
       <c r="B42" t="n">
-        <v>79131</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5238,41 +5220,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502795</v>
+        <v>502615</v>
       </c>
       <c r="R42" t="n">
-        <v>6919545</v>
+        <v>6919305</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5301,7 +5292,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5311,7 +5302,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5326,22 +5317,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120065228</v>
+        <v>120069026</v>
       </c>
       <c r="B43" t="n">
-        <v>91902</v>
+        <v>90594</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5354,34 +5345,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503010</v>
+        <v>502514</v>
       </c>
       <c r="R43" t="n">
-        <v>6919294</v>
+        <v>6919477</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5413,7 +5404,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5423,7 +5414,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5450,10 +5441,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120068117</v>
+        <v>120068779</v>
       </c>
       <c r="B44" t="n">
-        <v>79131</v>
+        <v>91902</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5466,21 +5457,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5490,10 +5481,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502709</v>
+        <v>502513</v>
       </c>
       <c r="R44" t="n">
-        <v>6919568</v>
+        <v>6919490</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5525,7 +5516,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5535,7 +5526,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5562,10 +5553,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120067639</v>
+        <v>120068252</v>
       </c>
       <c r="B45" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5574,25 +5565,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5602,10 +5593,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502795</v>
+        <v>502690</v>
       </c>
       <c r="R45" t="n">
-        <v>6919546</v>
+        <v>6919538</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5674,10 +5665,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120068779</v>
+        <v>120066170</v>
       </c>
       <c r="B46" t="n">
-        <v>91902</v>
+        <v>79160</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5690,34 +5681,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502513</v>
+        <v>502988</v>
       </c>
       <c r="R46" t="n">
-        <v>6919490</v>
+        <v>6919354</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5749,7 +5740,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5759,7 +5750,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5786,10 +5777,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120068130</v>
+        <v>120065504</v>
       </c>
       <c r="B47" t="n">
-        <v>79160</v>
+        <v>91852</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5802,21 +5793,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5826,13 +5817,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502709</v>
+        <v>502986</v>
       </c>
       <c r="R47" t="n">
-        <v>6919568</v>
+        <v>6919325</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5861,7 +5852,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5871,7 +5862,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5886,12 +5877,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6010,10 +6001,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120066423</v>
+        <v>120067975</v>
       </c>
       <c r="B49" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6022,38 +6013,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502973</v>
+        <v>502758</v>
       </c>
       <c r="R49" t="n">
-        <v>6919384</v>
+        <v>6919553</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6085,7 +6076,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6095,7 +6086,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6122,10 +6113,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120067311</v>
+        <v>120069700</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>91862</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6134,25 +6125,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6162,13 +6153,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502822</v>
+        <v>502566</v>
       </c>
       <c r="R50" t="n">
-        <v>6919420</v>
+        <v>6919324</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6197,7 +6188,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6207,7 +6198,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6222,22 +6213,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120069026</v>
+        <v>120069969</v>
       </c>
       <c r="B51" t="n">
-        <v>90594</v>
+        <v>78187</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6250,21 +6241,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6274,13 +6265,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502514</v>
+        <v>502630</v>
       </c>
       <c r="R51" t="n">
-        <v>6919477</v>
+        <v>6919303</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6309,7 +6300,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6319,7 +6310,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6334,22 +6325,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120065504</v>
+        <v>120065022</v>
       </c>
       <c r="B52" t="n">
-        <v>91852</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6358,38 +6349,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502986</v>
+        <v>503071</v>
       </c>
       <c r="R52" t="n">
-        <v>6919325</v>
+        <v>6919233</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120068252</v>
+        <v>120068117</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6470,25 +6470,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6498,13 +6498,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502690</v>
+        <v>502709</v>
       </c>
       <c r="R53" t="n">
-        <v>6919538</v>
+        <v>6919568</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6558,19 +6558,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120069360</v>
+        <v>120064989</v>
       </c>
       <c r="B54" t="n">
         <v>78279</v>
@@ -6606,17 +6606,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>502491</v>
+        <v>503055</v>
       </c>
       <c r="R54" t="n">
-        <v>6919384</v>
+        <v>6919216</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,22 +6670,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120142073</v>
+        <v>120120227</v>
       </c>
       <c r="B55" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6698,37 +6698,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>502373</v>
+        <v>502410</v>
       </c>
       <c r="R55" t="n">
-        <v>6919669</v>
+        <v>6919658</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6758,18 +6755,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6788,10 +6794,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120119728</v>
+        <v>120120273</v>
       </c>
       <c r="B56" t="n">
-        <v>90825</v>
+        <v>78279</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6800,25 +6806,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6828,10 +6834,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502366</v>
+        <v>502391</v>
       </c>
       <c r="R56" t="n">
-        <v>6919546</v>
+        <v>6919666</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6900,10 +6906,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120142120</v>
+        <v>120142102</v>
       </c>
       <c r="B57" t="n">
-        <v>57473</v>
+        <v>78187</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6916,31 +6922,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6948,10 +6949,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502335</v>
+        <v>502265</v>
       </c>
       <c r="R57" t="n">
-        <v>6919623</v>
+        <v>6919613</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6992,6 +6993,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7010,10 +7012,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120120273</v>
+        <v>120142120</v>
       </c>
       <c r="B58" t="n">
-        <v>78279</v>
+        <v>57473</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7026,34 +7028,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502391</v>
+        <v>502335</v>
       </c>
       <c r="R58" t="n">
-        <v>6919666</v>
+        <v>6919623</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7083,19 +7093,9 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7122,10 +7122,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120120181</v>
+        <v>120118385</v>
       </c>
       <c r="B59" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7134,25 +7134,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502417</v>
+        <v>502456</v>
       </c>
       <c r="R59" t="n">
-        <v>6919645</v>
+        <v>6919412</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7234,10 +7234,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120119046</v>
+        <v>120118347</v>
       </c>
       <c r="B60" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502418</v>
+        <v>502471</v>
       </c>
       <c r="R60" t="n">
-        <v>6919456</v>
+        <v>6919424</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7346,10 +7346,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120142102</v>
+        <v>120119046</v>
       </c>
       <c r="B61" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7362,37 +7362,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502265</v>
+        <v>502418</v>
       </c>
       <c r="R61" t="n">
-        <v>6919613</v>
+        <v>6919456</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7422,18 +7419,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7452,10 +7458,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120118385</v>
+        <v>120142073</v>
       </c>
       <c r="B62" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7468,34 +7474,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502456</v>
+        <v>502373</v>
       </c>
       <c r="R62" t="n">
-        <v>6919412</v>
+        <v>6919669</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7525,27 +7534,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7564,10 +7564,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120118347</v>
+        <v>120121333</v>
       </c>
       <c r="B63" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7576,25 +7576,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7604,10 +7604,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502471</v>
+        <v>502264</v>
       </c>
       <c r="R63" t="n">
-        <v>6919424</v>
+        <v>6919557</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7676,10 +7676,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120120227</v>
+        <v>120119728</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>90825</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7688,25 +7688,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7716,10 +7716,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502410</v>
+        <v>502366</v>
       </c>
       <c r="R64" t="n">
-        <v>6919658</v>
+        <v>6919546</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120121333</v>
+        <v>120120181</v>
       </c>
       <c r="B66" t="n">
         <v>91858</v>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502264</v>
+        <v>502417</v>
       </c>
       <c r="R66" t="n">
-        <v>6919557</v>
+        <v>6919645</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120024406</v>
+        <v>120028121</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>90545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502726</v>
+        <v>502828</v>
       </c>
       <c r="R15" t="n">
-        <v>6919308</v>
+        <v>6919422</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120028121</v>
+        <v>120024626</v>
       </c>
       <c r="B16" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,21 +2292,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502828</v>
+        <v>502784</v>
       </c>
       <c r="R16" t="n">
-        <v>6919422</v>
+        <v>6919311</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120024626</v>
+        <v>120024406</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,25 +2400,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502784</v>
+        <v>502726</v>
       </c>
       <c r="R17" t="n">
-        <v>6919311</v>
+        <v>6919308</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120028984</v>
+        <v>120024983</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502586</v>
+        <v>502808</v>
       </c>
       <c r="R2" t="n">
-        <v>6919340</v>
+        <v>6919302</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120024081</v>
+        <v>120028686</v>
       </c>
       <c r="B3" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502703</v>
+        <v>502735</v>
       </c>
       <c r="R3" t="n">
-        <v>6919322</v>
+        <v>6919361</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Inte jättegamla.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120024983</v>
+        <v>120027814</v>
       </c>
       <c r="B4" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502808</v>
+        <v>502886</v>
       </c>
       <c r="R4" t="n">
-        <v>6919302</v>
+        <v>6919441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120026409</v>
+        <v>120027055</v>
       </c>
       <c r="B5" t="n">
-        <v>89650</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502910</v>
+        <v>502889</v>
       </c>
       <c r="R5" t="n">
-        <v>6919294</v>
+        <v>6919376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120028686</v>
+        <v>120028121</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,43 +1150,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502735</v>
+        <v>502828</v>
       </c>
       <c r="R6" t="n">
-        <v>6919361</v>
+        <v>6919422</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,11 +1224,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Inte jättegamla.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120031101</v>
+        <v>120024081</v>
       </c>
       <c r="B7" t="n">
-        <v>90512</v>
+        <v>78279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,41 +1262,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2013</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502863</v>
+        <v>502703</v>
       </c>
       <c r="R7" t="n">
-        <v>6919305</v>
+        <v>6919322</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,18 +1323,27 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1478,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120029012</v>
+        <v>120028546</v>
       </c>
       <c r="B9" t="n">
-        <v>78279</v>
+        <v>90825</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1496,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502589</v>
+        <v>502717</v>
       </c>
       <c r="R9" t="n">
-        <v>6919321</v>
+        <v>6919429</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120025266</v>
+        <v>120027968</v>
       </c>
       <c r="B10" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502825</v>
+        <v>502856</v>
       </c>
       <c r="R10" t="n">
-        <v>6919306</v>
+        <v>6919392</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1702,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120027055</v>
+        <v>120024406</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,39 +1724,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502889</v>
+        <v>502726</v>
       </c>
       <c r="R11" t="n">
-        <v>6919376</v>
+        <v>6919308</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1819,7 +1820,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120027814</v>
+        <v>120024626</v>
       </c>
       <c r="B12" t="n">
         <v>91858</v>
@@ -1855,14 +1856,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502886</v>
+        <v>502784</v>
       </c>
       <c r="R12" t="n">
-        <v>6919441</v>
+        <v>6919311</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120028546</v>
+        <v>120029012</v>
       </c>
       <c r="B13" t="n">
-        <v>90825</v>
+        <v>78279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,25 +1944,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1971,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502717</v>
+        <v>502589</v>
       </c>
       <c r="R13" t="n">
-        <v>6919429</v>
+        <v>6919321</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120028274</v>
+        <v>120025266</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>78279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,43 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502778</v>
+        <v>502825</v>
       </c>
       <c r="R14" t="n">
-        <v>6919405</v>
+        <v>6919306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120028121</v>
+        <v>120028274</v>
       </c>
       <c r="B15" t="n">
-        <v>90545</v>
+        <v>57473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,38 +2168,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502828</v>
+        <v>502778</v>
       </c>
       <c r="R15" t="n">
-        <v>6919422</v>
+        <v>6919405</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120024626</v>
+        <v>120027766</v>
       </c>
       <c r="B16" t="n">
         <v>91858</v>
@@ -2316,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502784</v>
+        <v>502871</v>
       </c>
       <c r="R16" t="n">
-        <v>6919311</v>
+        <v>6919391</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2388,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120024406</v>
+        <v>120028984</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,34 +2405,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502726</v>
+        <v>502586</v>
       </c>
       <c r="R17" t="n">
-        <v>6919308</v>
+        <v>6919340</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120027766</v>
+        <v>120026409</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,38 +2518,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502871</v>
+        <v>502910</v>
       </c>
       <c r="R18" t="n">
-        <v>6919391</v>
+        <v>6919294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2612,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120027968</v>
+        <v>120031101</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>90512</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,38 +2630,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>2013</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502856</v>
+        <v>502863</v>
       </c>
       <c r="R19" t="n">
-        <v>6919392</v>
+        <v>6919305</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2685,27 +2694,18 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120066174</v>
+        <v>120069993</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,41 +2736,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502971</v>
+        <v>502615</v>
       </c>
       <c r="R20" t="n">
-        <v>6919362</v>
+        <v>6919305</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,22 +2833,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120068337</v>
+        <v>120065022</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,38 +2857,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502628</v>
+        <v>503071</v>
       </c>
       <c r="R21" t="n">
-        <v>6919549</v>
+        <v>6919233</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,10 +2966,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120065324</v>
+        <v>120067975</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,46 +2978,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503005</v>
+        <v>502758</v>
       </c>
       <c r="R22" t="n">
-        <v>6919310</v>
+        <v>6919553</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3028,7 +3041,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3038,7 +3051,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3053,22 +3066,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120067569</v>
+        <v>120069969</v>
       </c>
       <c r="B23" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3081,21 +3094,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3105,13 +3118,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502813</v>
+        <v>502630</v>
       </c>
       <c r="R23" t="n">
-        <v>6919527</v>
+        <v>6919303</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3140,7 +3153,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3150,7 +3163,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3165,22 +3178,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120065184</v>
+        <v>120069084</v>
       </c>
       <c r="B24" t="n">
-        <v>79160</v>
+        <v>90545</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3189,38 +3202,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503055</v>
+        <v>502514</v>
       </c>
       <c r="R24" t="n">
-        <v>6919216</v>
+        <v>6919477</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3252,7 +3265,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3275,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,10 +3302,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120069641</v>
+        <v>120068130</v>
       </c>
       <c r="B25" t="n">
-        <v>57473</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3305,42 +3318,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502573</v>
+        <v>502709</v>
       </c>
       <c r="R25" t="n">
-        <v>6919359</v>
+        <v>6919568</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3369,7 +3377,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3379,7 +3387,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3394,19 +3402,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120069360</v>
+        <v>120066423</v>
       </c>
       <c r="B26" t="n">
         <v>78279</v>
@@ -3442,17 +3450,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502491</v>
+        <v>502973</v>
       </c>
       <c r="R26" t="n">
         <v>6919384</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3481,7 +3489,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3491,7 +3499,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3506,22 +3514,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120067652</v>
+        <v>120065228</v>
       </c>
       <c r="B27" t="n">
-        <v>79131</v>
+        <v>91902</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3534,37 +3542,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502795</v>
+        <v>503010</v>
       </c>
       <c r="R27" t="n">
-        <v>6919545</v>
+        <v>6919294</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3593,7 +3601,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3603,7 +3611,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3618,22 +3626,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120066423</v>
+        <v>120069378</v>
       </c>
       <c r="B28" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3642,41 +3650,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502973</v>
+        <v>502481</v>
       </c>
       <c r="R28" t="n">
-        <v>6919384</v>
+        <v>6919451</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3705,7 +3713,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3715,7 +3723,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3742,10 +3750,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120069367</v>
+        <v>120069641</v>
       </c>
       <c r="B29" t="n">
-        <v>78278</v>
+        <v>57473</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3758,34 +3766,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502491</v>
+        <v>502573</v>
       </c>
       <c r="R29" t="n">
-        <v>6919384</v>
+        <v>6919359</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,10 +3867,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120069378</v>
+        <v>120067558</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3866,25 +3879,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3894,13 +3907,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502481</v>
+        <v>502813</v>
       </c>
       <c r="R30" t="n">
-        <v>6919451</v>
+        <v>6919527</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3929,7 +3942,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3939,7 +3952,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3966,10 +3979,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120067947</v>
+        <v>120065324</v>
       </c>
       <c r="B31" t="n">
-        <v>90948</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3978,41 +3991,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>298</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502748</v>
+        <v>503005</v>
       </c>
       <c r="R31" t="n">
-        <v>6919557</v>
+        <v>6919310</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4041,7 +4059,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4051,12 +4069,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Tillsammans med timmergröppa</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4071,22 +4084,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120067558</v>
+        <v>120065184</v>
       </c>
       <c r="B32" t="n">
-        <v>79131</v>
+        <v>79160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4099,34 +4112,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502813</v>
+        <v>503055</v>
       </c>
       <c r="R32" t="n">
-        <v>6919527</v>
+        <v>6919216</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4158,7 +4171,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4168,7 +4181,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4195,10 +4208,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120067639</v>
+        <v>120068779</v>
       </c>
       <c r="B33" t="n">
-        <v>78279</v>
+        <v>91902</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4211,21 +4224,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4235,13 +4248,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502795</v>
+        <v>502513</v>
       </c>
       <c r="R33" t="n">
-        <v>6919546</v>
+        <v>6919490</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4270,7 +4283,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4280,7 +4293,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4295,22 +4308,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120065915</v>
+        <v>120067569</v>
       </c>
       <c r="B34" t="n">
-        <v>57473</v>
+        <v>78279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4323,42 +4336,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502996</v>
+        <v>502813</v>
       </c>
       <c r="R34" t="n">
-        <v>6919352</v>
+        <v>6919527</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4387,7 +4395,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4397,7 +4405,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4412,22 +4420,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120068130</v>
+        <v>120069700</v>
       </c>
       <c r="B35" t="n">
-        <v>79160</v>
+        <v>91862</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4436,25 +4444,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4464,10 +4472,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502709</v>
+        <v>502566</v>
       </c>
       <c r="R35" t="n">
-        <v>6919568</v>
+        <v>6919324</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4499,7 +4507,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4509,7 +4517,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4536,10 +4544,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120065228</v>
+        <v>120065504</v>
       </c>
       <c r="B36" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4552,37 +4560,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503010</v>
+        <v>502986</v>
       </c>
       <c r="R36" t="n">
-        <v>6919294</v>
+        <v>6919325</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4611,7 +4619,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4621,7 +4629,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4636,22 +4644,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120067311</v>
+        <v>120069026</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4664,21 +4672,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4688,13 +4696,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502822</v>
+        <v>502514</v>
       </c>
       <c r="R37" t="n">
-        <v>6919420</v>
+        <v>6919477</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4723,7 +4731,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4733,7 +4741,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4748,22 +4756,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120067493</v>
+        <v>120068252</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4772,25 +4780,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4800,10 +4808,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502805</v>
+        <v>502690</v>
       </c>
       <c r="R38" t="n">
-        <v>6919532</v>
+        <v>6919538</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4872,10 +4880,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120067689</v>
+        <v>120067652</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4884,25 +4892,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4912,10 +4920,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502765</v>
+        <v>502795</v>
       </c>
       <c r="R39" t="n">
-        <v>6919539</v>
+        <v>6919545</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4984,10 +4992,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120067723</v>
+        <v>120066170</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4996,41 +5004,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502732</v>
+        <v>502988</v>
       </c>
       <c r="R40" t="n">
-        <v>6919555</v>
+        <v>6919354</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5059,7 +5067,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5069,7 +5077,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5084,22 +5092,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120069084</v>
+        <v>120067493</v>
       </c>
       <c r="B41" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5108,25 +5116,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5136,13 +5144,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502514</v>
+        <v>502805</v>
       </c>
       <c r="R41" t="n">
-        <v>6919477</v>
+        <v>6919532</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5171,7 +5179,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5181,7 +5189,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5196,22 +5204,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120069993</v>
+        <v>120069367</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5220,50 +5228,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502615</v>
+        <v>502491</v>
       </c>
       <c r="R42" t="n">
-        <v>6919305</v>
+        <v>6919384</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5292,7 +5291,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5302,7 +5301,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5317,22 +5316,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120069026</v>
+        <v>120067311</v>
       </c>
       <c r="B43" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5345,21 +5344,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5369,13 +5368,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502514</v>
+        <v>502822</v>
       </c>
       <c r="R43" t="n">
-        <v>6919477</v>
+        <v>6919420</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5404,7 +5403,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5414,7 +5413,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5429,22 +5428,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120068779</v>
+        <v>120067639</v>
       </c>
       <c r="B44" t="n">
-        <v>91902</v>
+        <v>78279</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5457,21 +5456,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5481,13 +5480,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502513</v>
+        <v>502795</v>
       </c>
       <c r="R44" t="n">
-        <v>6919490</v>
+        <v>6919546</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5516,7 +5515,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5526,7 +5525,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5541,19 +5540,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120068252</v>
+        <v>120066174</v>
       </c>
       <c r="B45" t="n">
         <v>91858</v>
@@ -5593,10 +5592,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502690</v>
+        <v>502971</v>
       </c>
       <c r="R45" t="n">
-        <v>6919538</v>
+        <v>6919362</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5665,10 +5664,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120066170</v>
+        <v>120065915</v>
       </c>
       <c r="B46" t="n">
-        <v>79160</v>
+        <v>57473</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5681,37 +5680,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502988</v>
+        <v>502996</v>
       </c>
       <c r="R46" t="n">
-        <v>6919354</v>
+        <v>6919352</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5740,7 +5744,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5750,7 +5754,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5765,22 +5769,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120065504</v>
+        <v>120067947</v>
       </c>
       <c r="B47" t="n">
-        <v>91852</v>
+        <v>90948</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5789,25 +5793,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5817,13 +5821,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502986</v>
+        <v>502748</v>
       </c>
       <c r="R47" t="n">
-        <v>6919325</v>
+        <v>6919557</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5852,7 +5856,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5862,7 +5866,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Tillsammans med timmergröppa</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5877,19 +5886,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120065342</v>
+        <v>120067689</v>
       </c>
       <c r="B48" t="n">
         <v>91858</v>
@@ -5929,10 +5938,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503007</v>
+        <v>502765</v>
       </c>
       <c r="R48" t="n">
-        <v>6919317</v>
+        <v>6919539</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6001,10 +6010,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120067975</v>
+        <v>120064989</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6013,38 +6022,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502758</v>
+        <v>503055</v>
       </c>
       <c r="R49" t="n">
-        <v>6919553</v>
+        <v>6919216</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6076,7 +6085,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6086,7 +6095,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6113,10 +6122,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120069700</v>
+        <v>120065342</v>
       </c>
       <c r="B50" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6125,25 +6134,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6153,13 +6162,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502566</v>
+        <v>503007</v>
       </c>
       <c r="R50" t="n">
-        <v>6919324</v>
+        <v>6919317</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6188,7 +6197,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6198,7 +6207,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6213,22 +6222,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120069969</v>
+        <v>120067723</v>
       </c>
       <c r="B51" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6237,25 +6246,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6265,10 +6274,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502630</v>
+        <v>502732</v>
       </c>
       <c r="R51" t="n">
-        <v>6919303</v>
+        <v>6919555</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6337,10 +6346,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120065022</v>
+        <v>120068337</v>
       </c>
       <c r="B52" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6349,47 +6358,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503071</v>
+        <v>502628</v>
       </c>
       <c r="R52" t="n">
-        <v>6919233</v>
+        <v>6919549</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120068117</v>
+        <v>120069360</v>
       </c>
       <c r="B53" t="n">
-        <v>79131</v>
+        <v>78279</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6474,21 +6474,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6498,13 +6498,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502709</v>
+        <v>502491</v>
       </c>
       <c r="R53" t="n">
-        <v>6919568</v>
+        <v>6919384</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6558,22 +6558,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120064989</v>
+        <v>120068117</v>
       </c>
       <c r="B54" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6586,34 +6586,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503055</v>
+        <v>502709</v>
       </c>
       <c r="R54" t="n">
-        <v>6919216</v>
+        <v>6919568</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6682,10 +6682,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120120227</v>
+        <v>120118347</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6698,21 +6698,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>502410</v>
+        <v>502471</v>
       </c>
       <c r="R55" t="n">
-        <v>6919658</v>
+        <v>6919424</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6794,10 +6794,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120120273</v>
+        <v>120142073</v>
       </c>
       <c r="B56" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6810,34 +6810,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502391</v>
+        <v>502373</v>
       </c>
       <c r="R56" t="n">
-        <v>6919666</v>
+        <v>6919669</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6867,27 +6870,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6906,10 +6900,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120142102</v>
+        <v>120120273</v>
       </c>
       <c r="B57" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6922,37 +6916,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502265</v>
+        <v>502391</v>
       </c>
       <c r="R57" t="n">
-        <v>6919613</v>
+        <v>6919666</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6982,18 +6973,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7012,10 +7012,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120142120</v>
+        <v>120121333</v>
       </c>
       <c r="B58" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7024,46 +7024,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502335</v>
+        <v>502264</v>
       </c>
       <c r="R58" t="n">
-        <v>6919623</v>
+        <v>6919557</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7093,9 +7085,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7122,10 +7124,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120118385</v>
+        <v>120119728</v>
       </c>
       <c r="B59" t="n">
-        <v>78279</v>
+        <v>90825</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7134,25 +7136,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7162,10 +7164,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502456</v>
+        <v>502366</v>
       </c>
       <c r="R59" t="n">
-        <v>6919412</v>
+        <v>6919546</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7234,10 +7236,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120118347</v>
+        <v>120120227</v>
       </c>
       <c r="B60" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7250,21 +7252,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7274,10 +7276,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502471</v>
+        <v>502410</v>
       </c>
       <c r="R60" t="n">
-        <v>6919424</v>
+        <v>6919658</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7346,10 +7348,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120119046</v>
+        <v>120142102</v>
       </c>
       <c r="B61" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7362,34 +7364,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502418</v>
+        <v>502265</v>
       </c>
       <c r="R61" t="n">
-        <v>6919456</v>
+        <v>6919613</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7419,27 +7424,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7458,10 +7454,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120142073</v>
+        <v>120142089</v>
       </c>
       <c r="B62" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7470,25 +7466,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7564,10 +7560,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120121333</v>
+        <v>120119046</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7576,25 +7572,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7604,10 +7600,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502264</v>
+        <v>502418</v>
       </c>
       <c r="R63" t="n">
-        <v>6919557</v>
+        <v>6919456</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7639,7 +7635,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7649,7 +7645,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7676,10 +7672,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120119728</v>
+        <v>120118385</v>
       </c>
       <c r="B64" t="n">
-        <v>90825</v>
+        <v>78279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7688,25 +7684,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7716,10 +7712,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502366</v>
+        <v>502456</v>
       </c>
       <c r="R64" t="n">
-        <v>6919546</v>
+        <v>6919412</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7788,10 +7784,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120142089</v>
+        <v>120142120</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7800,30 +7796,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7831,10 +7832,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>502373</v>
+        <v>502335</v>
       </c>
       <c r="R65" t="n">
-        <v>6919669</v>
+        <v>6919623</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7875,7 +7876,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120024983</v>
+        <v>120024081</v>
       </c>
       <c r="B2" t="n">
         <v>78279</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502808</v>
+        <v>502703</v>
       </c>
       <c r="R2" t="n">
-        <v>6919302</v>
+        <v>6919322</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120028686</v>
+        <v>120027055</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -828,14 +828,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502735</v>
+        <v>502889</v>
       </c>
       <c r="R3" t="n">
-        <v>6919361</v>
+        <v>6919376</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Inte jättegamla.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120027814</v>
+        <v>120028121</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502886</v>
+        <v>502828</v>
       </c>
       <c r="R4" t="n">
-        <v>6919441</v>
+        <v>6919422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120027055</v>
+        <v>120028984</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1062,14 +1057,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502889</v>
+        <v>502586</v>
       </c>
       <c r="R5" t="n">
-        <v>6919376</v>
+        <v>6919340</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120028121</v>
+        <v>120028274</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,38 +1145,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502828</v>
+        <v>502778</v>
       </c>
       <c r="R6" t="n">
-        <v>6919422</v>
+        <v>6919405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1254,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120024081</v>
+        <v>120025266</v>
       </c>
       <c r="B7" t="n">
         <v>78279</v>
@@ -1290,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502703</v>
+        <v>502825</v>
       </c>
       <c r="R7" t="n">
-        <v>6919322</v>
+        <v>6919306</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120027825</v>
+        <v>120024983</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,39 +1382,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502881</v>
+        <v>502808</v>
       </c>
       <c r="R8" t="n">
-        <v>6919412</v>
+        <v>6919302</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,11 +1452,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Både gamla och färska spår på samma tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120028546</v>
+        <v>120031101</v>
       </c>
       <c r="B9" t="n">
-        <v>90825</v>
+        <v>90512</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,38 +1490,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>2013</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502717</v>
+        <v>502863</v>
       </c>
       <c r="R9" t="n">
-        <v>6919429</v>
+        <v>6919305</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,27 +1554,18 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1596,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120027968</v>
+        <v>120026409</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1596,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502856</v>
+        <v>502910</v>
       </c>
       <c r="R10" t="n">
-        <v>6919392</v>
+        <v>6919294</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120024406</v>
+        <v>120028686</v>
       </c>
       <c r="B11" t="n">
-        <v>79160</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,34 +1712,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502726</v>
+        <v>502735</v>
       </c>
       <c r="R11" t="n">
-        <v>6919308</v>
+        <v>6919361</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1786,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Inte jättegamla.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120024626</v>
+        <v>120027825</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,38 +1830,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502784</v>
+        <v>502881</v>
       </c>
       <c r="R12" t="n">
-        <v>6919311</v>
+        <v>6919412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,6 +1909,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Både gamla och färska spår på samma tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120029012</v>
+        <v>120024626</v>
       </c>
       <c r="B13" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,25 +1952,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502589</v>
+        <v>502784</v>
       </c>
       <c r="R13" t="n">
-        <v>6919321</v>
+        <v>6919311</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,7 +2052,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120025266</v>
+        <v>120029012</v>
       </c>
       <c r="B14" t="n">
         <v>78279</v>
@@ -2084,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502825</v>
+        <v>502589</v>
       </c>
       <c r="R14" t="n">
-        <v>6919306</v>
+        <v>6919321</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120028274</v>
+        <v>120028546</v>
       </c>
       <c r="B15" t="n">
-        <v>57473</v>
+        <v>90825</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,47 +2176,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>65</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502778</v>
+        <v>502717</v>
       </c>
       <c r="R15" t="n">
-        <v>6919405</v>
+        <v>6919429</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120027766</v>
+        <v>120024406</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,25 +2288,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2317,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502871</v>
+        <v>502726</v>
       </c>
       <c r="R16" t="n">
-        <v>6919391</v>
+        <v>6919308</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2389,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120028984</v>
+        <v>120027766</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,43 +2400,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502586</v>
+        <v>502871</v>
       </c>
       <c r="R17" t="n">
-        <v>6919340</v>
+        <v>6919391</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120026409</v>
+        <v>120027968</v>
       </c>
       <c r="B18" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,38 +2512,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502910</v>
+        <v>502856</v>
       </c>
       <c r="R18" t="n">
-        <v>6919294</v>
+        <v>6919392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120031101</v>
+        <v>120027814</v>
       </c>
       <c r="B19" t="n">
-        <v>90512</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,41 +2624,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2013</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502863</v>
+        <v>502886</v>
       </c>
       <c r="R19" t="n">
-        <v>6919305</v>
+        <v>6919441</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2694,18 +2685,27 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120069993</v>
+        <v>120064989</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,47 +2736,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502615</v>
+        <v>503055</v>
       </c>
       <c r="R20" t="n">
-        <v>6919305</v>
+        <v>6919216</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2808,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120065022</v>
+        <v>120069360</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,47 +2848,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503071</v>
+        <v>502491</v>
       </c>
       <c r="R21" t="n">
-        <v>6919233</v>
+        <v>6919384</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,10 +2948,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120067975</v>
+        <v>120067493</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2978,25 +2960,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3006,13 +2988,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502758</v>
+        <v>502805</v>
       </c>
       <c r="R22" t="n">
-        <v>6919553</v>
+        <v>6919532</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3041,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3051,7 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,22 +3048,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120069969</v>
+        <v>120069993</v>
       </c>
       <c r="B23" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3090,41 +3072,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502630</v>
+        <v>502615</v>
       </c>
       <c r="R23" t="n">
-        <v>6919303</v>
+        <v>6919305</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3153,7 +3144,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3163,7 +3154,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3178,22 +3169,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120069084</v>
+        <v>120065324</v>
       </c>
       <c r="B24" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3202,41 +3193,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502514</v>
+        <v>503005</v>
       </c>
       <c r="R24" t="n">
-        <v>6919477</v>
+        <v>6919310</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3265,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3275,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3290,22 +3286,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120068130</v>
+        <v>120069700</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>91862</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3314,25 +3310,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3342,10 +3338,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502709</v>
+        <v>502566</v>
       </c>
       <c r="R25" t="n">
-        <v>6919568</v>
+        <v>6919324</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3377,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3387,7 +3383,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3414,10 +3410,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120066423</v>
+        <v>120067975</v>
       </c>
       <c r="B26" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3426,38 +3422,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502973</v>
+        <v>502758</v>
       </c>
       <c r="R26" t="n">
-        <v>6919384</v>
+        <v>6919553</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3489,7 +3485,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3499,7 +3495,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,10 +3522,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120065228</v>
+        <v>120066174</v>
       </c>
       <c r="B27" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3538,41 +3534,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503010</v>
+        <v>502971</v>
       </c>
       <c r="R27" t="n">
-        <v>6919294</v>
+        <v>6919362</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3601,7 +3597,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3611,7 +3607,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,19 +3622,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120069378</v>
+        <v>120067723</v>
       </c>
       <c r="B28" t="n">
         <v>91858</v>
@@ -3678,13 +3674,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502481</v>
+        <v>502732</v>
       </c>
       <c r="R28" t="n">
-        <v>6919451</v>
+        <v>6919555</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3713,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3723,7 +3719,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3738,22 +3734,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120069641</v>
+        <v>120069969</v>
       </c>
       <c r="B29" t="n">
-        <v>57473</v>
+        <v>78187</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3766,39 +3762,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502573</v>
+        <v>502630</v>
       </c>
       <c r="R29" t="n">
-        <v>6919359</v>
+        <v>6919303</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3867,10 +3858,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120067558</v>
+        <v>120065342</v>
       </c>
       <c r="B30" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3879,25 +3870,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3907,13 +3898,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502813</v>
+        <v>503007</v>
       </c>
       <c r="R30" t="n">
-        <v>6919527</v>
+        <v>6919317</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3942,7 +3933,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3952,7 +3943,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3967,22 +3958,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120065324</v>
+        <v>120066170</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3995,42 +3986,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503005</v>
+        <v>502988</v>
       </c>
       <c r="R31" t="n">
-        <v>6919310</v>
+        <v>6919354</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4059,7 +4045,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4069,7 +4055,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4084,12 +4070,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4208,10 +4194,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120068779</v>
+        <v>120067639</v>
       </c>
       <c r="B33" t="n">
-        <v>91902</v>
+        <v>78279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4224,21 +4210,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4248,13 +4234,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502513</v>
+        <v>502795</v>
       </c>
       <c r="R33" t="n">
-        <v>6919490</v>
+        <v>6919546</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4283,7 +4269,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4293,7 +4279,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4308,22 +4294,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120067569</v>
+        <v>120067311</v>
       </c>
       <c r="B34" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4336,21 +4322,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4360,13 +4346,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502813</v>
+        <v>502822</v>
       </c>
       <c r="R34" t="n">
-        <v>6919527</v>
+        <v>6919420</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4395,7 +4381,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4405,7 +4391,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4420,22 +4406,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120069700</v>
+        <v>120069084</v>
       </c>
       <c r="B35" t="n">
-        <v>91862</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4444,25 +4430,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4365</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4472,10 +4458,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502566</v>
+        <v>502514</v>
       </c>
       <c r="R35" t="n">
-        <v>6919324</v>
+        <v>6919477</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4507,7 +4493,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4517,7 +4503,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4544,10 +4530,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120065504</v>
+        <v>120065228</v>
       </c>
       <c r="B36" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4560,37 +4546,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502986</v>
+        <v>503010</v>
       </c>
       <c r="R36" t="n">
-        <v>6919325</v>
+        <v>6919294</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4619,7 +4605,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4629,7 +4615,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4644,22 +4630,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120069026</v>
+        <v>120065022</v>
       </c>
       <c r="B37" t="n">
-        <v>90594</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4668,41 +4654,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502514</v>
+        <v>503071</v>
       </c>
       <c r="R37" t="n">
-        <v>6919477</v>
+        <v>6919233</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4731,7 +4726,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4741,7 +4736,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4756,22 +4751,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120068252</v>
+        <v>120067558</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4780,25 +4775,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4808,13 +4803,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502690</v>
+        <v>502813</v>
       </c>
       <c r="R38" t="n">
-        <v>6919538</v>
+        <v>6919527</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4843,7 +4838,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4853,7 +4848,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4868,19 +4863,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120067652</v>
+        <v>120068117</v>
       </c>
       <c r="B39" t="n">
         <v>79131</v>
@@ -4920,13 +4915,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502795</v>
+        <v>502709</v>
       </c>
       <c r="R39" t="n">
-        <v>6919545</v>
+        <v>6919568</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4955,7 +4950,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4965,7 +4960,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4980,22 +4975,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120066170</v>
+        <v>120065915</v>
       </c>
       <c r="B40" t="n">
-        <v>79160</v>
+        <v>57473</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5008,37 +5003,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502988</v>
+        <v>502996</v>
       </c>
       <c r="R40" t="n">
-        <v>6919354</v>
+        <v>6919352</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,22 +5092,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120067493</v>
+        <v>120065504</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>91852</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5120,21 +5120,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502805</v>
+        <v>502986</v>
       </c>
       <c r="R41" t="n">
-        <v>6919532</v>
+        <v>6919325</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5216,10 +5216,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120069367</v>
+        <v>120067689</v>
       </c>
       <c r="B42" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5228,25 +5228,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502491</v>
+        <v>502765</v>
       </c>
       <c r="R42" t="n">
-        <v>6919384</v>
+        <v>6919539</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5328,10 +5328,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120067311</v>
+        <v>120067652</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>79131</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5344,21 +5344,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502822</v>
+        <v>502795</v>
       </c>
       <c r="R43" t="n">
-        <v>6919420</v>
+        <v>6919545</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120067639</v>
+        <v>120067569</v>
       </c>
       <c r="B44" t="n">
         <v>78279</v>
@@ -5480,13 +5480,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502795</v>
+        <v>502813</v>
       </c>
       <c r="R44" t="n">
-        <v>6919546</v>
+        <v>6919527</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5540,22 +5540,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120066174</v>
+        <v>120066423</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5564,41 +5564,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502971</v>
+        <v>502973</v>
       </c>
       <c r="R45" t="n">
-        <v>6919362</v>
+        <v>6919384</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5652,22 +5652,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120065915</v>
+        <v>120069026</v>
       </c>
       <c r="B46" t="n">
-        <v>57473</v>
+        <v>90594</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5680,42 +5680,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502996</v>
+        <v>502514</v>
       </c>
       <c r="R46" t="n">
-        <v>6919352</v>
+        <v>6919477</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5744,7 +5739,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5754,7 +5749,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5769,22 +5764,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120067947</v>
+        <v>120069378</v>
       </c>
       <c r="B47" t="n">
-        <v>90948</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5793,25 +5788,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>298</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5821,13 +5816,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502748</v>
+        <v>502481</v>
       </c>
       <c r="R47" t="n">
-        <v>6919557</v>
+        <v>6919451</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5856,7 +5851,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5866,12 +5861,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Tillsammans med timmergröppa</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5898,10 +5888,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120067689</v>
+        <v>120068130</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5910,25 +5900,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5938,13 +5928,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502765</v>
+        <v>502709</v>
       </c>
       <c r="R48" t="n">
-        <v>6919539</v>
+        <v>6919568</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5973,7 +5963,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5983,7 +5973,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5998,22 +5988,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120064989</v>
+        <v>120069367</v>
       </c>
       <c r="B49" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6026,37 +6016,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503055</v>
+        <v>502491</v>
       </c>
       <c r="R49" t="n">
-        <v>6919216</v>
+        <v>6919384</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6085,7 +6075,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6095,7 +6085,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6110,22 +6100,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120065342</v>
+        <v>120069641</v>
       </c>
       <c r="B50" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6134,38 +6124,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503007</v>
+        <v>502573</v>
       </c>
       <c r="R50" t="n">
-        <v>6919317</v>
+        <v>6919359</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6234,10 +6229,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120067723</v>
+        <v>120067947</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
+        <v>90948</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6246,25 +6241,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6274,13 +6269,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502732</v>
+        <v>502748</v>
       </c>
       <c r="R51" t="n">
-        <v>6919555</v>
+        <v>6919557</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6309,7 +6304,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6319,7 +6314,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Tillsammans med timmergröppa</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6334,19 +6334,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120068337</v>
+        <v>120068252</v>
       </c>
       <c r="B52" t="n">
         <v>91858</v>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502628</v>
+        <v>502690</v>
       </c>
       <c r="R52" t="n">
-        <v>6919549</v>
+        <v>6919538</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120069360</v>
+        <v>120068779</v>
       </c>
       <c r="B53" t="n">
-        <v>78279</v>
+        <v>91902</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6474,21 +6474,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6498,13 +6498,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502491</v>
+        <v>502513</v>
       </c>
       <c r="R53" t="n">
-        <v>6919384</v>
+        <v>6919490</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6558,22 +6558,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120068117</v>
+        <v>120068337</v>
       </c>
       <c r="B54" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>502709</v>
+        <v>502628</v>
       </c>
       <c r="R54" t="n">
-        <v>6919568</v>
+        <v>6919549</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,19 +6670,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120118347</v>
+        <v>120142102</v>
       </c>
       <c r="B55" t="n">
         <v>78187</v>
@@ -6716,16 +6716,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>502471</v>
+        <v>502265</v>
       </c>
       <c r="R55" t="n">
-        <v>6919424</v>
+        <v>6919613</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6755,27 +6758,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6900,10 +6894,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120120273</v>
+        <v>120121333</v>
       </c>
       <c r="B57" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6912,25 +6906,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6940,10 +6934,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502391</v>
+        <v>502264</v>
       </c>
       <c r="R57" t="n">
-        <v>6919666</v>
+        <v>6919557</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6975,7 +6969,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6985,7 +6979,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7012,10 +7006,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120121333</v>
+        <v>120118347</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7024,25 +7018,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7052,10 +7046,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502264</v>
+        <v>502471</v>
       </c>
       <c r="R58" t="n">
-        <v>6919557</v>
+        <v>6919424</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7087,7 +7081,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7097,7 +7091,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7124,10 +7118,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120119728</v>
+        <v>120120181</v>
       </c>
       <c r="B59" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7136,25 +7130,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7164,10 +7158,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502366</v>
+        <v>502417</v>
       </c>
       <c r="R59" t="n">
-        <v>6919546</v>
+        <v>6919645</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7348,10 +7342,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120142102</v>
+        <v>120119728</v>
       </c>
       <c r="B61" t="n">
-        <v>78187</v>
+        <v>90825</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7360,41 +7354,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502265</v>
+        <v>502366</v>
       </c>
       <c r="R61" t="n">
-        <v>6919613</v>
+        <v>6919546</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7424,18 +7415,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7454,10 +7454,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120142089</v>
+        <v>120142120</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7466,30 +7466,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7497,10 +7502,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502373</v>
+        <v>502335</v>
       </c>
       <c r="R62" t="n">
-        <v>6919669</v>
+        <v>6919623</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7541,7 +7546,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7672,10 +7676,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120118385</v>
+        <v>120142089</v>
       </c>
       <c r="B64" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7684,38 +7688,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502456</v>
+        <v>502373</v>
       </c>
       <c r="R64" t="n">
-        <v>6919412</v>
+        <v>6919669</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7745,27 +7752,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7784,10 +7782,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120142120</v>
+        <v>120120273</v>
       </c>
       <c r="B65" t="n">
-        <v>57473</v>
+        <v>78279</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7800,42 +7798,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>502335</v>
+        <v>502391</v>
       </c>
       <c r="R65" t="n">
-        <v>6919623</v>
+        <v>6919666</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7865,9 +7855,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7894,10 +7894,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120120181</v>
+        <v>120118385</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7906,25 +7906,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502417</v>
+        <v>502456</v>
       </c>
       <c r="R66" t="n">
-        <v>6919645</v>
+        <v>6919412</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120024081</v>
+        <v>120027055</v>
       </c>
       <c r="B2" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502703</v>
+        <v>502889</v>
       </c>
       <c r="R2" t="n">
-        <v>6919322</v>
+        <v>6919376</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120027055</v>
+        <v>120024081</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502889</v>
+        <v>502703</v>
       </c>
       <c r="R3" t="n">
-        <v>6919376</v>
+        <v>6919322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120024626</v>
+        <v>120029012</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,25 +1952,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502784</v>
+        <v>502589</v>
       </c>
       <c r="R13" t="n">
-        <v>6919311</v>
+        <v>6919321</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120029012</v>
+        <v>120024626</v>
       </c>
       <c r="B14" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,25 +2064,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502589</v>
+        <v>502784</v>
       </c>
       <c r="R14" t="n">
-        <v>6919321</v>
+        <v>6919311</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4987,10 +4987,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120065915</v>
+        <v>120065504</v>
       </c>
       <c r="B40" t="n">
-        <v>57473</v>
+        <v>91852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5003,39 +5003,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502996</v>
+        <v>502986</v>
       </c>
       <c r="R40" t="n">
-        <v>6919352</v>
+        <v>6919325</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5104,10 +5099,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120065504</v>
+        <v>120065915</v>
       </c>
       <c r="B41" t="n">
-        <v>91852</v>
+        <v>57473</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5120,34 +5115,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502986</v>
+        <v>502996</v>
       </c>
       <c r="R41" t="n">
-        <v>6919325</v>
+        <v>6919352</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120027055</v>
+        <v>120028274</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502889</v>
+        <v>502778</v>
       </c>
       <c r="R2" t="n">
-        <v>6919376</v>
+        <v>6919405</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120024081</v>
+        <v>120027814</v>
       </c>
       <c r="B3" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502703</v>
+        <v>502886</v>
       </c>
       <c r="R3" t="n">
-        <v>6919322</v>
+        <v>6919441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1016,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120028984</v>
+        <v>120027968</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,43 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502586</v>
+        <v>502856</v>
       </c>
       <c r="R5" t="n">
-        <v>6919340</v>
+        <v>6919392</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120028274</v>
+        <v>120028984</v>
       </c>
       <c r="B6" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,31 +1148,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1182,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502778</v>
+        <v>502586</v>
       </c>
       <c r="R6" t="n">
-        <v>6919405</v>
+        <v>6919340</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1254,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120025266</v>
+        <v>120027055</v>
       </c>
       <c r="B7" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,34 +1265,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502825</v>
+        <v>502889</v>
       </c>
       <c r="R7" t="n">
-        <v>6919306</v>
+        <v>6919376</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120024983</v>
+        <v>120027766</v>
       </c>
       <c r="B8" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,25 +1378,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502808</v>
+        <v>502871</v>
       </c>
       <c r="R8" t="n">
-        <v>6919302</v>
+        <v>6919391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120031101</v>
+        <v>120024406</v>
       </c>
       <c r="B9" t="n">
-        <v>90512</v>
+        <v>79160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,41 +1490,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2013</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502863</v>
+        <v>502726</v>
       </c>
       <c r="R9" t="n">
-        <v>6919305</v>
+        <v>6919308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,18 +1551,27 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1584,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120026409</v>
+        <v>120028686</v>
       </c>
       <c r="B10" t="n">
-        <v>89650</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,34 +1606,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502910</v>
+        <v>502735</v>
       </c>
       <c r="R10" t="n">
-        <v>6919294</v>
+        <v>6919361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1680,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Inte jättegamla.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1712,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120028686</v>
+        <v>120027825</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1732,19 +1748,19 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502735</v>
+        <v>502881</v>
       </c>
       <c r="R11" t="n">
-        <v>6919361</v>
+        <v>6919412</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,12 +1802,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Inte jättegamla.</t>
+          <t>Både gamla och färska spår på samma tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120027825</v>
+        <v>120024983</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,39 +1850,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502881</v>
+        <v>502808</v>
       </c>
       <c r="R12" t="n">
-        <v>6919412</v>
+        <v>6919302</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,11 +1920,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Både gamla och färska spår på samma tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120029012</v>
+        <v>120028546</v>
       </c>
       <c r="B13" t="n">
-        <v>78279</v>
+        <v>90825</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,25 +1958,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1980,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502589</v>
+        <v>502717</v>
       </c>
       <c r="R13" t="n">
-        <v>6919321</v>
+        <v>6919429</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2052,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120024626</v>
+        <v>120029012</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,25 +2070,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502784</v>
+        <v>502589</v>
       </c>
       <c r="R14" t="n">
-        <v>6919311</v>
+        <v>6919321</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120028546</v>
+        <v>120024626</v>
       </c>
       <c r="B15" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,25 +2182,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2204,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502717</v>
+        <v>502784</v>
       </c>
       <c r="R15" t="n">
-        <v>6919429</v>
+        <v>6919311</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120024406</v>
+        <v>120026409</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>89650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,34 +2298,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502726</v>
+        <v>502910</v>
       </c>
       <c r="R16" t="n">
-        <v>6919308</v>
+        <v>6919294</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2388,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120027766</v>
+        <v>120031101</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>90512</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,38 +2406,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>2013</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502871</v>
+        <v>502863</v>
       </c>
       <c r="R17" t="n">
-        <v>6919391</v>
+        <v>6919305</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,27 +2470,18 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120027968</v>
+        <v>120025266</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,25 +2512,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502856</v>
+        <v>502825</v>
       </c>
       <c r="R18" t="n">
-        <v>6919392</v>
+        <v>6919306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2612,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120027814</v>
+        <v>120024081</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,38 +2624,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502886</v>
+        <v>502703</v>
       </c>
       <c r="R19" t="n">
-        <v>6919441</v>
+        <v>6919322</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120064989</v>
+        <v>120065022</v>
       </c>
       <c r="B20" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,41 +2736,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503055</v>
+        <v>503071</v>
       </c>
       <c r="R20" t="n">
-        <v>6919216</v>
+        <v>6919233</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,22 +2833,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120069360</v>
+        <v>120068252</v>
       </c>
       <c r="B21" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,25 +2857,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2876,10 +2885,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502491</v>
+        <v>502690</v>
       </c>
       <c r="R21" t="n">
-        <v>6919384</v>
+        <v>6919538</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,10 +2957,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120067493</v>
+        <v>120067569</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2964,21 +2973,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,13 +2997,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502805</v>
+        <v>502813</v>
       </c>
       <c r="R22" t="n">
-        <v>6919532</v>
+        <v>6919527</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3023,7 +3032,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3042,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,22 +3057,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120069993</v>
+        <v>120069378</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,50 +3081,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502615</v>
+        <v>502481</v>
       </c>
       <c r="R23" t="n">
-        <v>6919305</v>
+        <v>6919451</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120065324</v>
+        <v>120069969</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>78187</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3197,39 +3197,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503005</v>
+        <v>502630</v>
       </c>
       <c r="R24" t="n">
-        <v>6919310</v>
+        <v>6919303</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3298,10 +3293,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120069700</v>
+        <v>120067558</v>
       </c>
       <c r="B25" t="n">
-        <v>91862</v>
+        <v>79131</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3310,25 +3305,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3338,10 +3333,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502566</v>
+        <v>502813</v>
       </c>
       <c r="R25" t="n">
-        <v>6919324</v>
+        <v>6919527</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3373,7 +3368,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3383,7 +3378,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3410,10 +3405,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120067975</v>
+        <v>120067639</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3422,25 +3417,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3450,13 +3445,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502758</v>
+        <v>502795</v>
       </c>
       <c r="R26" t="n">
-        <v>6919553</v>
+        <v>6919546</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3485,7 +3480,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3495,7 +3490,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,19 +3505,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120066174</v>
+        <v>120068337</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3562,10 +3557,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502971</v>
+        <v>502628</v>
       </c>
       <c r="R27" t="n">
-        <v>6919362</v>
+        <v>6919549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3634,7 +3629,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120067723</v>
+        <v>120067975</v>
       </c>
       <c r="B28" t="n">
         <v>91858</v>
@@ -3674,13 +3669,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502732</v>
+        <v>502758</v>
       </c>
       <c r="R28" t="n">
-        <v>6919555</v>
+        <v>6919553</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3709,7 +3704,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,7 +3714,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3734,22 +3729,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120069969</v>
+        <v>120066174</v>
       </c>
       <c r="B29" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3758,25 +3753,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3786,10 +3781,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502630</v>
+        <v>502971</v>
       </c>
       <c r="R29" t="n">
-        <v>6919303</v>
+        <v>6919362</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,10 +3853,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120065342</v>
+        <v>120067493</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3870,25 +3865,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3893,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503007</v>
+        <v>502805</v>
       </c>
       <c r="R30" t="n">
-        <v>6919317</v>
+        <v>6919532</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3970,10 +3965,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120066170</v>
+        <v>120065504</v>
       </c>
       <c r="B31" t="n">
-        <v>79160</v>
+        <v>91852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3986,37 +3981,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502988</v>
+        <v>502986</v>
       </c>
       <c r="R31" t="n">
-        <v>6919354</v>
+        <v>6919325</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4045,7 +4040,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4055,7 +4050,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,22 +4065,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120065184</v>
+        <v>120067723</v>
       </c>
       <c r="B32" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4094,41 +4089,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503055</v>
+        <v>502732</v>
       </c>
       <c r="R32" t="n">
-        <v>6919216</v>
+        <v>6919555</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4157,7 +4152,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4167,7 +4162,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,22 +4177,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120067639</v>
+        <v>120069993</v>
       </c>
       <c r="B33" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4206,41 +4201,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502795</v>
+        <v>502615</v>
       </c>
       <c r="R33" t="n">
-        <v>6919546</v>
+        <v>6919305</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4269,7 +4273,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4279,7 +4283,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,22 +4298,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120067311</v>
+        <v>120069360</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4322,21 +4326,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4346,10 +4350,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502822</v>
+        <v>502491</v>
       </c>
       <c r="R34" t="n">
-        <v>6919420</v>
+        <v>6919384</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4418,10 +4422,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120069084</v>
+        <v>120067947</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>90948</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4430,25 +4434,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4458,10 +4462,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502514</v>
+        <v>502748</v>
       </c>
       <c r="R35" t="n">
-        <v>6919477</v>
+        <v>6919557</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4493,7 +4497,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4503,7 +4507,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Tillsammans med timmergröppa</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,10 +4539,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120065228</v>
+        <v>120068117</v>
       </c>
       <c r="B36" t="n">
-        <v>91902</v>
+        <v>79131</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4546,34 +4555,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503010</v>
+        <v>502709</v>
       </c>
       <c r="R36" t="n">
-        <v>6919294</v>
+        <v>6919568</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4605,7 +4614,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4615,7 +4624,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4642,10 +4651,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120065022</v>
+        <v>120067689</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4654,47 +4663,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503071</v>
+        <v>502765</v>
       </c>
       <c r="R37" t="n">
-        <v>6919233</v>
+        <v>6919539</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4763,10 +4763,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120067558</v>
+        <v>120068130</v>
       </c>
       <c r="B38" t="n">
-        <v>79131</v>
+        <v>79160</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4779,21 +4779,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502813</v>
+        <v>502709</v>
       </c>
       <c r="R38" t="n">
-        <v>6919527</v>
+        <v>6919568</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4875,10 +4875,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120068117</v>
+        <v>120065184</v>
       </c>
       <c r="B39" t="n">
-        <v>79131</v>
+        <v>79160</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4891,34 +4891,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502709</v>
+        <v>503055</v>
       </c>
       <c r="R39" t="n">
-        <v>6919568</v>
+        <v>6919216</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4987,10 +4987,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120065504</v>
+        <v>120067311</v>
       </c>
       <c r="B40" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5003,21 +5003,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502986</v>
+        <v>502822</v>
       </c>
       <c r="R40" t="n">
-        <v>6919325</v>
+        <v>6919420</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5099,10 +5099,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120065915</v>
+        <v>120065342</v>
       </c>
       <c r="B41" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5111,43 +5111,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502996</v>
+        <v>503007</v>
       </c>
       <c r="R41" t="n">
-        <v>6919352</v>
+        <v>6919317</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5216,10 +5211,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120067689</v>
+        <v>120066423</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5228,41 +5223,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502765</v>
+        <v>502973</v>
       </c>
       <c r="R42" t="n">
-        <v>6919539</v>
+        <v>6919384</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5291,7 +5286,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5301,7 +5296,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,22 +5311,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120067652</v>
+        <v>120066170</v>
       </c>
       <c r="B43" t="n">
-        <v>79131</v>
+        <v>79160</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5344,37 +5339,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502795</v>
+        <v>502988</v>
       </c>
       <c r="R43" t="n">
-        <v>6919545</v>
+        <v>6919354</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5403,7 +5398,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5413,7 +5408,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,22 +5423,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120067569</v>
+        <v>120068779</v>
       </c>
       <c r="B44" t="n">
-        <v>78279</v>
+        <v>91902</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5456,21 +5451,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5480,10 +5475,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502813</v>
+        <v>502513</v>
       </c>
       <c r="R44" t="n">
-        <v>6919527</v>
+        <v>6919490</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5515,7 +5510,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5525,7 +5520,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5552,7 +5547,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120066423</v>
+        <v>120064989</v>
       </c>
       <c r="B45" t="n">
         <v>78279</v>
@@ -5588,14 +5583,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502973</v>
+        <v>503055</v>
       </c>
       <c r="R45" t="n">
-        <v>6919384</v>
+        <v>6919216</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5627,7 +5622,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5637,7 +5632,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5664,10 +5659,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120069026</v>
+        <v>120069367</v>
       </c>
       <c r="B46" t="n">
-        <v>90594</v>
+        <v>78278</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5680,21 +5675,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5704,13 +5699,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502514</v>
+        <v>502491</v>
       </c>
       <c r="R46" t="n">
-        <v>6919477</v>
+        <v>6919384</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5739,7 +5734,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5749,7 +5744,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5764,22 +5759,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120069378</v>
+        <v>120065228</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5788,41 +5783,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502481</v>
+        <v>503010</v>
       </c>
       <c r="R47" t="n">
-        <v>6919451</v>
+        <v>6919294</v>
       </c>
       <c r="S47" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5851,7 +5846,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5861,7 +5856,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5888,10 +5883,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120068130</v>
+        <v>120069700</v>
       </c>
       <c r="B48" t="n">
-        <v>79160</v>
+        <v>91862</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5900,25 +5895,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5928,10 +5923,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502709</v>
+        <v>502566</v>
       </c>
       <c r="R48" t="n">
-        <v>6919568</v>
+        <v>6919324</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5963,7 +5958,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5973,7 +5968,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6000,10 +5995,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120069367</v>
+        <v>120065324</v>
       </c>
       <c r="B49" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6016,34 +6011,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502491</v>
+        <v>503005</v>
       </c>
       <c r="R49" t="n">
-        <v>6919384</v>
+        <v>6919310</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120067947</v>
+        <v>120069084</v>
       </c>
       <c r="B51" t="n">
-        <v>90948</v>
+        <v>90545</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6241,25 +6241,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>298</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502748</v>
+        <v>502514</v>
       </c>
       <c r="R51" t="n">
-        <v>6919557</v>
+        <v>6919477</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6314,12 +6314,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Tillsammans med timmergröppa</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6346,10 +6341,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120068252</v>
+        <v>120067652</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6358,25 +6353,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6386,10 +6381,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502690</v>
+        <v>502795</v>
       </c>
       <c r="R52" t="n">
-        <v>6919538</v>
+        <v>6919545</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6458,10 +6453,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120068779</v>
+        <v>120065915</v>
       </c>
       <c r="B53" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6474,37 +6469,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502513</v>
+        <v>502996</v>
       </c>
       <c r="R53" t="n">
-        <v>6919490</v>
+        <v>6919352</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6558,22 +6558,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120068337</v>
+        <v>120069026</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>90594</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>502628</v>
+        <v>502514</v>
       </c>
       <c r="R54" t="n">
-        <v>6919549</v>
+        <v>6919477</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,22 +6670,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120142102</v>
+        <v>120119728</v>
       </c>
       <c r="B55" t="n">
-        <v>78187</v>
+        <v>90825</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6694,41 +6694,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>502265</v>
+        <v>502366</v>
       </c>
       <c r="R55" t="n">
-        <v>6919613</v>
+        <v>6919546</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6758,18 +6755,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6788,7 +6794,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120142073</v>
+        <v>120142102</v>
       </c>
       <c r="B56" t="n">
         <v>78187</v>
@@ -6831,10 +6837,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502373</v>
+        <v>502265</v>
       </c>
       <c r="R56" t="n">
-        <v>6919669</v>
+        <v>6919613</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6894,10 +6900,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120121333</v>
+        <v>120118347</v>
       </c>
       <c r="B57" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6906,25 +6912,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6934,10 +6940,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502264</v>
+        <v>502471</v>
       </c>
       <c r="R57" t="n">
-        <v>6919557</v>
+        <v>6919424</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6969,7 +6975,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6979,7 +6985,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7006,10 +7012,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120118347</v>
+        <v>120120273</v>
       </c>
       <c r="B58" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7022,21 +7028,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7046,10 +7052,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502471</v>
+        <v>502391</v>
       </c>
       <c r="R58" t="n">
-        <v>6919424</v>
+        <v>6919666</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7230,10 +7236,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120120227</v>
+        <v>120142073</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7246,34 +7252,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502410</v>
+        <v>502373</v>
       </c>
       <c r="R60" t="n">
-        <v>6919658</v>
+        <v>6919669</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7303,27 +7312,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7342,10 +7342,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120119728</v>
+        <v>120142120</v>
       </c>
       <c r="B61" t="n">
-        <v>90825</v>
+        <v>57473</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7354,38 +7354,46 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>65</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502366</v>
+        <v>502335</v>
       </c>
       <c r="R61" t="n">
-        <v>6919546</v>
+        <v>6919623</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7415,19 +7423,9 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7454,10 +7452,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120142120</v>
+        <v>120121333</v>
       </c>
       <c r="B62" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7466,46 +7464,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502335</v>
+        <v>502264</v>
       </c>
       <c r="R62" t="n">
-        <v>6919623</v>
+        <v>6919557</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7535,9 +7525,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7564,7 +7564,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120119046</v>
+        <v>120118385</v>
       </c>
       <c r="B63" t="n">
         <v>78279</v>
@@ -7604,10 +7604,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502418</v>
+        <v>502456</v>
       </c>
       <c r="R63" t="n">
-        <v>6919456</v>
+        <v>6919412</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7782,10 +7782,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120120273</v>
+        <v>120120227</v>
       </c>
       <c r="B65" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7798,21 +7798,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7822,10 +7822,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>502391</v>
+        <v>502410</v>
       </c>
       <c r="R65" t="n">
-        <v>6919666</v>
+        <v>6919658</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120118385</v>
+        <v>120119046</v>
       </c>
       <c r="B66" t="n">
         <v>78279</v>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502456</v>
+        <v>502418</v>
       </c>
       <c r="R66" t="n">
-        <v>6919412</v>
+        <v>6919456</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120028274</v>
+        <v>120024626</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502778</v>
+        <v>502784</v>
       </c>
       <c r="R2" t="n">
-        <v>6919405</v>
+        <v>6919311</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120027814</v>
+        <v>120024983</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502886</v>
+        <v>502808</v>
       </c>
       <c r="R3" t="n">
-        <v>6919441</v>
+        <v>6919302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120028121</v>
+        <v>120025266</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>78279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502828</v>
+        <v>502825</v>
       </c>
       <c r="R4" t="n">
-        <v>6919422</v>
+        <v>6919306</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1132,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120028984</v>
+        <v>120028274</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,27 +1139,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502586</v>
+        <v>502778</v>
       </c>
       <c r="R6" t="n">
-        <v>6919340</v>
+        <v>6919405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120027055</v>
+        <v>120028686</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1290,14 +1285,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502889</v>
+        <v>502735</v>
       </c>
       <c r="R7" t="n">
-        <v>6919376</v>
+        <v>6919361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1334,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Inte jättegamla.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120027766</v>
+        <v>120026409</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,38 +1378,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502871</v>
+        <v>502910</v>
       </c>
       <c r="R8" t="n">
-        <v>6919391</v>
+        <v>6919294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120024406</v>
+        <v>120028546</v>
       </c>
       <c r="B9" t="n">
-        <v>79160</v>
+        <v>90825</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502726</v>
+        <v>502717</v>
       </c>
       <c r="R9" t="n">
-        <v>6919308</v>
+        <v>6919429</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120028686</v>
+        <v>120027766</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,43 +1602,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502735</v>
+        <v>502871</v>
       </c>
       <c r="R10" t="n">
-        <v>6919361</v>
+        <v>6919391</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,12 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Inte jättegamla.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1834,7 +1824,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120024983</v>
+        <v>120024081</v>
       </c>
       <c r="B12" t="n">
         <v>78279</v>
@@ -1874,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502808</v>
+        <v>502703</v>
       </c>
       <c r="R12" t="n">
-        <v>6919302</v>
+        <v>6919322</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1946,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120028546</v>
+        <v>120024406</v>
       </c>
       <c r="B13" t="n">
-        <v>90825</v>
+        <v>79160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,25 +1948,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1986,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502717</v>
+        <v>502726</v>
       </c>
       <c r="R13" t="n">
-        <v>6919429</v>
+        <v>6919308</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2170,10 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120024626</v>
+        <v>120031101</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>90512</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,38 +2172,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>2013</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502784</v>
+        <v>502863</v>
       </c>
       <c r="R15" t="n">
-        <v>6919311</v>
+        <v>6919305</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,27 +2236,18 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2282,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120026409</v>
+        <v>120027814</v>
       </c>
       <c r="B16" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,38 +2278,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502910</v>
+        <v>502886</v>
       </c>
       <c r="R16" t="n">
-        <v>6919294</v>
+        <v>6919441</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2394,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120031101</v>
+        <v>120028121</v>
       </c>
       <c r="B17" t="n">
-        <v>90512</v>
+        <v>90545</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,41 +2390,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2013</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502863</v>
+        <v>502828</v>
       </c>
       <c r="R17" t="n">
-        <v>6919305</v>
+        <v>6919422</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,18 +2451,27 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2500,10 +2490,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120025266</v>
+        <v>120027055</v>
       </c>
       <c r="B18" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,34 +2506,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502825</v>
+        <v>502889</v>
       </c>
       <c r="R18" t="n">
-        <v>6919306</v>
+        <v>6919376</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2612,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120024081</v>
+        <v>120028984</v>
       </c>
       <c r="B19" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2628,34 +2623,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502703</v>
+        <v>502586</v>
       </c>
       <c r="R19" t="n">
-        <v>6919322</v>
+        <v>6919340</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120065022</v>
+        <v>120065504</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,47 +2736,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503071</v>
+        <v>502986</v>
       </c>
       <c r="R20" t="n">
-        <v>6919233</v>
+        <v>6919325</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2845,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120068252</v>
+        <v>120067311</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,25 +2848,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2885,10 +2876,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502690</v>
+        <v>502822</v>
       </c>
       <c r="R21" t="n">
-        <v>6919538</v>
+        <v>6919420</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,10 +2948,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120067569</v>
+        <v>120068130</v>
       </c>
       <c r="B22" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2973,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2997,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502813</v>
+        <v>502709</v>
       </c>
       <c r="R22" t="n">
-        <v>6919527</v>
+        <v>6919568</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3032,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3042,7 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3069,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120069378</v>
+        <v>120069084</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3085,21 +3076,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3109,13 +3100,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502481</v>
+        <v>502514</v>
       </c>
       <c r="R23" t="n">
-        <v>6919451</v>
+        <v>6919477</v>
       </c>
       <c r="S23" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3144,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3154,7 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3181,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120069969</v>
+        <v>120065324</v>
       </c>
       <c r="B24" t="n">
-        <v>78187</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3197,34 +3188,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502630</v>
+        <v>503005</v>
       </c>
       <c r="R24" t="n">
-        <v>6919303</v>
+        <v>6919310</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3293,10 +3289,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120067558</v>
+        <v>120069641</v>
       </c>
       <c r="B25" t="n">
-        <v>79131</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3309,37 +3305,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502813</v>
+        <v>502573</v>
       </c>
       <c r="R25" t="n">
-        <v>6919527</v>
+        <v>6919359</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3368,7 +3369,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3378,7 +3379,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3393,22 +3394,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120067639</v>
+        <v>120067558</v>
       </c>
       <c r="B26" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3421,21 +3422,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3445,13 +3446,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502795</v>
+        <v>502813</v>
       </c>
       <c r="R26" t="n">
-        <v>6919546</v>
+        <v>6919527</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3480,7 +3481,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3490,7 +3491,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3505,22 +3506,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120068337</v>
+        <v>120065184</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3529,41 +3530,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502628</v>
+        <v>503055</v>
       </c>
       <c r="R27" t="n">
-        <v>6919549</v>
+        <v>6919216</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3592,7 +3593,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3602,7 +3603,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,22 +3618,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120067975</v>
+        <v>120067639</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3641,25 +3642,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3669,13 +3670,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502758</v>
+        <v>502795</v>
       </c>
       <c r="R28" t="n">
-        <v>6919553</v>
+        <v>6919546</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3704,7 +3705,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3714,7 +3715,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,22 +3730,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120066174</v>
+        <v>120069969</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3753,25 +3754,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3781,10 +3782,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502971</v>
+        <v>502630</v>
       </c>
       <c r="R29" t="n">
-        <v>6919362</v>
+        <v>6919303</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3853,10 +3854,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120067493</v>
+        <v>120069378</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3865,25 +3866,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3893,13 +3894,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502805</v>
+        <v>502481</v>
       </c>
       <c r="R30" t="n">
-        <v>6919532</v>
+        <v>6919451</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3928,7 +3929,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3938,7 +3939,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3953,22 +3954,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120065504</v>
+        <v>120065915</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
+        <v>57473</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3981,34 +3982,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502986</v>
+        <v>502996</v>
       </c>
       <c r="R31" t="n">
-        <v>6919325</v>
+        <v>6919352</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4077,10 +4083,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120067723</v>
+        <v>120069367</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4089,25 +4095,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4117,10 +4123,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502732</v>
+        <v>502491</v>
       </c>
       <c r="R32" t="n">
-        <v>6919555</v>
+        <v>6919384</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4189,10 +4195,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120069993</v>
+        <v>120068117</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>79131</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4201,47 +4207,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502615</v>
+        <v>502709</v>
       </c>
       <c r="R33" t="n">
-        <v>6919305</v>
+        <v>6919568</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4273,7 +4270,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4283,7 +4280,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4310,10 +4307,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120069360</v>
+        <v>120067689</v>
       </c>
       <c r="B34" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4322,25 +4319,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4350,10 +4347,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502491</v>
+        <v>502765</v>
       </c>
       <c r="R34" t="n">
-        <v>6919384</v>
+        <v>6919539</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4539,10 +4536,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120068117</v>
+        <v>120068779</v>
       </c>
       <c r="B36" t="n">
-        <v>79131</v>
+        <v>91902</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4555,21 +4552,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4579,10 +4576,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502709</v>
+        <v>502513</v>
       </c>
       <c r="R36" t="n">
-        <v>6919568</v>
+        <v>6919490</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4614,7 +4611,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4624,7 +4621,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4651,10 +4648,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120067689</v>
+        <v>120064989</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4663,41 +4660,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502765</v>
+        <v>503055</v>
       </c>
       <c r="R37" t="n">
-        <v>6919539</v>
+        <v>6919216</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4726,7 +4723,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4736,7 +4733,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4751,22 +4748,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120068130</v>
+        <v>120069026</v>
       </c>
       <c r="B38" t="n">
-        <v>79160</v>
+        <v>90594</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4779,21 +4776,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4803,10 +4800,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502709</v>
+        <v>502514</v>
       </c>
       <c r="R38" t="n">
-        <v>6919568</v>
+        <v>6919477</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4838,7 +4835,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4848,7 +4845,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4875,10 +4872,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120065184</v>
+        <v>120067569</v>
       </c>
       <c r="B39" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4891,34 +4888,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503055</v>
+        <v>502813</v>
       </c>
       <c r="R39" t="n">
-        <v>6919216</v>
+        <v>6919527</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4950,7 +4947,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4960,7 +4957,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4987,10 +4984,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120067311</v>
+        <v>120066170</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5003,37 +5000,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502822</v>
+        <v>502988</v>
       </c>
       <c r="R40" t="n">
-        <v>6919420</v>
+        <v>6919354</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5062,7 +5059,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5072,7 +5069,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5087,19 +5084,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120065342</v>
+        <v>120067975</v>
       </c>
       <c r="B41" t="n">
         <v>91858</v>
@@ -5139,13 +5136,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503007</v>
+        <v>502758</v>
       </c>
       <c r="R41" t="n">
-        <v>6919317</v>
+        <v>6919553</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5174,7 +5171,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5184,7 +5181,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,22 +5196,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120066423</v>
+        <v>120069993</v>
       </c>
       <c r="B42" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5223,38 +5220,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502973</v>
+        <v>502615</v>
       </c>
       <c r="R42" t="n">
-        <v>6919384</v>
+        <v>6919305</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5286,7 +5292,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5296,7 +5302,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5323,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120066170</v>
+        <v>120065022</v>
       </c>
       <c r="B43" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5335,41 +5341,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502988</v>
+        <v>503071</v>
       </c>
       <c r="R43" t="n">
-        <v>6919354</v>
+        <v>6919233</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5398,7 +5413,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5408,7 +5423,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5423,19 +5438,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120068779</v>
+        <v>120065228</v>
       </c>
       <c r="B44" t="n">
         <v>91902</v>
@@ -5471,14 +5486,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502513</v>
+        <v>503010</v>
       </c>
       <c r="R44" t="n">
-        <v>6919490</v>
+        <v>6919294</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5510,7 +5525,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5520,7 +5535,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5547,10 +5562,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120064989</v>
+        <v>120065342</v>
       </c>
       <c r="B45" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5559,41 +5574,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503055</v>
+        <v>503007</v>
       </c>
       <c r="R45" t="n">
-        <v>6919216</v>
+        <v>6919317</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5622,7 +5637,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5632,7 +5647,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5647,22 +5662,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120069367</v>
+        <v>120067723</v>
       </c>
       <c r="B46" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5671,25 +5686,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5699,10 +5714,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502491</v>
+        <v>502732</v>
       </c>
       <c r="R46" t="n">
-        <v>6919384</v>
+        <v>6919555</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5771,10 +5786,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120065228</v>
+        <v>120067493</v>
       </c>
       <c r="B47" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5787,37 +5802,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503010</v>
+        <v>502805</v>
       </c>
       <c r="R47" t="n">
-        <v>6919294</v>
+        <v>6919532</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5846,7 +5861,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5856,7 +5871,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5871,12 +5886,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5995,10 +6010,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120065324</v>
+        <v>120068252</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6007,43 +6022,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503005</v>
+        <v>502690</v>
       </c>
       <c r="R49" t="n">
-        <v>6919310</v>
+        <v>6919538</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6112,10 +6122,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120069641</v>
+        <v>120068337</v>
       </c>
       <c r="B50" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6124,43 +6134,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502573</v>
+        <v>502628</v>
       </c>
       <c r="R50" t="n">
-        <v>6919359</v>
+        <v>6919549</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6229,10 +6234,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120069084</v>
+        <v>120067652</v>
       </c>
       <c r="B51" t="n">
-        <v>90545</v>
+        <v>79131</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6241,25 +6246,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6269,13 +6274,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502514</v>
+        <v>502795</v>
       </c>
       <c r="R51" t="n">
-        <v>6919477</v>
+        <v>6919545</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6304,7 +6309,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6314,7 +6319,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,22 +6334,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120067652</v>
+        <v>120066423</v>
       </c>
       <c r="B52" t="n">
-        <v>79131</v>
+        <v>78279</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6357,37 +6362,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hedtjärnen, Hedtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502795</v>
+        <v>502973</v>
       </c>
       <c r="R52" t="n">
-        <v>6919545</v>
+        <v>6919384</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6416,7 +6421,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6426,7 +6431,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6441,22 +6446,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120065915</v>
+        <v>120066174</v>
       </c>
       <c r="B53" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6465,43 +6470,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502996</v>
+        <v>502971</v>
       </c>
       <c r="R53" t="n">
-        <v>6919352</v>
+        <v>6919362</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120069026</v>
+        <v>120069360</v>
       </c>
       <c r="B54" t="n">
-        <v>90594</v>
+        <v>78279</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6586,21 +6586,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>502514</v>
+        <v>502491</v>
       </c>
       <c r="R54" t="n">
-        <v>6919477</v>
+        <v>6919384</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,22 +6670,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120119728</v>
+        <v>120120181</v>
       </c>
       <c r="B55" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6694,25 +6694,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>502366</v>
+        <v>502417</v>
       </c>
       <c r="R55" t="n">
-        <v>6919546</v>
+        <v>6919645</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6794,7 +6794,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120142102</v>
+        <v>120118347</v>
       </c>
       <c r="B56" t="n">
         <v>78187</v>
@@ -6828,19 +6828,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502265</v>
+        <v>502471</v>
       </c>
       <c r="R56" t="n">
-        <v>6919613</v>
+        <v>6919424</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6870,18 +6867,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6900,10 +6906,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120118347</v>
+        <v>120142089</v>
       </c>
       <c r="B57" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6912,38 +6918,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502471</v>
+        <v>502373</v>
       </c>
       <c r="R57" t="n">
-        <v>6919424</v>
+        <v>6919669</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6973,27 +6982,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7012,10 +7012,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120120273</v>
+        <v>120121333</v>
       </c>
       <c r="B58" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7024,25 +7024,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7052,10 +7052,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502391</v>
+        <v>502264</v>
       </c>
       <c r="R58" t="n">
-        <v>6919666</v>
+        <v>6919557</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7124,10 +7124,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120120181</v>
+        <v>120120227</v>
       </c>
       <c r="B59" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7136,25 +7136,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502417</v>
+        <v>502410</v>
       </c>
       <c r="R59" t="n">
-        <v>6919645</v>
+        <v>6919658</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7236,10 +7236,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120142073</v>
+        <v>120119046</v>
       </c>
       <c r="B60" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7252,37 +7252,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502373</v>
+        <v>502418</v>
       </c>
       <c r="R60" t="n">
-        <v>6919669</v>
+        <v>6919456</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7312,18 +7309,27 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7342,10 +7348,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120142120</v>
+        <v>120119728</v>
       </c>
       <c r="B61" t="n">
-        <v>57473</v>
+        <v>90825</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7354,46 +7360,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>65</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502335</v>
+        <v>502366</v>
       </c>
       <c r="R61" t="n">
-        <v>6919623</v>
+        <v>6919546</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7423,9 +7421,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7452,10 +7460,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120121333</v>
+        <v>120120273</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7464,25 +7472,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7492,10 +7500,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502264</v>
+        <v>502391</v>
       </c>
       <c r="R62" t="n">
-        <v>6919557</v>
+        <v>6919666</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7527,7 +7535,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7537,7 +7545,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7564,10 +7572,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120118385</v>
+        <v>120142120</v>
       </c>
       <c r="B63" t="n">
-        <v>78279</v>
+        <v>57473</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7580,34 +7588,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502456</v>
+        <v>502335</v>
       </c>
       <c r="R63" t="n">
-        <v>6919412</v>
+        <v>6919623</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7637,19 +7653,9 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>09:29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7676,10 +7682,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120142089</v>
+        <v>120142102</v>
       </c>
       <c r="B64" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7688,25 +7694,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7719,10 +7725,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502373</v>
+        <v>502265</v>
       </c>
       <c r="R64" t="n">
-        <v>6919669</v>
+        <v>6919613</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7782,10 +7788,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120120227</v>
+        <v>120118385</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7798,21 +7804,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7822,10 +7828,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>502410</v>
+        <v>502456</v>
       </c>
       <c r="R65" t="n">
-        <v>6919658</v>
+        <v>6919412</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7894,10 +7900,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120119046</v>
+        <v>120142073</v>
       </c>
       <c r="B66" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7910,34 +7916,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502418</v>
+        <v>502373</v>
       </c>
       <c r="R66" t="n">
-        <v>6919456</v>
+        <v>6919669</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7967,27 +7976,18 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -4760,10 +4760,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120069026</v>
+        <v>120067569</v>
       </c>
       <c r="B38" t="n">
-        <v>90594</v>
+        <v>78279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4776,21 +4776,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502514</v>
+        <v>502813</v>
       </c>
       <c r="R38" t="n">
-        <v>6919477</v>
+        <v>6919527</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4872,10 +4872,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120067569</v>
+        <v>120069026</v>
       </c>
       <c r="B39" t="n">
-        <v>78279</v>
+        <v>90594</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4888,21 +4888,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502813</v>
+        <v>502514</v>
       </c>
       <c r="R39" t="n">
-        <v>6919527</v>
+        <v>6919477</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>120031101</v>
       </c>
       <c r="B4" t="n">
-        <v>90619</v>
+        <v>90629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>120031101</v>
       </c>
       <c r="B4" t="n">
-        <v>90629</v>
+        <v>90641</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>120031101</v>
       </c>
       <c r="B4" t="n">
-        <v>90641</v>
+        <v>90642</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>120031101</v>
       </c>
       <c r="B4" t="n">
-        <v>90642</v>
+        <v>90645</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>120031101</v>
       </c>
       <c r="B4" t="n">
-        <v>90645</v>
+        <v>90651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>120031101</v>
       </c>
       <c r="B4" t="n">
-        <v>90651</v>
+        <v>90652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>120031101</v>
       </c>
       <c r="B4" t="n">
-        <v>90652</v>
+        <v>90657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120027055</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>120028984</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>120028686</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>120027825</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>120065324</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120027055</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>120028984</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>120028686</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>120027825</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>120065324</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120027055</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>120028984</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>120028686</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>120027825</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>120065324</v>
       </c>
       <c r="B43" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 41416-2024 artfynd.xlsx
+++ b/artfynd/A 41416-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8004,6 +8004,134 @@
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125885646</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6281</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100524</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Skrovlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Calitys scabra</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Thunberg, 1784)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Haverö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>502716</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6919285</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Foto av Isabelle Holmström. Artbestämd av Magnus Andersson på foran</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
